--- a/config/成衣工艺单_设计师填表模板_v7.xlsx
+++ b/config/成衣工艺单_设计师填表模板_v7.xlsx
@@ -17,7 +17,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="26">
+  <fonts count="28">
     <font>
       <name val="宋体"/>
       <charset val="134"/>
@@ -202,10 +202,20 @@
     </font>
     <font>
       <b val="1"/>
+      <color rgb="00FFFFFF"/>
       <sz val="12"/>
     </font>
+    <font>
+      <b val="1"/>
+      <sz val="12"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <color rgb="00FFFFFF"/>
+      <sz val="10"/>
+    </font>
   </fonts>
-  <fills count="38">
+  <fills count="40">
     <fill>
       <patternFill/>
     </fill>
@@ -426,6 +436,16 @@
       <patternFill patternType="solid">
         <fgColor theme="9" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="004472C4"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FFFF00"/>
       </patternFill>
     </fill>
   </fills>
@@ -775,7 +795,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="24">
+  <cellXfs count="26">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -831,7 +851,9 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="25" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="26" fillId="39" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="27" fillId="38" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="25" fillId="38" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="49">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
@@ -1244,13 +1266,13 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:S43"/>
+  <dimension ref="A1:S59"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
-    <col width="8.75" customWidth="1" min="1" max="1"/>
-    <col width="13" customWidth="1" min="2" max="2"/>
-    <col width="11.875" customWidth="1" min="3" max="3"/>
-    <col width="13" customWidth="1" min="4" max="6"/>
+    <col width="8" customWidth="1" min="1" max="1"/>
+    <col width="28" customWidth="1" min="2" max="2"/>
+    <col width="16" customWidth="1" min="3" max="3"/>
+    <col width="10" customWidth="1" min="4" max="6"/>
     <col width="10" customWidth="1" min="7" max="7"/>
     <col width="9.75" customWidth="1" min="8" max="8"/>
     <col width="8.125" customWidth="1" min="9" max="9"/>
@@ -1372,586 +1394,705 @@
       <c r="Q10" s="8" t="inlineStr"/>
     </row>
     <row r="12" ht="24" customHeight="1">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>▼ 工艺制作（三区）</t>
+      <c r="A12" s="23" t="inlineStr">
+        <is>
+          <t>▼ 工艺制作</t>
         </is>
       </c>
     </row>
     <row r="13" ht="16.5" customHeight="1">
-      <c r="A13" t="inlineStr">
+      <c r="A13" s="24" t="inlineStr">
         <is>
           <t>序号</t>
         </is>
       </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>工艺制作</t>
-        </is>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>车缝工艺</t>
-        </is>
-      </c>
-      <c r="D13" t="inlineStr">
-        <is>
-          <t>成衣工艺</t>
-        </is>
-      </c>
-      <c r="E13" s="13" t="n"/>
-      <c r="F13" s="13" t="n"/>
-      <c r="G13" s="13" t="n"/>
-      <c r="H13" s="14" t="n"/>
+      <c r="B13" s="24" t="inlineStr">
+        <is>
+          <t>工艺名称</t>
+        </is>
+      </c>
+      <c r="C13" s="24" t="inlineStr">
+        <is>
+          <t>制衣厂</t>
+        </is>
+      </c>
+      <c r="D13" s="24" t="inlineStr">
+        <is>
+          <t>单价</t>
+        </is>
+      </c>
     </row>
     <row r="14" ht="22" customHeight="1">
       <c r="A14" t="n">
         <v>1</v>
       </c>
-      <c r="E14" s="6" t="n"/>
-      <c r="F14" s="6" t="n"/>
-      <c r="G14" s="6" t="n"/>
-      <c r="H14" s="7" t="n"/>
     </row>
     <row r="15" ht="22" customHeight="1">
       <c r="A15" t="n">
         <v>2</v>
       </c>
-      <c r="E15" s="6" t="n"/>
-      <c r="F15" s="6" t="n"/>
-      <c r="G15" s="6" t="n"/>
-      <c r="H15" s="7" t="n"/>
     </row>
     <row r="16" ht="22" customHeight="1">
       <c r="A16" t="n">
         <v>3</v>
       </c>
-      <c r="E16" s="6" t="n"/>
-      <c r="F16" s="6" t="n"/>
-      <c r="G16" s="6" t="n"/>
-      <c r="H16" s="7" t="n"/>
     </row>
     <row r="17" ht="22" customHeight="1">
       <c r="A17" t="n">
         <v>4</v>
       </c>
-      <c r="E17" s="6" t="n"/>
-      <c r="F17" s="6" t="n"/>
-      <c r="G17" s="6" t="n"/>
-      <c r="H17" s="7" t="n"/>
-    </row>
-    <row r="18">
-      <c r="A18" t="n">
-        <v>5</v>
-      </c>
     </row>
     <row r="19" ht="24" customHeight="1">
-      <c r="A19" t="n">
-        <v>6</v>
-      </c>
-      <c r="S19" s="16" t="n"/>
+      <c r="A19" s="23" t="inlineStr">
+        <is>
+          <t>▼ 车缝工艺</t>
+        </is>
+      </c>
     </row>
     <row r="20" ht="20" customHeight="1">
-      <c r="A20" t="n">
-        <v>7</v>
-      </c>
-      <c r="E20" s="17" t="inlineStr">
-        <is>
-          <t>布类</t>
-        </is>
-      </c>
-      <c r="F20" s="4" t="inlineStr">
-        <is>
-          <t>面料编号</t>
-        </is>
-      </c>
-      <c r="G20" s="4" t="inlineStr">
-        <is>
-          <t>色号</t>
-        </is>
-      </c>
-      <c r="H20" s="4" t="inlineStr">
-        <is>
-          <t>颜色名</t>
-        </is>
-      </c>
-      <c r="I20" s="17" t="inlineStr">
-        <is>
-          <t>是否罗纹</t>
-        </is>
-      </c>
-      <c r="J20" s="17" t="inlineStr">
-        <is>
-          <t>幅宽/CM</t>
-        </is>
-      </c>
-      <c r="K20" s="17" t="inlineStr">
-        <is>
-          <t>克重</t>
-        </is>
-      </c>
-      <c r="L20" s="17" t="inlineStr">
-        <is>
-          <t>供应商</t>
-        </is>
-      </c>
-      <c r="M20" s="17" t="inlineStr">
-        <is>
-          <t>成分</t>
-        </is>
-      </c>
-      <c r="N20" s="17" t="inlineStr">
-        <is>
-          <t>品名</t>
-        </is>
-      </c>
-      <c r="O20" s="17" t="inlineStr">
-        <is>
-          <t>采购米长</t>
-        </is>
-      </c>
-      <c r="P20" s="17" t="inlineStr">
-        <is>
-          <t>采购金额</t>
-        </is>
-      </c>
-      <c r="Q20" s="17" t="inlineStr">
-        <is>
-          <t>采购人</t>
-        </is>
-      </c>
-      <c r="R20" s="17" t="inlineStr">
-        <is>
-          <t>要求到货时间</t>
+      <c r="A20" s="24" t="inlineStr">
+        <is>
+          <t>序号</t>
+        </is>
+      </c>
+      <c r="B20" s="24" t="inlineStr">
+        <is>
+          <t>工艺名称</t>
+        </is>
+      </c>
+      <c r="C20" s="24" t="inlineStr">
+        <is>
+          <t>制衣厂</t>
+        </is>
+      </c>
+      <c r="D20" s="24" t="inlineStr">
+        <is>
+          <t>单价</t>
         </is>
       </c>
     </row>
     <row r="21" ht="22" customHeight="1">
       <c r="A21" t="n">
-        <v>8</v>
-      </c>
-      <c r="E21" s="15" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="F21" s="18" t="inlineStr"/>
-      <c r="G21" s="18" t="inlineStr"/>
-      <c r="H21" s="18" t="inlineStr"/>
-      <c r="I21" s="19" t="n"/>
-      <c r="J21" s="19" t="n"/>
-      <c r="K21" s="19" t="n"/>
-      <c r="L21" s="19" t="n"/>
-      <c r="M21" s="19" t="n"/>
-      <c r="N21" s="19" t="n"/>
-      <c r="O21" s="19" t="n"/>
-      <c r="P21" s="19" t="n"/>
-      <c r="Q21" s="19" t="n"/>
-      <c r="R21" s="19" t="n"/>
+        <v>1</v>
+      </c>
     </row>
     <row r="22" ht="22" customHeight="1">
       <c r="A22" t="n">
-        <v>9</v>
-      </c>
-      <c r="E22" s="15" t="inlineStr">
-        <is>
-          <t>B</t>
-        </is>
-      </c>
-      <c r="F22" s="18" t="inlineStr"/>
-      <c r="G22" s="18" t="inlineStr"/>
-      <c r="H22" s="18" t="inlineStr"/>
-      <c r="I22" s="19" t="n"/>
-      <c r="J22" s="19" t="n"/>
-      <c r="K22" s="19" t="n"/>
-      <c r="L22" s="19" t="n"/>
-      <c r="M22" s="19" t="n"/>
-      <c r="N22" s="19" t="n"/>
-      <c r="O22" s="19" t="n"/>
-      <c r="P22" s="19" t="n"/>
-      <c r="Q22" s="19" t="n"/>
-      <c r="R22" s="19" t="n"/>
+        <v>2</v>
+      </c>
     </row>
     <row r="23" ht="22" customHeight="1">
       <c r="A23" t="n">
-        <v>10</v>
-      </c>
-      <c r="E23" s="15" t="inlineStr"/>
-      <c r="F23" s="18" t="inlineStr"/>
-      <c r="G23" s="18" t="inlineStr"/>
-      <c r="H23" s="18" t="inlineStr"/>
-      <c r="I23" s="19" t="n"/>
-      <c r="J23" s="19" t="n"/>
-      <c r="K23" s="19" t="n"/>
-      <c r="L23" s="19" t="n"/>
-      <c r="M23" s="19" t="n"/>
-      <c r="N23" s="19" t="n"/>
-      <c r="O23" s="19" t="n"/>
-      <c r="P23" s="19" t="n"/>
-      <c r="Q23" s="19" t="n"/>
-      <c r="R23" s="19" t="n"/>
+        <v>3</v>
+      </c>
     </row>
     <row r="24" ht="22" customHeight="1">
       <c r="A24" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="25" ht="22" customHeight="1"/>
+    <row r="26" ht="22" customHeight="1">
+      <c r="A26" s="23" t="inlineStr">
+        <is>
+          <t>▼ 成衣工艺</t>
+        </is>
+      </c>
+    </row>
+    <row r="27" ht="22" customHeight="1">
+      <c r="A27" s="24" t="inlineStr">
+        <is>
+          <t>序号</t>
+        </is>
+      </c>
+      <c r="B27" s="24" t="inlineStr">
+        <is>
+          <t>工艺名称</t>
+        </is>
+      </c>
+      <c r="C27" s="24" t="inlineStr">
+        <is>
+          <t>制衣厂</t>
+        </is>
+      </c>
+      <c r="D27" s="24" t="inlineStr">
+        <is>
+          <t>单价</t>
+        </is>
+      </c>
+    </row>
+    <row r="28" ht="22" customHeight="1">
+      <c r="A28" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="30" ht="24" customHeight="1">
+      <c r="A30" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="31" ht="14.25" customHeight="1">
+      <c r="A31" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="32" ht="22" customHeight="1"/>
+    <row r="33" ht="22" customHeight="1"/>
+    <row r="34" ht="22" customHeight="1"/>
+    <row r="35" ht="22" customHeight="1">
+      <c r="A35" s="3" t="inlineStr">
+        <is>
+          <t>▼ SKU 与面料</t>
+        </is>
+      </c>
+      <c r="S35" s="16" t="n"/>
+    </row>
+    <row r="36" ht="22" customHeight="1">
+      <c r="A36" s="9" t="inlineStr">
+        <is>
+          <t>SKU编号</t>
+        </is>
+      </c>
+      <c r="B36" s="4" t="inlineStr">
+        <is>
+          <t>颜色</t>
+        </is>
+      </c>
+      <c r="C36" s="4" t="inlineStr">
+        <is>
+          <t>尺码</t>
+        </is>
+      </c>
+      <c r="D36" s="4" t="inlineStr">
+        <is>
+          <t>件数</t>
+        </is>
+      </c>
+      <c r="E36" s="17" t="inlineStr">
+        <is>
+          <t>布类</t>
+        </is>
+      </c>
+      <c r="F36" s="4" t="inlineStr">
+        <is>
+          <t>面料编号</t>
+        </is>
+      </c>
+      <c r="G36" s="4" t="inlineStr">
+        <is>
+          <t>色号</t>
+        </is>
+      </c>
+      <c r="H36" s="4" t="inlineStr">
+        <is>
+          <t>颜色名</t>
+        </is>
+      </c>
+      <c r="I36" s="17" t="inlineStr">
+        <is>
+          <t>是否罗纹</t>
+        </is>
+      </c>
+      <c r="J36" s="17" t="inlineStr">
+        <is>
+          <t>幅宽/CM</t>
+        </is>
+      </c>
+      <c r="K36" s="17" t="inlineStr">
+        <is>
+          <t>克重</t>
+        </is>
+      </c>
+      <c r="L36" s="17" t="inlineStr">
+        <is>
+          <t>供应商</t>
+        </is>
+      </c>
+      <c r="M36" s="17" t="inlineStr">
+        <is>
+          <t>成分</t>
+        </is>
+      </c>
+      <c r="N36" s="17" t="inlineStr">
+        <is>
+          <t>品名</t>
+        </is>
+      </c>
+      <c r="O36" s="17" t="inlineStr">
+        <is>
+          <t>采购米长</t>
+        </is>
+      </c>
+      <c r="P36" s="17" t="inlineStr">
+        <is>
+          <t>采购金额</t>
+        </is>
+      </c>
+      <c r="Q36" s="17" t="inlineStr">
+        <is>
+          <t>采购人</t>
+        </is>
+      </c>
+      <c r="R36" s="17" t="inlineStr">
+        <is>
+          <t>要求到货时间</t>
+        </is>
+      </c>
+    </row>
+    <row r="37" ht="22" customHeight="1">
+      <c r="A37" s="15" t="n">
+        <v>1</v>
+      </c>
+      <c r="B37" s="5" t="inlineStr"/>
+      <c r="C37" s="5" t="inlineStr"/>
+      <c r="D37" s="5" t="inlineStr"/>
+      <c r="E37" s="15" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="F37" s="18" t="inlineStr"/>
+      <c r="G37" s="18" t="inlineStr"/>
+      <c r="H37" s="18" t="inlineStr"/>
+      <c r="I37" s="19" t="n"/>
+      <c r="J37" s="19" t="n"/>
+      <c r="K37" s="19" t="n"/>
+      <c r="L37" s="19" t="n"/>
+      <c r="M37" s="19" t="n"/>
+      <c r="N37" s="19" t="n"/>
+      <c r="O37" s="19" t="n"/>
+      <c r="P37" s="19" t="n"/>
+      <c r="Q37" s="19" t="n"/>
+      <c r="R37" s="19" t="n"/>
+    </row>
+    <row r="38" ht="22" customHeight="1">
+      <c r="A38" s="15" t="inlineStr"/>
+      <c r="B38" s="5" t="inlineStr"/>
+      <c r="C38" s="5" t="inlineStr"/>
+      <c r="D38" s="5" t="inlineStr"/>
+      <c r="E38" s="15" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="F38" s="18" t="inlineStr"/>
+      <c r="G38" s="18" t="inlineStr"/>
+      <c r="H38" s="18" t="inlineStr"/>
+      <c r="I38" s="19" t="n"/>
+      <c r="J38" s="19" t="n"/>
+      <c r="K38" s="19" t="n"/>
+      <c r="L38" s="19" t="n"/>
+      <c r="M38" s="19" t="n"/>
+      <c r="N38" s="19" t="n"/>
+      <c r="O38" s="19" t="n"/>
+      <c r="P38" s="19" t="n"/>
+      <c r="Q38" s="19" t="n"/>
+      <c r="R38" s="19" t="n"/>
+    </row>
+    <row r="39" ht="22" customHeight="1">
+      <c r="A39" s="15" t="inlineStr"/>
+      <c r="B39" s="5" t="inlineStr"/>
+      <c r="C39" s="5" t="inlineStr"/>
+      <c r="D39" s="5" t="inlineStr"/>
+      <c r="E39" s="15" t="inlineStr"/>
+      <c r="F39" s="18" t="inlineStr"/>
+      <c r="G39" s="18" t="inlineStr"/>
+      <c r="H39" s="18" t="inlineStr"/>
+      <c r="I39" s="19" t="n"/>
+      <c r="J39" s="19" t="n"/>
+      <c r="K39" s="19" t="n"/>
+      <c r="L39" s="19" t="n"/>
+      <c r="M39" s="19" t="n"/>
+      <c r="N39" s="19" t="n"/>
+      <c r="O39" s="19" t="n"/>
+      <c r="P39" s="19" t="n"/>
+      <c r="Q39" s="19" t="n"/>
+      <c r="R39" s="19" t="n"/>
+    </row>
+    <row r="40" ht="22" customHeight="1">
+      <c r="A40" s="15" t="inlineStr"/>
+      <c r="B40" s="5" t="inlineStr"/>
+      <c r="C40" s="5" t="inlineStr"/>
+      <c r="D40" s="5" t="inlineStr"/>
+      <c r="E40" s="15" t="inlineStr"/>
+      <c r="F40" s="18" t="inlineStr"/>
+      <c r="G40" s="18" t="inlineStr"/>
+      <c r="H40" s="18" t="inlineStr"/>
+      <c r="I40" s="19" t="n"/>
+      <c r="J40" s="19" t="n"/>
+      <c r="K40" s="19" t="n"/>
+      <c r="L40" s="19" t="n"/>
+      <c r="M40" s="19" t="n"/>
+      <c r="N40" s="19" t="n"/>
+      <c r="O40" s="19" t="n"/>
+      <c r="P40" s="19" t="n"/>
+      <c r="Q40" s="19" t="n"/>
+      <c r="R40" s="19" t="n"/>
+    </row>
+    <row r="41" ht="22" customHeight="1">
+      <c r="A41" s="15" t="inlineStr"/>
+      <c r="B41" s="5" t="inlineStr"/>
+      <c r="C41" s="5" t="inlineStr"/>
+      <c r="D41" s="5" t="inlineStr"/>
+      <c r="E41" s="15" t="inlineStr"/>
+      <c r="F41" s="18" t="inlineStr"/>
+      <c r="G41" s="18" t="inlineStr"/>
+      <c r="H41" s="18" t="inlineStr"/>
+      <c r="I41" s="19" t="n"/>
+      <c r="J41" s="19" t="n"/>
+      <c r="K41" s="19" t="n"/>
+      <c r="L41" s="19" t="n"/>
+      <c r="M41" s="19" t="n"/>
+      <c r="N41" s="19" t="n"/>
+      <c r="O41" s="19" t="n"/>
+      <c r="P41" s="19" t="n"/>
+      <c r="Q41" s="19" t="n"/>
+      <c r="R41" s="19" t="n"/>
+    </row>
+    <row r="42" ht="22" customHeight="1">
+      <c r="A42" s="15" t="inlineStr"/>
+      <c r="B42" s="5" t="inlineStr"/>
+      <c r="C42" s="5" t="inlineStr"/>
+      <c r="D42" s="5" t="inlineStr"/>
+      <c r="E42" s="15" t="inlineStr"/>
+      <c r="F42" s="18" t="inlineStr"/>
+      <c r="G42" s="18" t="inlineStr"/>
+      <c r="H42" s="18" t="inlineStr"/>
+      <c r="I42" s="19" t="n"/>
+      <c r="J42" s="19" t="n"/>
+      <c r="K42" s="19" t="n"/>
+      <c r="L42" s="19" t="n"/>
+      <c r="M42" s="19" t="n"/>
+      <c r="N42" s="19" t="n"/>
+      <c r="O42" s="19" t="n"/>
+      <c r="P42" s="19" t="n"/>
+      <c r="Q42" s="19" t="n"/>
+      <c r="R42" s="19" t="n"/>
+    </row>
+    <row r="43" ht="22" customHeight="1">
+      <c r="A43" s="15" t="inlineStr"/>
+      <c r="B43" s="5" t="inlineStr"/>
+      <c r="C43" s="5" t="n"/>
+      <c r="D43" s="5" t="inlineStr"/>
+      <c r="E43" s="15" t="inlineStr"/>
+      <c r="F43" s="18" t="inlineStr"/>
+      <c r="G43" s="18" t="inlineStr"/>
+      <c r="H43" s="18" t="inlineStr"/>
+      <c r="I43" s="19" t="n"/>
+      <c r="J43" s="19" t="n"/>
+      <c r="K43" s="19" t="n"/>
+      <c r="L43" s="19" t="n"/>
+      <c r="M43" s="19" t="n"/>
+      <c r="N43" s="19" t="n"/>
+      <c r="O43" s="19" t="n"/>
+      <c r="P43" s="19" t="n"/>
+      <c r="Q43" s="19" t="n"/>
+      <c r="R43" s="19" t="n"/>
+    </row>
+    <row r="44">
+      <c r="A44" s="15" t="inlineStr"/>
+      <c r="B44" s="5" t="inlineStr"/>
+      <c r="C44" s="5" t="inlineStr"/>
+      <c r="D44" s="5" t="inlineStr"/>
+      <c r="E44" s="15" t="inlineStr"/>
+      <c r="F44" s="18" t="inlineStr"/>
+      <c r="G44" s="18" t="inlineStr"/>
+      <c r="H44" s="18" t="inlineStr"/>
+      <c r="I44" s="19" t="n"/>
+      <c r="J44" s="19" t="n"/>
+      <c r="K44" s="19" t="n"/>
+      <c r="L44" s="19" t="n"/>
+      <c r="M44" s="19" t="n"/>
+      <c r="N44" s="19" t="n"/>
+      <c r="O44" s="19" t="n"/>
+      <c r="P44" s="19" t="n"/>
+      <c r="Q44" s="19" t="n"/>
+      <c r="R44" s="19" t="n"/>
+    </row>
+    <row r="45"/>
+    <row r="46">
+      <c r="A46" s="3" t="inlineStr">
+        <is>
+          <t>▼ 辅料信息</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="20" t="inlineStr">
+        <is>
+          <t>序号</t>
+        </is>
+      </c>
+      <c r="B47" s="20" t="inlineStr">
+        <is>
+          <t>辅料名称</t>
+        </is>
+      </c>
+      <c r="C47" s="20" t="inlineStr">
+        <is>
+          <t>规格型号</t>
+        </is>
+      </c>
+      <c r="D47" s="20" t="inlineStr">
+        <is>
+          <t>颜色</t>
+        </is>
+      </c>
+      <c r="E47" s="20" t="inlineStr">
+        <is>
+          <t>用量</t>
+        </is>
+      </c>
+      <c r="F47" s="20" t="inlineStr">
+        <is>
+          <t>单位</t>
+        </is>
+      </c>
+      <c r="G47" s="20" t="inlineStr">
+        <is>
+          <t>采购单价</t>
+        </is>
+      </c>
+      <c r="H47" s="20" t="inlineStr">
+        <is>
+          <t>供应商</t>
+        </is>
+      </c>
+      <c r="I47" s="20" t="inlineStr">
+        <is>
+          <t>联系方式</t>
+        </is>
+      </c>
+      <c r="J47" s="20" t="inlineStr">
+        <is>
+          <t>采购数量</t>
+        </is>
+      </c>
+      <c r="K47" s="20" t="inlineStr">
+        <is>
+          <t>采购人</t>
+        </is>
+      </c>
+      <c r="L47" s="20" t="inlineStr">
+        <is>
+          <t>要求到货时间</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="21" t="n">
+        <v>1</v>
+      </c>
+      <c r="B48" s="22" t="inlineStr"/>
+      <c r="C48" s="22" t="inlineStr"/>
+      <c r="D48" s="22" t="inlineStr"/>
+      <c r="E48" s="22" t="inlineStr"/>
+      <c r="F48" s="22" t="inlineStr"/>
+      <c r="G48" s="22" t="inlineStr"/>
+      <c r="H48" s="22" t="inlineStr"/>
+      <c r="I48" s="22" t="inlineStr"/>
+      <c r="J48" s="19" t="n"/>
+      <c r="K48" s="22" t="inlineStr"/>
+      <c r="L48" s="22" t="n"/>
+    </row>
+    <row r="49">
+      <c r="A49" s="21" t="n">
+        <v>2</v>
+      </c>
+      <c r="B49" s="22" t="inlineStr"/>
+      <c r="C49" s="22" t="inlineStr"/>
+      <c r="D49" s="22" t="inlineStr"/>
+      <c r="E49" s="22" t="inlineStr"/>
+      <c r="F49" s="22" t="inlineStr"/>
+      <c r="G49" s="22" t="inlineStr"/>
+      <c r="H49" s="22" t="inlineStr"/>
+      <c r="I49" s="22" t="inlineStr"/>
+      <c r="J49" s="19" t="n"/>
+      <c r="K49" s="22" t="inlineStr"/>
+      <c r="L49" s="22" t="inlineStr"/>
+    </row>
+    <row r="50">
+      <c r="A50" s="21" t="n">
+        <v>3</v>
+      </c>
+      <c r="B50" s="22" t="inlineStr"/>
+      <c r="C50" s="22" t="inlineStr"/>
+      <c r="D50" s="22" t="inlineStr"/>
+      <c r="E50" s="22" t="inlineStr"/>
+      <c r="F50" s="22" t="inlineStr"/>
+      <c r="G50" s="22" t="inlineStr"/>
+      <c r="H50" s="22" t="inlineStr"/>
+      <c r="I50" s="22" t="inlineStr"/>
+      <c r="J50" s="19" t="n"/>
+      <c r="K50" s="22" t="inlineStr"/>
+      <c r="L50" s="22" t="inlineStr"/>
+    </row>
+    <row r="51">
+      <c r="A51" s="21" t="n">
+        <v>4</v>
+      </c>
+      <c r="B51" s="22" t="inlineStr"/>
+      <c r="C51" s="22" t="inlineStr"/>
+      <c r="D51" s="22" t="inlineStr"/>
+      <c r="E51" s="22" t="inlineStr"/>
+      <c r="F51" s="22" t="inlineStr"/>
+      <c r="G51" s="22" t="inlineStr"/>
+      <c r="H51" s="22" t="inlineStr"/>
+      <c r="I51" s="22" t="inlineStr"/>
+      <c r="J51" s="19" t="n"/>
+      <c r="K51" s="22" t="inlineStr"/>
+      <c r="L51" s="22" t="n"/>
+    </row>
+    <row r="52">
+      <c r="A52" s="21" t="n">
+        <v>5</v>
+      </c>
+      <c r="B52" s="22" t="inlineStr"/>
+      <c r="C52" s="22" t="inlineStr"/>
+      <c r="D52" s="22" t="inlineStr"/>
+      <c r="E52" s="22" t="inlineStr"/>
+      <c r="F52" s="22" t="inlineStr"/>
+      <c r="G52" s="22" t="inlineStr"/>
+      <c r="H52" s="22" t="inlineStr"/>
+      <c r="I52" s="22" t="inlineStr"/>
+      <c r="J52" s="19" t="n"/>
+      <c r="K52" s="22" t="inlineStr"/>
+      <c r="L52" s="22" t="inlineStr"/>
+    </row>
+    <row r="53">
+      <c r="A53" s="21" t="n">
+        <v>6</v>
+      </c>
+      <c r="B53" s="22" t="inlineStr"/>
+      <c r="C53" s="22" t="inlineStr"/>
+      <c r="D53" s="22" t="inlineStr"/>
+      <c r="E53" s="22" t="inlineStr"/>
+      <c r="F53" s="22" t="inlineStr"/>
+      <c r="G53" s="22" t="inlineStr"/>
+      <c r="H53" s="22" t="inlineStr"/>
+      <c r="I53" s="22" t="inlineStr"/>
+      <c r="J53" s="19" t="n"/>
+      <c r="K53" s="22" t="inlineStr"/>
+      <c r="L53" s="22" t="inlineStr"/>
+    </row>
+    <row r="54">
+      <c r="A54" s="21" t="n">
+        <v>7</v>
+      </c>
+      <c r="B54" s="22" t="inlineStr"/>
+      <c r="C54" s="22" t="inlineStr"/>
+      <c r="D54" s="22" t="inlineStr"/>
+      <c r="E54" s="22" t="inlineStr"/>
+      <c r="F54" s="22" t="inlineStr"/>
+      <c r="G54" s="22" t="inlineStr"/>
+      <c r="H54" s="22" t="inlineStr"/>
+      <c r="I54" s="22" t="inlineStr"/>
+      <c r="J54" s="19" t="n"/>
+      <c r="K54" s="22" t="inlineStr"/>
+      <c r="L54" s="22" t="n"/>
+    </row>
+    <row r="55">
+      <c r="A55" s="21" t="n">
+        <v>8</v>
+      </c>
+      <c r="B55" s="22" t="inlineStr"/>
+      <c r="C55" s="22" t="inlineStr"/>
+      <c r="D55" s="22" t="inlineStr"/>
+      <c r="E55" s="22" t="inlineStr"/>
+      <c r="F55" s="22" t="inlineStr"/>
+      <c r="G55" s="22" t="inlineStr"/>
+      <c r="H55" s="22" t="inlineStr"/>
+      <c r="I55" s="22" t="inlineStr"/>
+      <c r="J55" s="19" t="n"/>
+      <c r="K55" s="22" t="inlineStr"/>
+      <c r="L55" s="22" t="inlineStr"/>
+    </row>
+    <row r="56">
+      <c r="A56" s="21" t="n">
+        <v>9</v>
+      </c>
+      <c r="B56" s="22" t="inlineStr"/>
+      <c r="C56" s="22" t="inlineStr"/>
+      <c r="D56" s="22" t="inlineStr"/>
+      <c r="E56" s="22" t="inlineStr"/>
+      <c r="F56" s="22" t="inlineStr"/>
+      <c r="G56" s="22" t="inlineStr"/>
+      <c r="H56" s="22" t="inlineStr"/>
+      <c r="I56" s="22" t="inlineStr"/>
+      <c r="J56" s="19" t="n"/>
+      <c r="K56" s="22" t="inlineStr"/>
+      <c r="L56" s="22" t="inlineStr"/>
+    </row>
+    <row r="57">
+      <c r="A57" s="21" t="n">
+        <v>10</v>
+      </c>
+      <c r="B57" s="22" t="inlineStr"/>
+      <c r="C57" s="22" t="inlineStr"/>
+      <c r="D57" s="22" t="inlineStr"/>
+      <c r="E57" s="22" t="inlineStr"/>
+      <c r="F57" s="22" t="inlineStr"/>
+      <c r="G57" s="22" t="inlineStr"/>
+      <c r="H57" s="22" t="inlineStr"/>
+      <c r="I57" s="22" t="inlineStr"/>
+      <c r="J57" s="19" t="n"/>
+      <c r="K57" s="22" t="inlineStr"/>
+      <c r="L57" s="22" t="n"/>
+    </row>
+    <row r="58">
+      <c r="A58" s="21" t="n">
         <v>11</v>
       </c>
-      <c r="E24" s="15" t="inlineStr"/>
-      <c r="F24" s="18" t="inlineStr"/>
-      <c r="G24" s="18" t="inlineStr"/>
-      <c r="H24" s="18" t="inlineStr"/>
-      <c r="I24" s="19" t="n"/>
-      <c r="J24" s="19" t="n"/>
-      <c r="K24" s="19" t="n"/>
-      <c r="L24" s="19" t="n"/>
-      <c r="M24" s="19" t="n"/>
-      <c r="N24" s="19" t="n"/>
-      <c r="O24" s="19" t="n"/>
-      <c r="P24" s="19" t="n"/>
-      <c r="Q24" s="19" t="n"/>
-      <c r="R24" s="19" t="n"/>
-    </row>
-    <row r="25" ht="22" customHeight="1">
-      <c r="A25" t="n">
+      <c r="B58" s="22" t="inlineStr"/>
+      <c r="C58" s="22" t="inlineStr"/>
+      <c r="D58" s="22" t="inlineStr"/>
+      <c r="E58" s="22" t="inlineStr"/>
+      <c r="F58" s="22" t="inlineStr"/>
+      <c r="G58" s="22" t="inlineStr"/>
+      <c r="H58" s="22" t="inlineStr"/>
+      <c r="I58" s="22" t="inlineStr"/>
+      <c r="J58" s="19" t="n"/>
+      <c r="K58" s="22" t="inlineStr"/>
+      <c r="L58" s="22" t="inlineStr"/>
+    </row>
+    <row r="59">
+      <c r="A59" s="21" t="n">
         <v>12</v>
       </c>
-      <c r="E25" s="15" t="inlineStr"/>
-      <c r="F25" s="18" t="inlineStr"/>
-      <c r="G25" s="18" t="inlineStr"/>
-      <c r="H25" s="18" t="inlineStr"/>
-      <c r="I25" s="19" t="n"/>
-      <c r="J25" s="19" t="n"/>
-      <c r="K25" s="19" t="n"/>
-      <c r="L25" s="19" t="n"/>
-      <c r="M25" s="19" t="n"/>
-      <c r="N25" s="19" t="n"/>
-      <c r="O25" s="19" t="n"/>
-      <c r="P25" s="19" t="n"/>
-      <c r="Q25" s="19" t="n"/>
-      <c r="R25" s="19" t="n"/>
-    </row>
-    <row r="26" ht="22" customHeight="1">
-      <c r="E26" s="15" t="inlineStr"/>
-      <c r="F26" s="18" t="inlineStr"/>
-      <c r="G26" s="18" t="inlineStr"/>
-      <c r="H26" s="18" t="inlineStr"/>
-      <c r="I26" s="19" t="n"/>
-      <c r="J26" s="19" t="n"/>
-      <c r="K26" s="19" t="n"/>
-      <c r="L26" s="19" t="n"/>
-      <c r="M26" s="19" t="n"/>
-      <c r="N26" s="19" t="n"/>
-      <c r="O26" s="19" t="n"/>
-      <c r="P26" s="19" t="n"/>
-      <c r="Q26" s="19" t="n"/>
-      <c r="R26" s="19" t="n"/>
-    </row>
-    <row r="27" ht="22" customHeight="1">
-      <c r="E27" s="15" t="inlineStr"/>
-      <c r="F27" s="18" t="inlineStr"/>
-      <c r="G27" s="18" t="inlineStr"/>
-      <c r="H27" s="18" t="inlineStr"/>
-      <c r="I27" s="19" t="n"/>
-      <c r="J27" s="19" t="n"/>
-      <c r="K27" s="19" t="n"/>
-      <c r="L27" s="19" t="n"/>
-      <c r="M27" s="19" t="n"/>
-      <c r="N27" s="19" t="n"/>
-      <c r="O27" s="19" t="n"/>
-      <c r="P27" s="19" t="n"/>
-      <c r="Q27" s="19" t="n"/>
-      <c r="R27" s="19" t="n"/>
-    </row>
-    <row r="28" ht="22" customHeight="1">
-      <c r="E28" s="15" t="inlineStr"/>
-      <c r="F28" s="18" t="inlineStr"/>
-      <c r="G28" s="18" t="inlineStr"/>
-      <c r="H28" s="18" t="inlineStr"/>
-      <c r="I28" s="19" t="n"/>
-      <c r="J28" s="19" t="n"/>
-      <c r="K28" s="19" t="n"/>
-      <c r="L28" s="19" t="n"/>
-      <c r="M28" s="19" t="n"/>
-      <c r="N28" s="19" t="n"/>
-      <c r="O28" s="19" t="n"/>
-      <c r="P28" s="19" t="n"/>
-      <c r="Q28" s="19" t="n"/>
-      <c r="R28" s="19" t="n"/>
-    </row>
-    <row r="30" ht="24" customHeight="1">
-      <c r="A30" s="3" t="inlineStr">
-        <is>
-          <t>▼ 辅料信息</t>
-        </is>
-      </c>
-    </row>
-    <row r="31" ht="14.25" customHeight="1">
-      <c r="A31" s="20" t="inlineStr">
-        <is>
-          <t>序号</t>
-        </is>
-      </c>
-      <c r="B31" s="20" t="inlineStr">
-        <is>
-          <t>辅料名称</t>
-        </is>
-      </c>
-      <c r="C31" s="20" t="inlineStr">
-        <is>
-          <t>规格型号</t>
-        </is>
-      </c>
-      <c r="D31" s="20" t="inlineStr">
-        <is>
-          <t>颜色</t>
-        </is>
-      </c>
-      <c r="E31" s="20" t="inlineStr">
-        <is>
-          <t>用量</t>
-        </is>
-      </c>
-      <c r="F31" s="20" t="inlineStr">
-        <is>
-          <t>单位</t>
-        </is>
-      </c>
-      <c r="G31" s="20" t="inlineStr">
-        <is>
-          <t>采购单价</t>
-        </is>
-      </c>
-      <c r="H31" s="20" t="inlineStr">
-        <is>
-          <t>供应商</t>
-        </is>
-      </c>
-      <c r="I31" s="20" t="inlineStr">
-        <is>
-          <t>联系方式</t>
-        </is>
-      </c>
-      <c r="J31" s="20" t="inlineStr">
-        <is>
-          <t>采购数量</t>
-        </is>
-      </c>
-      <c r="K31" s="20" t="inlineStr">
-        <is>
-          <t>采购人</t>
-        </is>
-      </c>
-      <c r="L31" s="20" t="inlineStr">
-        <is>
-          <t>要求到货时间</t>
-        </is>
-      </c>
-    </row>
-    <row r="32" ht="22" customHeight="1">
-      <c r="A32" s="21" t="n">
-        <v>1</v>
-      </c>
-      <c r="B32" s="22" t="inlineStr"/>
-      <c r="C32" s="22" t="inlineStr"/>
-      <c r="D32" s="22" t="inlineStr"/>
-      <c r="E32" s="22" t="inlineStr"/>
-      <c r="F32" s="22" t="inlineStr"/>
-      <c r="G32" s="22" t="inlineStr"/>
-      <c r="H32" s="22" t="inlineStr"/>
-      <c r="I32" s="22" t="inlineStr"/>
-      <c r="J32" s="19" t="n"/>
-      <c r="K32" s="22" t="inlineStr"/>
-      <c r="L32" s="22" t="n"/>
-    </row>
-    <row r="33" ht="22" customHeight="1">
-      <c r="A33" s="21" t="n">
-        <v>2</v>
-      </c>
-      <c r="B33" s="22" t="inlineStr"/>
-      <c r="C33" s="22" t="inlineStr"/>
-      <c r="D33" s="22" t="inlineStr"/>
-      <c r="E33" s="22" t="inlineStr"/>
-      <c r="F33" s="22" t="inlineStr"/>
-      <c r="G33" s="22" t="inlineStr"/>
-      <c r="H33" s="22" t="inlineStr"/>
-      <c r="I33" s="22" t="inlineStr"/>
-      <c r="J33" s="19" t="n"/>
-      <c r="K33" s="22" t="inlineStr"/>
-      <c r="L33" s="22" t="inlineStr"/>
-    </row>
-    <row r="34" ht="22" customHeight="1">
-      <c r="A34" s="21" t="n">
-        <v>3</v>
-      </c>
-      <c r="B34" s="22" t="inlineStr"/>
-      <c r="C34" s="22" t="inlineStr"/>
-      <c r="D34" s="22" t="inlineStr"/>
-      <c r="E34" s="22" t="inlineStr"/>
-      <c r="F34" s="22" t="inlineStr"/>
-      <c r="G34" s="22" t="inlineStr"/>
-      <c r="H34" s="22" t="inlineStr"/>
-      <c r="I34" s="22" t="inlineStr"/>
-      <c r="J34" s="19" t="n"/>
-      <c r="K34" s="22" t="inlineStr"/>
-      <c r="L34" s="22" t="inlineStr"/>
-    </row>
-    <row r="35" ht="22" customHeight="1">
-      <c r="A35" s="21" t="n">
-        <v>4</v>
-      </c>
-      <c r="B35" s="22" t="inlineStr"/>
-      <c r="C35" s="22" t="inlineStr"/>
-      <c r="D35" s="22" t="inlineStr"/>
-      <c r="E35" s="22" t="inlineStr"/>
-      <c r="F35" s="22" t="inlineStr"/>
-      <c r="G35" s="22" t="inlineStr"/>
-      <c r="H35" s="22" t="inlineStr"/>
-      <c r="I35" s="22" t="inlineStr"/>
-      <c r="J35" s="19" t="n"/>
-      <c r="K35" s="22" t="inlineStr"/>
-      <c r="L35" s="22" t="n"/>
-    </row>
-    <row r="36" ht="22" customHeight="1">
-      <c r="A36" s="21" t="n">
-        <v>5</v>
-      </c>
-      <c r="B36" s="22" t="inlineStr"/>
-      <c r="C36" s="22" t="inlineStr"/>
-      <c r="D36" s="22" t="inlineStr"/>
-      <c r="E36" s="22" t="inlineStr"/>
-      <c r="F36" s="22" t="inlineStr"/>
-      <c r="G36" s="22" t="inlineStr"/>
-      <c r="H36" s="22" t="inlineStr"/>
-      <c r="I36" s="22" t="inlineStr"/>
-      <c r="J36" s="19" t="n"/>
-      <c r="K36" s="22" t="inlineStr"/>
-      <c r="L36" s="22" t="inlineStr"/>
-    </row>
-    <row r="37" ht="22" customHeight="1">
-      <c r="A37" s="21" t="n">
-        <v>6</v>
-      </c>
-      <c r="B37" s="22" t="inlineStr"/>
-      <c r="C37" s="22" t="inlineStr"/>
-      <c r="D37" s="22" t="inlineStr"/>
-      <c r="E37" s="22" t="inlineStr"/>
-      <c r="F37" s="22" t="inlineStr"/>
-      <c r="G37" s="22" t="inlineStr"/>
-      <c r="H37" s="22" t="inlineStr"/>
-      <c r="I37" s="22" t="inlineStr"/>
-      <c r="J37" s="19" t="n"/>
-      <c r="K37" s="22" t="inlineStr"/>
-      <c r="L37" s="22" t="inlineStr"/>
-    </row>
-    <row r="38" ht="22" customHeight="1">
-      <c r="A38" s="21" t="n">
-        <v>7</v>
-      </c>
-      <c r="B38" s="22" t="inlineStr"/>
-      <c r="C38" s="22" t="inlineStr"/>
-      <c r="D38" s="22" t="inlineStr"/>
-      <c r="E38" s="22" t="inlineStr"/>
-      <c r="F38" s="22" t="inlineStr"/>
-      <c r="G38" s="22" t="inlineStr"/>
-      <c r="H38" s="22" t="inlineStr"/>
-      <c r="I38" s="22" t="inlineStr"/>
-      <c r="J38" s="19" t="n"/>
-      <c r="K38" s="22" t="inlineStr"/>
-      <c r="L38" s="22" t="n"/>
-    </row>
-    <row r="39" ht="22" customHeight="1">
-      <c r="A39" s="21" t="n">
-        <v>8</v>
-      </c>
-      <c r="B39" s="22" t="inlineStr"/>
-      <c r="C39" s="22" t="inlineStr"/>
-      <c r="D39" s="22" t="inlineStr"/>
-      <c r="E39" s="22" t="inlineStr"/>
-      <c r="F39" s="22" t="inlineStr"/>
-      <c r="G39" s="22" t="inlineStr"/>
-      <c r="H39" s="22" t="inlineStr"/>
-      <c r="I39" s="22" t="inlineStr"/>
-      <c r="J39" s="19" t="n"/>
-      <c r="K39" s="22" t="inlineStr"/>
-      <c r="L39" s="22" t="inlineStr"/>
-    </row>
-    <row r="40" ht="22" customHeight="1">
-      <c r="A40" s="21" t="n">
-        <v>9</v>
-      </c>
-      <c r="B40" s="22" t="inlineStr"/>
-      <c r="C40" s="22" t="inlineStr"/>
-      <c r="D40" s="22" t="inlineStr"/>
-      <c r="E40" s="22" t="inlineStr"/>
-      <c r="F40" s="22" t="inlineStr"/>
-      <c r="G40" s="22" t="inlineStr"/>
-      <c r="H40" s="22" t="inlineStr"/>
-      <c r="I40" s="22" t="inlineStr"/>
-      <c r="J40" s="19" t="n"/>
-      <c r="K40" s="22" t="inlineStr"/>
-      <c r="L40" s="22" t="inlineStr"/>
-    </row>
-    <row r="41" ht="22" customHeight="1">
-      <c r="A41" s="21" t="n">
-        <v>10</v>
-      </c>
-      <c r="B41" s="22" t="inlineStr"/>
-      <c r="C41" s="22" t="inlineStr"/>
-      <c r="D41" s="22" t="inlineStr"/>
-      <c r="E41" s="22" t="inlineStr"/>
-      <c r="F41" s="22" t="inlineStr"/>
-      <c r="G41" s="22" t="inlineStr"/>
-      <c r="H41" s="22" t="inlineStr"/>
-      <c r="I41" s="22" t="inlineStr"/>
-      <c r="J41" s="19" t="n"/>
-      <c r="K41" s="22" t="inlineStr"/>
-      <c r="L41" s="22" t="n"/>
-    </row>
-    <row r="42" ht="22" customHeight="1">
-      <c r="A42" s="21" t="n">
-        <v>11</v>
-      </c>
-      <c r="B42" s="22" t="inlineStr"/>
-      <c r="C42" s="22" t="inlineStr"/>
-      <c r="D42" s="22" t="inlineStr"/>
-      <c r="E42" s="22" t="inlineStr"/>
-      <c r="F42" s="22" t="inlineStr"/>
-      <c r="G42" s="22" t="inlineStr"/>
-      <c r="H42" s="22" t="inlineStr"/>
-      <c r="I42" s="22" t="inlineStr"/>
-      <c r="J42" s="19" t="n"/>
-      <c r="K42" s="22" t="inlineStr"/>
-      <c r="L42" s="22" t="inlineStr"/>
-    </row>
-    <row r="43" ht="22" customHeight="1">
-      <c r="A43" s="21" t="n">
-        <v>12</v>
-      </c>
-      <c r="B43" s="22" t="inlineStr"/>
-      <c r="C43" s="22" t="inlineStr"/>
-      <c r="D43" s="22" t="inlineStr"/>
-      <c r="E43" s="22" t="inlineStr"/>
-      <c r="F43" s="22" t="inlineStr"/>
-      <c r="G43" s="22" t="inlineStr"/>
-      <c r="H43" s="22" t="inlineStr"/>
-      <c r="I43" s="22" t="inlineStr"/>
-      <c r="J43" s="19" t="n"/>
-      <c r="K43" s="22" t="inlineStr"/>
-      <c r="L43" s="22" t="inlineStr"/>
+      <c r="B59" s="22" t="inlineStr"/>
+      <c r="C59" s="22" t="inlineStr"/>
+      <c r="D59" s="22" t="inlineStr"/>
+      <c r="E59" s="22" t="inlineStr"/>
+      <c r="F59" s="22" t="inlineStr"/>
+      <c r="G59" s="22" t="inlineStr"/>
+      <c r="H59" s="22" t="inlineStr"/>
+      <c r="I59" s="22" t="inlineStr"/>
+      <c r="J59" s="19" t="n"/>
+      <c r="K59" s="22" t="inlineStr"/>
+      <c r="L59" s="22" t="inlineStr"/>
     </row>
   </sheetData>
-  <mergeCells count="13">
+  <mergeCells count="16">
     <mergeCell ref="A1:H1"/>
     <mergeCell ref="B10:D10"/>
     <mergeCell ref="B9:D9"/>
     <mergeCell ref="F9:H9"/>
     <mergeCell ref="B6:D6"/>
     <mergeCell ref="A3:H3"/>
+    <mergeCell ref="A19:R19"/>
     <mergeCell ref="A5:H5"/>
     <mergeCell ref="B7:D7"/>
     <mergeCell ref="A30:L30"/>
     <mergeCell ref="B8:H8"/>
     <mergeCell ref="F10:H10"/>
     <mergeCell ref="F6:H6"/>
+    <mergeCell ref="A12:D12"/>
+    <mergeCell ref="A26:D26"/>
     <mergeCell ref="F7:H7"/>
   </mergeCells>
   <dataValidations count="9">
@@ -1973,14 +2114,14 @@
     <dataValidation sqref="I21:I28" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="输入错误" error="请选择是或否" type="list">
       <formula1>"是,否"</formula1>
     </dataValidation>
-    <dataValidation sqref="B14 B15 B16 B17 B18 B19 B20 B21 B22 B23 B24 B25" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="无效选择" error="请选择工艺制作项目" promptTitle="工艺制作" prompt="从下拉菜单选择工艺制作项目" type="list">
-      <formula1>工艺数据库!$A$2:$A$61</formula1>
+    <dataValidation sqref="B14 B15 B16 B17" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="无效选择" error="请从下拉菜单选择工艺制作项目" promptTitle="工艺制作" prompt="点击选择工艺制作" type="list">
+      <formula1>工艺数据库!$A$2:$A$65</formula1>
     </dataValidation>
-    <dataValidation sqref="C14 C15 C16 C17 C18 C19 C20 C21 C22 C23 C24 C25" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="无效选择" error="请选择车缝工艺项目" promptTitle="车缝工艺" prompt="从下拉菜单选择车缝工艺项目" type="list">
-      <formula1>工艺数据库!$B$2:$B$31</formula1>
+    <dataValidation sqref="B21 B22 B23 B24" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="无效选择" error="请从下拉菜单选择车缝工艺项目" promptTitle="车缝工艺" prompt="点击选择车缝工艺" type="list">
+      <formula1>工艺数据库!$B$2:$B$27</formula1>
     </dataValidation>
-    <dataValidation sqref="D14 D15 D16 D17 D18 D19 D20 D21 D22 D23 D24 D25" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="无效选择" error="请选择成衣工艺项目" promptTitle="成衣工艺" prompt="从下拉菜单选择成衣工艺项目" type="list">
-      <formula1>工艺数据库!$C$2:$C$27</formula1>
+    <dataValidation sqref="B28 B29 B30 B31" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="无效选择" error="请从下拉菜单选择成衣工艺项目" promptTitle="成衣工艺" prompt="点击选择成衣工艺" type="list">
+      <formula1>工艺数据库!$C$2:$C$13</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -1993,26 +2134,26 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C61"/>
+  <dimension ref="A1:C65"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="30" customWidth="1" min="1" max="1"/>
-    <col width="30" customWidth="1" min="2" max="2"/>
-    <col width="40" customWidth="1" min="3" max="3"/>
+    <col width="32" customWidth="1" min="1" max="1"/>
+    <col width="32" customWidth="1" min="2" max="2"/>
+    <col width="32" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="23" t="inlineStr">
-        <is>
-          <t>工艺制作（印花/洗水/其他）</t>
-        </is>
-      </c>
-      <c r="B1" s="23" t="inlineStr">
+      <c r="A1" s="25" t="inlineStr">
+        <is>
+          <t>工艺制作(印花/洗水)</t>
+        </is>
+      </c>
+      <c r="B1" s="25" t="inlineStr">
         <is>
           <t>车缝工艺</t>
         </is>
       </c>
-      <c r="C1" s="23" t="inlineStr">
+      <c r="C1" s="25" t="inlineStr">
         <is>
           <t>成衣工艺</t>
         </is>
@@ -2031,14 +2172,14 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>LJ三针五线（领标）</t>
+          <t>分割线按效果图</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>光变印</t>
+          <t>刻字膜</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -2048,14 +2189,14 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>分割线按效果图</t>
+          <t>压皱</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>刻字膜</t>
+          <t>压胶</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -2072,7 +2213,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>压皱</t>
+          <t>压胶B</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -2082,14 +2223,14 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>工艺1</t>
+          <t>帽口、袖口和脚口包条</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>压胶</t>
+          <t>厚板印</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -2099,14 +2240,14 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>工艺10</t>
+          <t>帽口、袖口和脚口包条用C布</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>压胶B</t>
+          <t>反光印</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -2116,14 +2257,14 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>工艺11</t>
+          <t>无缝</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>厚板印</t>
+          <t>发泡印</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -2133,14 +2274,14 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>工艺12</t>
+          <t>无缝贴袋</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>反光印</t>
+          <t>吊染</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -2150,14 +2291,14 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>工艺13</t>
+          <t>猫须</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>发泡印</t>
+          <t>哑光胶浆</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -2167,14 +2308,14 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>工艺14</t>
+          <t>破洞</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>吊染</t>
+          <t>喷马骝</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -2184,14 +2325,14 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>工艺15</t>
+          <t>袋布用C布</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>吊磨</t>
+          <t>基础洗水</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -2201,14 +2342,14 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>工艺2</t>
+          <t>车线对布色</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>哑光胶浆</t>
+          <t>夜光印</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -2218,226 +2359,161 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>工艺3</t>
+          <t>镭射</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>喷马骝</t>
+          <t>工艺1</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>人字车</t>
-        </is>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>工艺4</t>
+          <t>冚车双针</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>基础洗水</t>
+          <t>工艺10</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>冚车双针</t>
-        </is>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>工艺5</t>
+          <t>分割线按效果图</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>夜光印</t>
+          <t>工艺11</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>分割线按效果图</t>
-        </is>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>工艺6</t>
+          <t>包边</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>怀旧洗</t>
+          <t>工艺12</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>包边</t>
-        </is>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>工艺7</t>
+          <t>四针六线</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>成衣染色</t>
+          <t>工艺13</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>四针六线</t>
-        </is>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>工艺8</t>
+          <t>埋夹</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>成衣涂料染色</t>
+          <t>工艺14</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>埋夹</t>
-        </is>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>工艺9</t>
+          <t>平车</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>手擦</t>
+          <t>工艺15</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>帽口、袖口和脚口包条用C布</t>
-        </is>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>帽口、袖口和脚口包条</t>
+          <t>打揽</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>手绘</t>
+          <t>工艺2</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>平车</t>
-        </is>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>无缝</t>
+          <t>拉筒</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>扎染</t>
+          <t>工艺3</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>打揽</t>
-        </is>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>无缝贴袋</t>
+          <t>暗缝</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>打枣</t>
+          <t>工艺4</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>拉筒</t>
-        </is>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>白色</t>
+          <t>机车折</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>拨印</t>
+          <t>工艺5</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>暗缝</t>
-        </is>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>绿色</t>
+          <t>来去缝</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>无缝</t>
+          <t>工艺6</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>机车折</t>
-        </is>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>袋布用C布</t>
+          <t>缩褶</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>无缝B</t>
+          <t>工艺7</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
-        <is>
-          <t>来去缝</t>
-        </is>
-      </c>
-      <c r="C26" t="inlineStr">
         <is>
           <t>车线对布色</t>
         </is>
@@ -2446,275 +2522,278 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>无缝贴袋用B布</t>
+          <t>工艺8</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>缩褶</t>
-        </is>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>黑色</t>
+          <t>鸡英</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>普洗</t>
-        </is>
-      </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>袋布用C布</t>
+          <t>工艺9</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>普通胶浆</t>
-        </is>
-      </c>
-      <c r="B29" t="inlineStr">
-        <is>
-          <t>车线对布色</t>
+          <t>怀旧洗</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>植绒印</t>
-        </is>
-      </c>
-      <c r="B30" t="inlineStr">
-        <is>
-          <t>隐形拉链16-18cm长上下打枣</t>
+          <t>成衣染色</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>毛巾绣</t>
-        </is>
-      </c>
-      <c r="B31" t="inlineStr">
-        <is>
-          <t>鸡英</t>
+          <t>手擦</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>水浆</t>
+          <t>扎染</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>洗水酵洗</t>
+          <t>打枣</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>温变印</t>
+          <t>拨印</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>滴塑</t>
+          <t>无缝</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>漂洗</t>
+          <t>无缝B</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>炒盐</t>
+          <t>无缝贴袋用B布</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>炒雪花</t>
+          <t>普洗</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>烫金</t>
+          <t>普通胶浆</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>烫银</t>
+          <t>植绒印</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>热转印</t>
+          <t>毛巾绣</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>热转印B</t>
+          <t>水浆</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>牙刷绣</t>
+          <t>洗水酵洗</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>猫须</t>
+          <t>滴塑</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>珠片绣</t>
+          <t>炒盐</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>电脑绣</t>
+          <t>炒雪花</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>盘带绣</t>
+          <t>烫金</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>石磨</t>
+          <t>烫银</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>破洞</t>
+          <t>热转印</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>硅胶印</t>
+          <t>热转印B</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>碧纹洗</t>
+          <t>白色</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>绣花</t>
+          <t>石磨</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>绳绣</t>
+          <t>硅胶印</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>贴布绣</t>
+          <t>碧纹洗</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>透气胶印</t>
+          <t>绣花</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>酵洗</t>
+          <t>绳绣</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>酵洗加软</t>
+          <t>绿色</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>锁链绣</t>
+          <t>贴布绣</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>镭射</t>
+          <t>透气胶印</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>高周波</t>
+          <t>酵洗</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
+          <t>酵洗加软</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>隐形拉链16-18cm长上下打枣</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>高周波</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
           <t>高频烫画</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>黑色</t>
         </is>
       </c>
     </row>

--- a/config/成衣工艺单_设计师填表模板_v7.xlsx
+++ b/config/成衣工艺单_设计师填表模板_v7.xlsx
@@ -7,9 +7,21 @@
   </bookViews>
   <sheets>
     <sheet name="成衣工艺制单" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="工艺数据库" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="工艺数据库" sheetId="2" state="hidden" r:id="rId2"/>
   </sheets>
-  <definedNames/>
+  <definedNames>
+    <definedName name="cat_make_洗水">工艺数据库!$B$2:$B$21</definedName>
+    <definedName name="cat_make_热转压印">工艺数据库!$C$2:$C$21</definedName>
+    <definedName name="cat_make_直喷印花">工艺数据库!$D$2:$D$21</definedName>
+    <definedName name="cat_make_绣花">工艺数据库!$E$2:$E$21</definedName>
+    <definedName name="cat_make_网板印花">工艺数据库!$F$2:$F$21</definedName>
+    <definedName name="cat_sew_无缝">工艺数据库!$B$11:$B$24</definedName>
+    <definedName name="cat_sew_洗水">工艺数据库!$C$11:$C$24</definedName>
+    <definedName name="cat_sew_热转压印">工艺数据库!$D$11:$D$24</definedName>
+    <definedName name="cat_sew_绣花">工艺数据库!$E$11:$E$24</definedName>
+    <definedName name="cat_sew_网板印花">工艺数据库!$F$11:$F$24</definedName>
+    <definedName name="cat_garm">工艺数据库!$A$30:$A$47</definedName>
+  </definedNames>
   <calcPr calcId="191029" fullCalcOnLoad="1"/>
 </workbook>
 </file>
@@ -17,7 +29,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="28">
+  <fonts count="27">
     <font>
       <name val="宋体"/>
       <charset val="134"/>
@@ -202,11 +214,6 @@
     </font>
     <font>
       <b val="1"/>
-      <color rgb="00FFFFFF"/>
-      <sz val="12"/>
-    </font>
-    <font>
-      <b val="1"/>
       <sz val="12"/>
     </font>
     <font>
@@ -440,12 +447,12 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="00FFFF00"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="004472C4"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00FFFF00"/>
       </patternFill>
     </fill>
   </fills>
@@ -795,7 +802,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="26">
+  <cellXfs count="28">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -851,9 +858,19 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="25" fillId="38" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="26" fillId="39" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="27" fillId="38" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="25" fillId="38" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="26" fillId="39" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="38" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="39" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="49">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
@@ -1266,13 +1283,14 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:S59"/>
+  <dimension ref="A1:S43"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
-    <col width="28" customWidth="1" min="2" max="2"/>
-    <col width="16" customWidth="1" min="3" max="3"/>
-    <col width="10" customWidth="1" min="4" max="6"/>
+    <col width="18" customWidth="1" min="2" max="2"/>
+    <col width="22" customWidth="1" min="3" max="3"/>
+    <col width="16" customWidth="1" min="4" max="6"/>
+    <col width="10" customWidth="1" min="5" max="5"/>
     <col width="10" customWidth="1" min="7" max="7"/>
     <col width="9.75" customWidth="1" min="8" max="8"/>
     <col width="8.125" customWidth="1" min="9" max="9"/>
@@ -1408,15 +1426,20 @@
       </c>
       <c r="B13" s="24" t="inlineStr">
         <is>
+          <t>工艺大类</t>
+        </is>
+      </c>
+      <c r="C13" s="24" t="inlineStr">
+        <is>
           <t>工艺名称</t>
         </is>
       </c>
-      <c r="C13" s="24" t="inlineStr">
+      <c r="D13" s="24" t="inlineStr">
         <is>
           <t>制衣厂</t>
         </is>
       </c>
-      <c r="D13" s="24" t="inlineStr">
+      <c r="E13" s="24" t="inlineStr">
         <is>
           <t>单价</t>
         </is>
@@ -1448,83 +1471,297 @@
           <t>▼ 车缝工艺</t>
         </is>
       </c>
+      <c r="S19" s="16" t="n"/>
     </row>
     <row r="20" ht="20" customHeight="1">
-      <c r="A20" s="24" t="inlineStr">
+      <c r="A20" s="25" t="inlineStr">
         <is>
           <t>序号</t>
         </is>
       </c>
-      <c r="B20" s="24" t="inlineStr">
+      <c r="B20" s="25" t="inlineStr">
+        <is>
+          <t>工艺大类</t>
+        </is>
+      </c>
+      <c r="C20" s="25" t="inlineStr">
         <is>
           <t>工艺名称</t>
         </is>
       </c>
-      <c r="C20" s="24" t="inlineStr">
+      <c r="D20" s="25" t="inlineStr">
         <is>
           <t>制衣厂</t>
         </is>
       </c>
-      <c r="D20" s="24" t="inlineStr">
+      <c r="E20" s="25" t="inlineStr">
         <is>
           <t>单价</t>
         </is>
       </c>
+      <c r="F20" s="4" t="inlineStr">
+        <is>
+          <t>面料编号</t>
+        </is>
+      </c>
+      <c r="G20" s="4" t="inlineStr">
+        <is>
+          <t>色号</t>
+        </is>
+      </c>
+      <c r="H20" s="4" t="inlineStr">
+        <is>
+          <t>颜色名</t>
+        </is>
+      </c>
+      <c r="I20" s="17" t="inlineStr">
+        <is>
+          <t>是否罗纹</t>
+        </is>
+      </c>
+      <c r="J20" s="17" t="inlineStr">
+        <is>
+          <t>幅宽/CM</t>
+        </is>
+      </c>
+      <c r="K20" s="17" t="inlineStr">
+        <is>
+          <t>克重</t>
+        </is>
+      </c>
+      <c r="L20" s="17" t="inlineStr">
+        <is>
+          <t>供应商</t>
+        </is>
+      </c>
+      <c r="M20" s="17" t="inlineStr">
+        <is>
+          <t>成分</t>
+        </is>
+      </c>
+      <c r="N20" s="17" t="inlineStr">
+        <is>
+          <t>品名</t>
+        </is>
+      </c>
+      <c r="O20" s="17" t="inlineStr">
+        <is>
+          <t>采购米长</t>
+        </is>
+      </c>
+      <c r="P20" s="17" t="inlineStr">
+        <is>
+          <t>采购金额</t>
+        </is>
+      </c>
+      <c r="Q20" s="17" t="inlineStr">
+        <is>
+          <t>采购人</t>
+        </is>
+      </c>
+      <c r="R20" s="17" t="inlineStr">
+        <is>
+          <t>要求到货时间</t>
+        </is>
+      </c>
     </row>
     <row r="21" ht="22" customHeight="1">
-      <c r="A21" t="n">
+      <c r="A21" s="15" t="n">
         <v>1</v>
       </c>
+      <c r="B21" s="5" t="inlineStr"/>
+      <c r="C21" s="5" t="inlineStr"/>
+      <c r="D21" s="5" t="inlineStr"/>
+      <c r="E21" s="15" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="F21" s="18" t="inlineStr"/>
+      <c r="G21" s="18" t="inlineStr"/>
+      <c r="H21" s="18" t="inlineStr"/>
+      <c r="I21" s="19" t="n"/>
+      <c r="J21" s="19" t="n"/>
+      <c r="K21" s="19" t="n"/>
+      <c r="L21" s="19" t="n"/>
+      <c r="M21" s="19" t="n"/>
+      <c r="N21" s="19" t="n"/>
+      <c r="O21" s="19" t="n"/>
+      <c r="P21" s="19" t="n"/>
+      <c r="Q21" s="19" t="n"/>
+      <c r="R21" s="19" t="n"/>
     </row>
     <row r="22" ht="22" customHeight="1">
-      <c r="A22" t="n">
+      <c r="A22" s="15" t="n">
         <v>2</v>
       </c>
+      <c r="B22" s="5" t="inlineStr"/>
+      <c r="C22" s="5" t="inlineStr"/>
+      <c r="D22" s="5" t="inlineStr"/>
+      <c r="E22" s="15" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="F22" s="18" t="inlineStr"/>
+      <c r="G22" s="18" t="inlineStr"/>
+      <c r="H22" s="18" t="inlineStr"/>
+      <c r="I22" s="19" t="n"/>
+      <c r="J22" s="19" t="n"/>
+      <c r="K22" s="19" t="n"/>
+      <c r="L22" s="19" t="n"/>
+      <c r="M22" s="19" t="n"/>
+      <c r="N22" s="19" t="n"/>
+      <c r="O22" s="19" t="n"/>
+      <c r="P22" s="19" t="n"/>
+      <c r="Q22" s="19" t="n"/>
+      <c r="R22" s="19" t="n"/>
     </row>
     <row r="23" ht="22" customHeight="1">
-      <c r="A23" t="n">
+      <c r="A23" s="15" t="n">
         <v>3</v>
       </c>
+      <c r="B23" s="5" t="inlineStr"/>
+      <c r="C23" s="5" t="inlineStr"/>
+      <c r="D23" s="5" t="inlineStr"/>
+      <c r="E23" s="15" t="inlineStr"/>
+      <c r="F23" s="18" t="inlineStr"/>
+      <c r="G23" s="18" t="inlineStr"/>
+      <c r="H23" s="18" t="inlineStr"/>
+      <c r="I23" s="19" t="n"/>
+      <c r="J23" s="19" t="n"/>
+      <c r="K23" s="19" t="n"/>
+      <c r="L23" s="19" t="n"/>
+      <c r="M23" s="19" t="n"/>
+      <c r="N23" s="19" t="n"/>
+      <c r="O23" s="19" t="n"/>
+      <c r="P23" s="19" t="n"/>
+      <c r="Q23" s="19" t="n"/>
+      <c r="R23" s="19" t="n"/>
     </row>
     <row r="24" ht="22" customHeight="1">
-      <c r="A24" t="n">
+      <c r="A24" s="15" t="n">
         <v>4</v>
       </c>
-    </row>
-    <row r="25" ht="22" customHeight="1"/>
+      <c r="B24" s="5" t="inlineStr"/>
+      <c r="C24" s="5" t="inlineStr"/>
+      <c r="D24" s="5" t="inlineStr"/>
+      <c r="E24" s="15" t="inlineStr"/>
+      <c r="F24" s="18" t="inlineStr"/>
+      <c r="G24" s="18" t="inlineStr"/>
+      <c r="H24" s="18" t="inlineStr"/>
+      <c r="I24" s="19" t="n"/>
+      <c r="J24" s="19" t="n"/>
+      <c r="K24" s="19" t="n"/>
+      <c r="L24" s="19" t="n"/>
+      <c r="M24" s="19" t="n"/>
+      <c r="N24" s="19" t="n"/>
+      <c r="O24" s="19" t="n"/>
+      <c r="P24" s="19" t="n"/>
+      <c r="Q24" s="19" t="n"/>
+      <c r="R24" s="19" t="n"/>
+    </row>
+    <row r="25" ht="22" customHeight="1">
+      <c r="A25" s="15" t="inlineStr"/>
+      <c r="B25" s="5" t="inlineStr"/>
+      <c r="C25" s="5" t="inlineStr"/>
+      <c r="D25" s="5" t="inlineStr"/>
+      <c r="E25" s="15" t="inlineStr"/>
+      <c r="F25" s="18" t="inlineStr"/>
+      <c r="G25" s="18" t="inlineStr"/>
+      <c r="H25" s="18" t="inlineStr"/>
+      <c r="I25" s="19" t="n"/>
+      <c r="J25" s="19" t="n"/>
+      <c r="K25" s="19" t="n"/>
+      <c r="L25" s="19" t="n"/>
+      <c r="M25" s="19" t="n"/>
+      <c r="N25" s="19" t="n"/>
+      <c r="O25" s="19" t="n"/>
+      <c r="P25" s="19" t="n"/>
+      <c r="Q25" s="19" t="n"/>
+      <c r="R25" s="19" t="n"/>
+    </row>
     <row r="26" ht="22" customHeight="1">
-      <c r="A26" s="23" t="inlineStr">
+      <c r="A26" s="26" t="inlineStr">
         <is>
           <t>▼ 成衣工艺</t>
         </is>
       </c>
+      <c r="B26" s="6" t="n"/>
+      <c r="C26" s="6" t="n"/>
+      <c r="D26" s="6" t="n"/>
+      <c r="E26" s="7" t="n"/>
+      <c r="F26" s="18" t="inlineStr"/>
+      <c r="G26" s="18" t="inlineStr"/>
+      <c r="H26" s="18" t="inlineStr"/>
+      <c r="I26" s="19" t="n"/>
+      <c r="J26" s="19" t="n"/>
+      <c r="K26" s="19" t="n"/>
+      <c r="L26" s="19" t="n"/>
+      <c r="M26" s="19" t="n"/>
+      <c r="N26" s="19" t="n"/>
+      <c r="O26" s="19" t="n"/>
+      <c r="P26" s="19" t="n"/>
+      <c r="Q26" s="19" t="n"/>
+      <c r="R26" s="19" t="n"/>
     </row>
     <row r="27" ht="22" customHeight="1">
-      <c r="A27" s="24" t="inlineStr">
+      <c r="A27" s="25" t="inlineStr">
         <is>
           <t>序号</t>
         </is>
       </c>
-      <c r="B27" s="24" t="inlineStr">
+      <c r="B27" s="27" t="inlineStr">
         <is>
           <t>工艺名称</t>
         </is>
       </c>
-      <c r="C27" s="24" t="inlineStr">
+      <c r="C27" s="27" t="inlineStr">
         <is>
           <t>制衣厂</t>
         </is>
       </c>
-      <c r="D27" s="24" t="inlineStr">
+      <c r="D27" s="27" t="inlineStr">
         <is>
           <t>单价</t>
         </is>
       </c>
+      <c r="E27" s="15" t="inlineStr"/>
+      <c r="F27" s="18" t="inlineStr"/>
+      <c r="G27" s="18" t="inlineStr"/>
+      <c r="H27" s="18" t="inlineStr"/>
+      <c r="I27" s="19" t="n"/>
+      <c r="J27" s="19" t="n"/>
+      <c r="K27" s="19" t="n"/>
+      <c r="L27" s="19" t="n"/>
+      <c r="M27" s="19" t="n"/>
+      <c r="N27" s="19" t="n"/>
+      <c r="O27" s="19" t="n"/>
+      <c r="P27" s="19" t="n"/>
+      <c r="Q27" s="19" t="n"/>
+      <c r="R27" s="19" t="n"/>
     </row>
     <row r="28" ht="22" customHeight="1">
-      <c r="A28" t="n">
+      <c r="A28" s="15" t="n">
         <v>1</v>
       </c>
+      <c r="B28" s="5" t="inlineStr"/>
+      <c r="C28" s="5" t="inlineStr"/>
+      <c r="D28" s="5" t="inlineStr"/>
+      <c r="E28" s="15" t="inlineStr"/>
+      <c r="F28" s="18" t="inlineStr"/>
+      <c r="G28" s="18" t="inlineStr"/>
+      <c r="H28" s="18" t="inlineStr"/>
+      <c r="I28" s="19" t="n"/>
+      <c r="J28" s="19" t="n"/>
+      <c r="K28" s="19" t="n"/>
+      <c r="L28" s="19" t="n"/>
+      <c r="M28" s="19" t="n"/>
+      <c r="N28" s="19" t="n"/>
+      <c r="O28" s="19" t="n"/>
+      <c r="P28" s="19" t="n"/>
+      <c r="Q28" s="19" t="n"/>
+      <c r="R28" s="19" t="n"/>
     </row>
     <row r="29">
       <c r="A29" t="n">
@@ -1532,549 +1769,261 @@
       </c>
     </row>
     <row r="30" ht="24" customHeight="1">
-      <c r="A30" t="n">
+      <c r="A30" s="3" t="n">
         <v>3</v>
       </c>
     </row>
     <row r="31" ht="14.25" customHeight="1">
-      <c r="A31" t="n">
+      <c r="A31" s="20" t="n">
         <v>4</v>
       </c>
-    </row>
-    <row r="32" ht="22" customHeight="1"/>
-    <row r="33" ht="22" customHeight="1"/>
-    <row r="34" ht="22" customHeight="1"/>
+      <c r="B31" s="20" t="inlineStr">
+        <is>
+          <t>辅料名称</t>
+        </is>
+      </c>
+      <c r="C31" s="20" t="inlineStr">
+        <is>
+          <t>规格型号</t>
+        </is>
+      </c>
+      <c r="D31" s="20" t="inlineStr">
+        <is>
+          <t>颜色</t>
+        </is>
+      </c>
+      <c r="E31" s="20" t="inlineStr">
+        <is>
+          <t>用量</t>
+        </is>
+      </c>
+      <c r="F31" s="20" t="inlineStr">
+        <is>
+          <t>单位</t>
+        </is>
+      </c>
+      <c r="G31" s="20" t="inlineStr">
+        <is>
+          <t>采购单价</t>
+        </is>
+      </c>
+      <c r="H31" s="20" t="inlineStr">
+        <is>
+          <t>供应商</t>
+        </is>
+      </c>
+      <c r="I31" s="20" t="inlineStr">
+        <is>
+          <t>联系方式</t>
+        </is>
+      </c>
+      <c r="J31" s="20" t="inlineStr">
+        <is>
+          <t>采购数量</t>
+        </is>
+      </c>
+      <c r="K31" s="20" t="inlineStr">
+        <is>
+          <t>采购人</t>
+        </is>
+      </c>
+      <c r="L31" s="20" t="inlineStr">
+        <is>
+          <t>要求到货时间</t>
+        </is>
+      </c>
+    </row>
+    <row r="32" ht="22" customHeight="1">
+      <c r="A32" s="21" t="n">
+        <v>1</v>
+      </c>
+      <c r="B32" s="22" t="inlineStr"/>
+      <c r="C32" s="22" t="inlineStr"/>
+      <c r="D32" s="22" t="inlineStr"/>
+      <c r="E32" s="22" t="inlineStr"/>
+      <c r="F32" s="22" t="inlineStr"/>
+      <c r="G32" s="22" t="inlineStr"/>
+      <c r="H32" s="22" t="inlineStr"/>
+      <c r="I32" s="22" t="inlineStr"/>
+      <c r="J32" s="19" t="n"/>
+      <c r="K32" s="22" t="inlineStr"/>
+      <c r="L32" s="22" t="n"/>
+    </row>
+    <row r="33" ht="22" customHeight="1">
+      <c r="A33" s="21" t="n">
+        <v>2</v>
+      </c>
+      <c r="B33" s="22" t="inlineStr"/>
+      <c r="C33" s="22" t="inlineStr"/>
+      <c r="D33" s="22" t="inlineStr"/>
+      <c r="E33" s="22" t="inlineStr"/>
+      <c r="F33" s="22" t="inlineStr"/>
+      <c r="G33" s="22" t="inlineStr"/>
+      <c r="H33" s="22" t="inlineStr"/>
+      <c r="I33" s="22" t="inlineStr"/>
+      <c r="J33" s="19" t="n"/>
+      <c r="K33" s="22" t="inlineStr"/>
+      <c r="L33" s="22" t="inlineStr"/>
+    </row>
+    <row r="34" ht="22" customHeight="1">
+      <c r="A34" s="21" t="n">
+        <v>3</v>
+      </c>
+      <c r="B34" s="22" t="inlineStr"/>
+      <c r="C34" s="22" t="inlineStr"/>
+      <c r="D34" s="22" t="inlineStr"/>
+      <c r="E34" s="22" t="inlineStr"/>
+      <c r="F34" s="22" t="inlineStr"/>
+      <c r="G34" s="22" t="inlineStr"/>
+      <c r="H34" s="22" t="inlineStr"/>
+      <c r="I34" s="22" t="inlineStr"/>
+      <c r="J34" s="19" t="n"/>
+      <c r="K34" s="22" t="inlineStr"/>
+      <c r="L34" s="22" t="inlineStr"/>
+    </row>
     <row r="35" ht="22" customHeight="1">
-      <c r="A35" s="3" t="inlineStr">
-        <is>
-          <t>▼ SKU 与面料</t>
-        </is>
-      </c>
-      <c r="S35" s="16" t="n"/>
+      <c r="A35" s="21" t="n">
+        <v>4</v>
+      </c>
+      <c r="B35" s="22" t="inlineStr"/>
+      <c r="C35" s="22" t="inlineStr"/>
+      <c r="D35" s="22" t="inlineStr"/>
+      <c r="E35" s="22" t="inlineStr"/>
+      <c r="F35" s="22" t="inlineStr"/>
+      <c r="G35" s="22" t="inlineStr"/>
+      <c r="H35" s="22" t="inlineStr"/>
+      <c r="I35" s="22" t="inlineStr"/>
+      <c r="J35" s="19" t="n"/>
+      <c r="K35" s="22" t="inlineStr"/>
+      <c r="L35" s="22" t="n"/>
     </row>
     <row r="36" ht="22" customHeight="1">
-      <c r="A36" s="9" t="inlineStr">
-        <is>
-          <t>SKU编号</t>
-        </is>
-      </c>
-      <c r="B36" s="4" t="inlineStr">
-        <is>
-          <t>颜色</t>
-        </is>
-      </c>
-      <c r="C36" s="4" t="inlineStr">
-        <is>
-          <t>尺码</t>
-        </is>
-      </c>
-      <c r="D36" s="4" t="inlineStr">
-        <is>
-          <t>件数</t>
-        </is>
-      </c>
-      <c r="E36" s="17" t="inlineStr">
-        <is>
-          <t>布类</t>
-        </is>
-      </c>
-      <c r="F36" s="4" t="inlineStr">
-        <is>
-          <t>面料编号</t>
-        </is>
-      </c>
-      <c r="G36" s="4" t="inlineStr">
-        <is>
-          <t>色号</t>
-        </is>
-      </c>
-      <c r="H36" s="4" t="inlineStr">
-        <is>
-          <t>颜色名</t>
-        </is>
-      </c>
-      <c r="I36" s="17" t="inlineStr">
-        <is>
-          <t>是否罗纹</t>
-        </is>
-      </c>
-      <c r="J36" s="17" t="inlineStr">
-        <is>
-          <t>幅宽/CM</t>
-        </is>
-      </c>
-      <c r="K36" s="17" t="inlineStr">
-        <is>
-          <t>克重</t>
-        </is>
-      </c>
-      <c r="L36" s="17" t="inlineStr">
-        <is>
-          <t>供应商</t>
-        </is>
-      </c>
-      <c r="M36" s="17" t="inlineStr">
-        <is>
-          <t>成分</t>
-        </is>
-      </c>
-      <c r="N36" s="17" t="inlineStr">
-        <is>
-          <t>品名</t>
-        </is>
-      </c>
-      <c r="O36" s="17" t="inlineStr">
-        <is>
-          <t>采购米长</t>
-        </is>
-      </c>
-      <c r="P36" s="17" t="inlineStr">
-        <is>
-          <t>采购金额</t>
-        </is>
-      </c>
-      <c r="Q36" s="17" t="inlineStr">
-        <is>
-          <t>采购人</t>
-        </is>
-      </c>
-      <c r="R36" s="17" t="inlineStr">
-        <is>
-          <t>要求到货时间</t>
-        </is>
-      </c>
+      <c r="A36" s="21" t="n">
+        <v>5</v>
+      </c>
+      <c r="B36" s="22" t="inlineStr"/>
+      <c r="C36" s="22" t="inlineStr"/>
+      <c r="D36" s="22" t="inlineStr"/>
+      <c r="E36" s="22" t="inlineStr"/>
+      <c r="F36" s="22" t="inlineStr"/>
+      <c r="G36" s="22" t="inlineStr"/>
+      <c r="H36" s="22" t="inlineStr"/>
+      <c r="I36" s="22" t="inlineStr"/>
+      <c r="J36" s="19" t="n"/>
+      <c r="K36" s="22" t="inlineStr"/>
+      <c r="L36" s="22" t="inlineStr"/>
     </row>
     <row r="37" ht="22" customHeight="1">
-      <c r="A37" s="15" t="n">
-        <v>1</v>
-      </c>
-      <c r="B37" s="5" t="inlineStr"/>
-      <c r="C37" s="5" t="inlineStr"/>
-      <c r="D37" s="5" t="inlineStr"/>
-      <c r="E37" s="15" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="F37" s="18" t="inlineStr"/>
-      <c r="G37" s="18" t="inlineStr"/>
-      <c r="H37" s="18" t="inlineStr"/>
-      <c r="I37" s="19" t="n"/>
+      <c r="A37" s="21" t="n">
+        <v>6</v>
+      </c>
+      <c r="B37" s="22" t="inlineStr"/>
+      <c r="C37" s="22" t="inlineStr"/>
+      <c r="D37" s="22" t="inlineStr"/>
+      <c r="E37" s="22" t="inlineStr"/>
+      <c r="F37" s="22" t="inlineStr"/>
+      <c r="G37" s="22" t="inlineStr"/>
+      <c r="H37" s="22" t="inlineStr"/>
+      <c r="I37" s="22" t="inlineStr"/>
       <c r="J37" s="19" t="n"/>
-      <c r="K37" s="19" t="n"/>
-      <c r="L37" s="19" t="n"/>
-      <c r="M37" s="19" t="n"/>
-      <c r="N37" s="19" t="n"/>
-      <c r="O37" s="19" t="n"/>
-      <c r="P37" s="19" t="n"/>
-      <c r="Q37" s="19" t="n"/>
-      <c r="R37" s="19" t="n"/>
+      <c r="K37" s="22" t="inlineStr"/>
+      <c r="L37" s="22" t="inlineStr"/>
     </row>
     <row r="38" ht="22" customHeight="1">
-      <c r="A38" s="15" t="inlineStr"/>
-      <c r="B38" s="5" t="inlineStr"/>
-      <c r="C38" s="5" t="inlineStr"/>
-      <c r="D38" s="5" t="inlineStr"/>
-      <c r="E38" s="15" t="inlineStr">
-        <is>
-          <t>B</t>
-        </is>
-      </c>
-      <c r="F38" s="18" t="inlineStr"/>
-      <c r="G38" s="18" t="inlineStr"/>
-      <c r="H38" s="18" t="inlineStr"/>
-      <c r="I38" s="19" t="n"/>
+      <c r="A38" s="21" t="n">
+        <v>7</v>
+      </c>
+      <c r="B38" s="22" t="inlineStr"/>
+      <c r="C38" s="22" t="inlineStr"/>
+      <c r="D38" s="22" t="inlineStr"/>
+      <c r="E38" s="22" t="inlineStr"/>
+      <c r="F38" s="22" t="inlineStr"/>
+      <c r="G38" s="22" t="inlineStr"/>
+      <c r="H38" s="22" t="inlineStr"/>
+      <c r="I38" s="22" t="inlineStr"/>
       <c r="J38" s="19" t="n"/>
-      <c r="K38" s="19" t="n"/>
-      <c r="L38" s="19" t="n"/>
-      <c r="M38" s="19" t="n"/>
-      <c r="N38" s="19" t="n"/>
-      <c r="O38" s="19" t="n"/>
-      <c r="P38" s="19" t="n"/>
-      <c r="Q38" s="19" t="n"/>
-      <c r="R38" s="19" t="n"/>
+      <c r="K38" s="22" t="inlineStr"/>
+      <c r="L38" s="22" t="n"/>
     </row>
     <row r="39" ht="22" customHeight="1">
-      <c r="A39" s="15" t="inlineStr"/>
-      <c r="B39" s="5" t="inlineStr"/>
-      <c r="C39" s="5" t="inlineStr"/>
-      <c r="D39" s="5" t="inlineStr"/>
-      <c r="E39" s="15" t="inlineStr"/>
-      <c r="F39" s="18" t="inlineStr"/>
-      <c r="G39" s="18" t="inlineStr"/>
-      <c r="H39" s="18" t="inlineStr"/>
-      <c r="I39" s="19" t="n"/>
+      <c r="A39" s="21" t="n">
+        <v>8</v>
+      </c>
+      <c r="B39" s="22" t="inlineStr"/>
+      <c r="C39" s="22" t="inlineStr"/>
+      <c r="D39" s="22" t="inlineStr"/>
+      <c r="E39" s="22" t="inlineStr"/>
+      <c r="F39" s="22" t="inlineStr"/>
+      <c r="G39" s="22" t="inlineStr"/>
+      <c r="H39" s="22" t="inlineStr"/>
+      <c r="I39" s="22" t="inlineStr"/>
       <c r="J39" s="19" t="n"/>
-      <c r="K39" s="19" t="n"/>
-      <c r="L39" s="19" t="n"/>
-      <c r="M39" s="19" t="n"/>
-      <c r="N39" s="19" t="n"/>
-      <c r="O39" s="19" t="n"/>
-      <c r="P39" s="19" t="n"/>
-      <c r="Q39" s="19" t="n"/>
-      <c r="R39" s="19" t="n"/>
+      <c r="K39" s="22" t="inlineStr"/>
+      <c r="L39" s="22" t="inlineStr"/>
     </row>
     <row r="40" ht="22" customHeight="1">
-      <c r="A40" s="15" t="inlineStr"/>
-      <c r="B40" s="5" t="inlineStr"/>
-      <c r="C40" s="5" t="inlineStr"/>
-      <c r="D40" s="5" t="inlineStr"/>
-      <c r="E40" s="15" t="inlineStr"/>
-      <c r="F40" s="18" t="inlineStr"/>
-      <c r="G40" s="18" t="inlineStr"/>
-      <c r="H40" s="18" t="inlineStr"/>
-      <c r="I40" s="19" t="n"/>
+      <c r="A40" s="21" t="n">
+        <v>9</v>
+      </c>
+      <c r="B40" s="22" t="inlineStr"/>
+      <c r="C40" s="22" t="inlineStr"/>
+      <c r="D40" s="22" t="inlineStr"/>
+      <c r="E40" s="22" t="inlineStr"/>
+      <c r="F40" s="22" t="inlineStr"/>
+      <c r="G40" s="22" t="inlineStr"/>
+      <c r="H40" s="22" t="inlineStr"/>
+      <c r="I40" s="22" t="inlineStr"/>
       <c r="J40" s="19" t="n"/>
-      <c r="K40" s="19" t="n"/>
-      <c r="L40" s="19" t="n"/>
-      <c r="M40" s="19" t="n"/>
-      <c r="N40" s="19" t="n"/>
-      <c r="O40" s="19" t="n"/>
-      <c r="P40" s="19" t="n"/>
-      <c r="Q40" s="19" t="n"/>
-      <c r="R40" s="19" t="n"/>
+      <c r="K40" s="22" t="inlineStr"/>
+      <c r="L40" s="22" t="inlineStr"/>
     </row>
     <row r="41" ht="22" customHeight="1">
-      <c r="A41" s="15" t="inlineStr"/>
-      <c r="B41" s="5" t="inlineStr"/>
-      <c r="C41" s="5" t="inlineStr"/>
-      <c r="D41" s="5" t="inlineStr"/>
-      <c r="E41" s="15" t="inlineStr"/>
-      <c r="F41" s="18" t="inlineStr"/>
-      <c r="G41" s="18" t="inlineStr"/>
-      <c r="H41" s="18" t="inlineStr"/>
-      <c r="I41" s="19" t="n"/>
+      <c r="A41" s="21" t="n">
+        <v>10</v>
+      </c>
+      <c r="B41" s="22" t="inlineStr"/>
+      <c r="C41" s="22" t="inlineStr"/>
+      <c r="D41" s="22" t="inlineStr"/>
+      <c r="E41" s="22" t="inlineStr"/>
+      <c r="F41" s="22" t="inlineStr"/>
+      <c r="G41" s="22" t="inlineStr"/>
+      <c r="H41" s="22" t="inlineStr"/>
+      <c r="I41" s="22" t="inlineStr"/>
       <c r="J41" s="19" t="n"/>
-      <c r="K41" s="19" t="n"/>
-      <c r="L41" s="19" t="n"/>
-      <c r="M41" s="19" t="n"/>
-      <c r="N41" s="19" t="n"/>
-      <c r="O41" s="19" t="n"/>
-      <c r="P41" s="19" t="n"/>
-      <c r="Q41" s="19" t="n"/>
-      <c r="R41" s="19" t="n"/>
+      <c r="K41" s="22" t="inlineStr"/>
+      <c r="L41" s="22" t="n"/>
     </row>
     <row r="42" ht="22" customHeight="1">
-      <c r="A42" s="15" t="inlineStr"/>
-      <c r="B42" s="5" t="inlineStr"/>
-      <c r="C42" s="5" t="inlineStr"/>
-      <c r="D42" s="5" t="inlineStr"/>
-      <c r="E42" s="15" t="inlineStr"/>
-      <c r="F42" s="18" t="inlineStr"/>
-      <c r="G42" s="18" t="inlineStr"/>
-      <c r="H42" s="18" t="inlineStr"/>
-      <c r="I42" s="19" t="n"/>
+      <c r="A42" s="21" t="n">
+        <v>11</v>
+      </c>
+      <c r="B42" s="22" t="inlineStr"/>
+      <c r="C42" s="22" t="inlineStr"/>
+      <c r="D42" s="22" t="inlineStr"/>
+      <c r="E42" s="22" t="inlineStr"/>
+      <c r="F42" s="22" t="inlineStr"/>
+      <c r="G42" s="22" t="inlineStr"/>
+      <c r="H42" s="22" t="inlineStr"/>
+      <c r="I42" s="22" t="inlineStr"/>
       <c r="J42" s="19" t="n"/>
-      <c r="K42" s="19" t="n"/>
-      <c r="L42" s="19" t="n"/>
-      <c r="M42" s="19" t="n"/>
-      <c r="N42" s="19" t="n"/>
-      <c r="O42" s="19" t="n"/>
-      <c r="P42" s="19" t="n"/>
-      <c r="Q42" s="19" t="n"/>
-      <c r="R42" s="19" t="n"/>
+      <c r="K42" s="22" t="inlineStr"/>
+      <c r="L42" s="22" t="inlineStr"/>
     </row>
     <row r="43" ht="22" customHeight="1">
-      <c r="A43" s="15" t="inlineStr"/>
-      <c r="B43" s="5" t="inlineStr"/>
-      <c r="C43" s="5" t="n"/>
-      <c r="D43" s="5" t="inlineStr"/>
-      <c r="E43" s="15" t="inlineStr"/>
-      <c r="F43" s="18" t="inlineStr"/>
-      <c r="G43" s="18" t="inlineStr"/>
-      <c r="H43" s="18" t="inlineStr"/>
-      <c r="I43" s="19" t="n"/>
+      <c r="A43" s="21" t="n">
+        <v>12</v>
+      </c>
+      <c r="B43" s="22" t="inlineStr"/>
+      <c r="C43" s="22" t="inlineStr"/>
+      <c r="D43" s="22" t="inlineStr"/>
+      <c r="E43" s="22" t="inlineStr"/>
+      <c r="F43" s="22" t="inlineStr"/>
+      <c r="G43" s="22" t="inlineStr"/>
+      <c r="H43" s="22" t="inlineStr"/>
+      <c r="I43" s="22" t="inlineStr"/>
       <c r="J43" s="19" t="n"/>
-      <c r="K43" s="19" t="n"/>
-      <c r="L43" s="19" t="n"/>
-      <c r="M43" s="19" t="n"/>
-      <c r="N43" s="19" t="n"/>
-      <c r="O43" s="19" t="n"/>
-      <c r="P43" s="19" t="n"/>
-      <c r="Q43" s="19" t="n"/>
-      <c r="R43" s="19" t="n"/>
-    </row>
-    <row r="44">
-      <c r="A44" s="15" t="inlineStr"/>
-      <c r="B44" s="5" t="inlineStr"/>
-      <c r="C44" s="5" t="inlineStr"/>
-      <c r="D44" s="5" t="inlineStr"/>
-      <c r="E44" s="15" t="inlineStr"/>
-      <c r="F44" s="18" t="inlineStr"/>
-      <c r="G44" s="18" t="inlineStr"/>
-      <c r="H44" s="18" t="inlineStr"/>
-      <c r="I44" s="19" t="n"/>
-      <c r="J44" s="19" t="n"/>
-      <c r="K44" s="19" t="n"/>
-      <c r="L44" s="19" t="n"/>
-      <c r="M44" s="19" t="n"/>
-      <c r="N44" s="19" t="n"/>
-      <c r="O44" s="19" t="n"/>
-      <c r="P44" s="19" t="n"/>
-      <c r="Q44" s="19" t="n"/>
-      <c r="R44" s="19" t="n"/>
-    </row>
-    <row r="45"/>
-    <row r="46">
-      <c r="A46" s="3" t="inlineStr">
-        <is>
-          <t>▼ 辅料信息</t>
-        </is>
-      </c>
-    </row>
-    <row r="47">
-      <c r="A47" s="20" t="inlineStr">
-        <is>
-          <t>序号</t>
-        </is>
-      </c>
-      <c r="B47" s="20" t="inlineStr">
-        <is>
-          <t>辅料名称</t>
-        </is>
-      </c>
-      <c r="C47" s="20" t="inlineStr">
-        <is>
-          <t>规格型号</t>
-        </is>
-      </c>
-      <c r="D47" s="20" t="inlineStr">
-        <is>
-          <t>颜色</t>
-        </is>
-      </c>
-      <c r="E47" s="20" t="inlineStr">
-        <is>
-          <t>用量</t>
-        </is>
-      </c>
-      <c r="F47" s="20" t="inlineStr">
-        <is>
-          <t>单位</t>
-        </is>
-      </c>
-      <c r="G47" s="20" t="inlineStr">
-        <is>
-          <t>采购单价</t>
-        </is>
-      </c>
-      <c r="H47" s="20" t="inlineStr">
-        <is>
-          <t>供应商</t>
-        </is>
-      </c>
-      <c r="I47" s="20" t="inlineStr">
-        <is>
-          <t>联系方式</t>
-        </is>
-      </c>
-      <c r="J47" s="20" t="inlineStr">
-        <is>
-          <t>采购数量</t>
-        </is>
-      </c>
-      <c r="K47" s="20" t="inlineStr">
-        <is>
-          <t>采购人</t>
-        </is>
-      </c>
-      <c r="L47" s="20" t="inlineStr">
-        <is>
-          <t>要求到货时间</t>
-        </is>
-      </c>
-    </row>
-    <row r="48">
-      <c r="A48" s="21" t="n">
-        <v>1</v>
-      </c>
-      <c r="B48" s="22" t="inlineStr"/>
-      <c r="C48" s="22" t="inlineStr"/>
-      <c r="D48" s="22" t="inlineStr"/>
-      <c r="E48" s="22" t="inlineStr"/>
-      <c r="F48" s="22" t="inlineStr"/>
-      <c r="G48" s="22" t="inlineStr"/>
-      <c r="H48" s="22" t="inlineStr"/>
-      <c r="I48" s="22" t="inlineStr"/>
-      <c r="J48" s="19" t="n"/>
-      <c r="K48" s="22" t="inlineStr"/>
-      <c r="L48" s="22" t="n"/>
-    </row>
-    <row r="49">
-      <c r="A49" s="21" t="n">
-        <v>2</v>
-      </c>
-      <c r="B49" s="22" t="inlineStr"/>
-      <c r="C49" s="22" t="inlineStr"/>
-      <c r="D49" s="22" t="inlineStr"/>
-      <c r="E49" s="22" t="inlineStr"/>
-      <c r="F49" s="22" t="inlineStr"/>
-      <c r="G49" s="22" t="inlineStr"/>
-      <c r="H49" s="22" t="inlineStr"/>
-      <c r="I49" s="22" t="inlineStr"/>
-      <c r="J49" s="19" t="n"/>
-      <c r="K49" s="22" t="inlineStr"/>
-      <c r="L49" s="22" t="inlineStr"/>
-    </row>
-    <row r="50">
-      <c r="A50" s="21" t="n">
-        <v>3</v>
-      </c>
-      <c r="B50" s="22" t="inlineStr"/>
-      <c r="C50" s="22" t="inlineStr"/>
-      <c r="D50" s="22" t="inlineStr"/>
-      <c r="E50" s="22" t="inlineStr"/>
-      <c r="F50" s="22" t="inlineStr"/>
-      <c r="G50" s="22" t="inlineStr"/>
-      <c r="H50" s="22" t="inlineStr"/>
-      <c r="I50" s="22" t="inlineStr"/>
-      <c r="J50" s="19" t="n"/>
-      <c r="K50" s="22" t="inlineStr"/>
-      <c r="L50" s="22" t="inlineStr"/>
-    </row>
-    <row r="51">
-      <c r="A51" s="21" t="n">
-        <v>4</v>
-      </c>
-      <c r="B51" s="22" t="inlineStr"/>
-      <c r="C51" s="22" t="inlineStr"/>
-      <c r="D51" s="22" t="inlineStr"/>
-      <c r="E51" s="22" t="inlineStr"/>
-      <c r="F51" s="22" t="inlineStr"/>
-      <c r="G51" s="22" t="inlineStr"/>
-      <c r="H51" s="22" t="inlineStr"/>
-      <c r="I51" s="22" t="inlineStr"/>
-      <c r="J51" s="19" t="n"/>
-      <c r="K51" s="22" t="inlineStr"/>
-      <c r="L51" s="22" t="n"/>
-    </row>
-    <row r="52">
-      <c r="A52" s="21" t="n">
-        <v>5</v>
-      </c>
-      <c r="B52" s="22" t="inlineStr"/>
-      <c r="C52" s="22" t="inlineStr"/>
-      <c r="D52" s="22" t="inlineStr"/>
-      <c r="E52" s="22" t="inlineStr"/>
-      <c r="F52" s="22" t="inlineStr"/>
-      <c r="G52" s="22" t="inlineStr"/>
-      <c r="H52" s="22" t="inlineStr"/>
-      <c r="I52" s="22" t="inlineStr"/>
-      <c r="J52" s="19" t="n"/>
-      <c r="K52" s="22" t="inlineStr"/>
-      <c r="L52" s="22" t="inlineStr"/>
-    </row>
-    <row r="53">
-      <c r="A53" s="21" t="n">
-        <v>6</v>
-      </c>
-      <c r="B53" s="22" t="inlineStr"/>
-      <c r="C53" s="22" t="inlineStr"/>
-      <c r="D53" s="22" t="inlineStr"/>
-      <c r="E53" s="22" t="inlineStr"/>
-      <c r="F53" s="22" t="inlineStr"/>
-      <c r="G53" s="22" t="inlineStr"/>
-      <c r="H53" s="22" t="inlineStr"/>
-      <c r="I53" s="22" t="inlineStr"/>
-      <c r="J53" s="19" t="n"/>
-      <c r="K53" s="22" t="inlineStr"/>
-      <c r="L53" s="22" t="inlineStr"/>
-    </row>
-    <row r="54">
-      <c r="A54" s="21" t="n">
-        <v>7</v>
-      </c>
-      <c r="B54" s="22" t="inlineStr"/>
-      <c r="C54" s="22" t="inlineStr"/>
-      <c r="D54" s="22" t="inlineStr"/>
-      <c r="E54" s="22" t="inlineStr"/>
-      <c r="F54" s="22" t="inlineStr"/>
-      <c r="G54" s="22" t="inlineStr"/>
-      <c r="H54" s="22" t="inlineStr"/>
-      <c r="I54" s="22" t="inlineStr"/>
-      <c r="J54" s="19" t="n"/>
-      <c r="K54" s="22" t="inlineStr"/>
-      <c r="L54" s="22" t="n"/>
-    </row>
-    <row r="55">
-      <c r="A55" s="21" t="n">
-        <v>8</v>
-      </c>
-      <c r="B55" s="22" t="inlineStr"/>
-      <c r="C55" s="22" t="inlineStr"/>
-      <c r="D55" s="22" t="inlineStr"/>
-      <c r="E55" s="22" t="inlineStr"/>
-      <c r="F55" s="22" t="inlineStr"/>
-      <c r="G55" s="22" t="inlineStr"/>
-      <c r="H55" s="22" t="inlineStr"/>
-      <c r="I55" s="22" t="inlineStr"/>
-      <c r="J55" s="19" t="n"/>
-      <c r="K55" s="22" t="inlineStr"/>
-      <c r="L55" s="22" t="inlineStr"/>
-    </row>
-    <row r="56">
-      <c r="A56" s="21" t="n">
-        <v>9</v>
-      </c>
-      <c r="B56" s="22" t="inlineStr"/>
-      <c r="C56" s="22" t="inlineStr"/>
-      <c r="D56" s="22" t="inlineStr"/>
-      <c r="E56" s="22" t="inlineStr"/>
-      <c r="F56" s="22" t="inlineStr"/>
-      <c r="G56" s="22" t="inlineStr"/>
-      <c r="H56" s="22" t="inlineStr"/>
-      <c r="I56" s="22" t="inlineStr"/>
-      <c r="J56" s="19" t="n"/>
-      <c r="K56" s="22" t="inlineStr"/>
-      <c r="L56" s="22" t="inlineStr"/>
-    </row>
-    <row r="57">
-      <c r="A57" s="21" t="n">
-        <v>10</v>
-      </c>
-      <c r="B57" s="22" t="inlineStr"/>
-      <c r="C57" s="22" t="inlineStr"/>
-      <c r="D57" s="22" t="inlineStr"/>
-      <c r="E57" s="22" t="inlineStr"/>
-      <c r="F57" s="22" t="inlineStr"/>
-      <c r="G57" s="22" t="inlineStr"/>
-      <c r="H57" s="22" t="inlineStr"/>
-      <c r="I57" s="22" t="inlineStr"/>
-      <c r="J57" s="19" t="n"/>
-      <c r="K57" s="22" t="inlineStr"/>
-      <c r="L57" s="22" t="n"/>
-    </row>
-    <row r="58">
-      <c r="A58" s="21" t="n">
-        <v>11</v>
-      </c>
-      <c r="B58" s="22" t="inlineStr"/>
-      <c r="C58" s="22" t="inlineStr"/>
-      <c r="D58" s="22" t="inlineStr"/>
-      <c r="E58" s="22" t="inlineStr"/>
-      <c r="F58" s="22" t="inlineStr"/>
-      <c r="G58" s="22" t="inlineStr"/>
-      <c r="H58" s="22" t="inlineStr"/>
-      <c r="I58" s="22" t="inlineStr"/>
-      <c r="J58" s="19" t="n"/>
-      <c r="K58" s="22" t="inlineStr"/>
-      <c r="L58" s="22" t="inlineStr"/>
-    </row>
-    <row r="59">
-      <c r="A59" s="21" t="n">
-        <v>12</v>
-      </c>
-      <c r="B59" s="22" t="inlineStr"/>
-      <c r="C59" s="22" t="inlineStr"/>
-      <c r="D59" s="22" t="inlineStr"/>
-      <c r="E59" s="22" t="inlineStr"/>
-      <c r="F59" s="22" t="inlineStr"/>
-      <c r="G59" s="22" t="inlineStr"/>
-      <c r="H59" s="22" t="inlineStr"/>
-      <c r="I59" s="22" t="inlineStr"/>
-      <c r="J59" s="19" t="n"/>
-      <c r="K59" s="22" t="inlineStr"/>
-      <c r="L59" s="22" t="inlineStr"/>
+      <c r="K43" s="22" t="inlineStr"/>
+      <c r="L43" s="22" t="inlineStr"/>
     </row>
   </sheetData>
   <mergeCells count="16">
@@ -2084,6 +2033,8 @@
     <mergeCell ref="F9:H9"/>
     <mergeCell ref="B6:D6"/>
     <mergeCell ref="A3:H3"/>
+    <mergeCell ref="A12:E12"/>
+    <mergeCell ref="A26:E26"/>
     <mergeCell ref="A19:R19"/>
     <mergeCell ref="A5:H5"/>
     <mergeCell ref="B7:D7"/>
@@ -2091,11 +2042,9 @@
     <mergeCell ref="B8:H8"/>
     <mergeCell ref="F10:H10"/>
     <mergeCell ref="F6:H6"/>
-    <mergeCell ref="A12:D12"/>
-    <mergeCell ref="A26:D26"/>
     <mergeCell ref="F7:H7"/>
   </mergeCells>
-  <dataValidations count="9">
+  <dataValidations count="17">
     <dataValidation sqref="F6" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="0" type="list">
       <formula1>"OEM,ODM,OBM"</formula1>
     </dataValidation>
@@ -2114,14 +2063,38 @@
     <dataValidation sqref="I21:I28" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="输入错误" error="请选择是或否" type="list">
       <formula1>"是,否"</formula1>
     </dataValidation>
-    <dataValidation sqref="B14 B15 B16 B17" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="无效选择" error="请从下拉菜单选择工艺制作项目" promptTitle="工艺制作" prompt="点击选择工艺制作" type="list">
-      <formula1>工艺数据库!$A$2:$A$65</formula1>
+    <dataValidation sqref="B14 B15 B16 B17" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="无效选择" error="请选择工艺制作的工艺大类" promptTitle="工艺大类" prompt="点击选择工艺制作的工艺大类" type="list">
+      <formula1>工艺数据库!$A$2:$A$6</formula1>
     </dataValidation>
-    <dataValidation sqref="B21 B22 B23 B24" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="无效选择" error="请从下拉菜单选择车缝工艺项目" promptTitle="车缝工艺" prompt="点击选择车缝工艺" type="list">
-      <formula1>工艺数据库!$B$2:$B$27</formula1>
+    <dataValidation sqref="C14" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="无效" error="请先选择大类，再选择工艺制作" promptTitle="工艺名称" prompt="先选大类，再选工艺制作名称" type="list">
+      <formula1>=INDIRECT("'cat_make_'"&amp;SUBSTITUTE($B14,"/","_"))</formula1>
     </dataValidation>
-    <dataValidation sqref="B28 B29 B30 B31" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="无效选择" error="请从下拉菜单选择成衣工艺项目" promptTitle="成衣工艺" prompt="点击选择成衣工艺" type="list">
-      <formula1>工艺数据库!$C$2:$C$13</formula1>
+    <dataValidation sqref="C15" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="无效" error="请先选择大类，再选择工艺制作" promptTitle="工艺名称" prompt="先选大类，再选工艺制作名称" type="list">
+      <formula1>=INDIRECT("'cat_make_'"&amp;SUBSTITUTE($B15,"/","_"))</formula1>
+    </dataValidation>
+    <dataValidation sqref="C16" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="无效" error="请先选择大类，再选择工艺制作" promptTitle="工艺名称" prompt="先选大类，再选工艺制作名称" type="list">
+      <formula1>=INDIRECT("'cat_make_'"&amp;SUBSTITUTE($B16,"/","_"))</formula1>
+    </dataValidation>
+    <dataValidation sqref="C17" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="无效" error="请先选择大类，再选择工艺制作" promptTitle="工艺名称" prompt="先选大类，再选工艺制作名称" type="list">
+      <formula1>=INDIRECT("'cat_make_'"&amp;SUBSTITUTE($B17,"/","_"))</formula1>
+    </dataValidation>
+    <dataValidation sqref="B21 B22 B23 B24" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="无效选择" error="请选择车缝工艺的工艺大类" promptTitle="工艺大类" prompt="点击选择车缝工艺的工艺大类" type="list">
+      <formula1>工艺数据库!$A$11:$A$15</formula1>
+    </dataValidation>
+    <dataValidation sqref="C21" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="无效" error="请先选择大类，再选择车缝工艺" promptTitle="工艺名称" prompt="先选大类，再选车缝工艺名称" type="list">
+      <formula1>=INDIRECT("'cat_sew_'"&amp;SUBSTITUTE($B21,"/","_"))</formula1>
+    </dataValidation>
+    <dataValidation sqref="C22" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="无效" error="请先选择大类，再选择车缝工艺" promptTitle="工艺名称" prompt="先选大类，再选车缝工艺名称" type="list">
+      <formula1>=INDIRECT("'cat_sew_'"&amp;SUBSTITUTE($B22,"/","_"))</formula1>
+    </dataValidation>
+    <dataValidation sqref="C23" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="无效" error="请先选择大类，再选择车缝工艺" promptTitle="工艺名称" prompt="先选大类，再选车缝工艺名称" type="list">
+      <formula1>=INDIRECT("'cat_sew_'"&amp;SUBSTITUTE($B23,"/","_"))</formula1>
+    </dataValidation>
+    <dataValidation sqref="C24" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="无效" error="请先选择大类，再选择车缝工艺" promptTitle="工艺名称" prompt="先选大类，再选车缝工艺名称" type="list">
+      <formula1>=INDIRECT("'cat_sew_'"&amp;SUBSTITUTE($B24,"/","_"))</formula1>
+    </dataValidation>
+    <dataValidation sqref="B28 B29 B30 B31" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="无效" error="请选择成衣工艺" promptTitle="成衣工艺" prompt="点击选择成衣工艺" type="list">
+      <formula1>工艺数据库!$A$30:$A$47</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -2134,666 +2107,682 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C65"/>
+  <dimension ref="A1:F47"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="32" customWidth="1" min="1" max="1"/>
-    <col width="32" customWidth="1" min="2" max="2"/>
-    <col width="32" customWidth="1" min="3" max="3"/>
-  </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="25" t="inlineStr">
-        <is>
-          <t>工艺制作(印花/洗水)</t>
-        </is>
-      </c>
-      <c r="B1" s="25" t="inlineStr">
-        <is>
-          <t>车缝工艺</t>
-        </is>
-      </c>
-      <c r="C1" s="25" t="inlineStr">
-        <is>
-          <t>成衣工艺</t>
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>工艺制作-大类</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>洗水</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>热转压印</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>直喷印花</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>绣花</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>网板印花</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2号隐形拉链，用无缝做法</t>
+          <t>洗水</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>0.2边线</t>
+          <t>吊染</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>分割线按效果图</t>
+          <t>丝印刻字膜烫标</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>数码直喷/不打底</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>V字针绣</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>仿拨印</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>刻字膜</t>
+          <t>热转压印</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>0.3边线</t>
+          <t>喷色</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>压皱</t>
+          <t>丝印烫标（加防升华）</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>数码直喷/打底</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>一字绣（特种专机）</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>光感印</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>压胶</t>
+          <t>直喷印花</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>0.6边线</t>
+          <t>喷马骝</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>取消龟背</t>
+          <t>刻字膜</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>热转印/热升华</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>中空绣</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>厚板印</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>压胶B</t>
+          <t>绣花</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>LJ三针五线（领标）</t>
+          <t>手擦</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>帽口、袖口和脚口包条</t>
+          <t>压褶</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>白墨直喷/不打底</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>人字车</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>反光浆</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>厚板印</t>
+          <t>网板印花</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>三线锁边</t>
+          <t>扎染</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>帽口、袖口和脚口包条用C布</t>
+          <t>厚版肤感弹力硅胶章</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>白墨直喷/打底</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>充棉工艺</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>发泡印</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>反光印</t>
-        </is>
-      </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>三针五线</t>
+          <t>炒盐</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>无缝</t>
+          <t>反光刻字膜</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>包边绣</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>哑光胶浆</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>发泡印</t>
-        </is>
-      </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>三针五线B</t>
+          <t>炒色</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>无缝贴袋</t>
+          <t>激光冲孔</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>十字绣</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>彩色硅胶印</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>吊染</t>
-        </is>
-      </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>三针五线大哈苏</t>
+          <t>炒雪花</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>猫须</t>
+          <t>烫画</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>平绣</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>拉浆/石头浆</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>哑光胶浆</t>
+          <t>车缝工艺-大类</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>两段红色线也LJ三针五线</t>
+          <t>无缝</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>破洞</t>
+          <t>洗水</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>热转压印</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>绣花</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>网板印花</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>喷马骝</t>
+          <t>无缝</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>两针四线</t>
+          <t>无缝压胶</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>袋布用C布</t>
+          <t>吊染</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>成衣刻字膜</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>背胶章仔绣</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>丝印烫标</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>基础洗水</t>
+          <t>洗水</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>两针四线大哈苏</t>
+          <t>酵洗</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>车线对布色</t>
+          <t>喷色</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>高弹肤感硅胶</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>榻榻米绣</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>水显印</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>夜光印</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>五线锁边</t>
+          <t>热转压印</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>镭射</t>
+          <t>喷马骝</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>毛巾绣</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>水浆</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>工艺1</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>冚车双针</t>
+          <t>绣花</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>手擦</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>牙刷绣</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>活性印花</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>工艺10</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>分割线按效果图</t>
+          <t>网板印花</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>扎染</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>珠片绣</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>温变印</t>
         </is>
       </c>
     </row>
     <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>工艺11</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>包边</t>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>普洗</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>立体绣</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>烫金/烫银</t>
         </is>
       </c>
     </row>
     <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>工艺12</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>四针六线</t>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>水床冲孔</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>绳绣</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>热固油墨</t>
         </is>
       </c>
     </row>
     <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>工艺13</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>埋夹</t>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>激光烧花</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>菱形打边绣（特种专机）</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>硅胶印</t>
         </is>
       </c>
     </row>
     <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>工艺14</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>平车</t>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>炒盐</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>贴布绣</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>网点印</t>
         </is>
       </c>
     </row>
     <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>工艺15</t>
-        </is>
-      </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>打揽</t>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>炒色</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>锁链绣</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>裂纹印</t>
         </is>
       </c>
     </row>
     <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>工艺2</t>
-        </is>
-      </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>拉筒</t>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>炒雪花</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>镂空绣</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>轻薄热固油墨</t>
         </is>
       </c>
     </row>
     <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>工艺3</t>
-        </is>
-      </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>暗缝</t>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>砂洗</t>
         </is>
       </c>
     </row>
     <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>工艺4</t>
-        </is>
-      </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>机车折</t>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>破坏</t>
         </is>
       </c>
     </row>
     <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>工艺5</t>
-        </is>
-      </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>来去缝</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>工艺6</t>
-        </is>
-      </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>缩褶</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>工艺7</t>
-        </is>
-      </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>车线对布色</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t>工艺8</t>
-        </is>
-      </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>鸡英</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" t="inlineStr">
-        <is>
-          <t>工艺9</t>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>酵洗</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>怀旧洗</t>
+          <t>成衣工艺</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>成衣染色</t>
+          <t>0.2边线</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>手擦</t>
+          <t>0.5单线</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>扎染</t>
+          <t>2号反底</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>打枣</t>
+          <t>三针五线大哈苏</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>拨印</t>
+          <t>三针四线</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>无缝</t>
+          <t>两针四线大哈苏</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>无缝B</t>
+          <t>分中坎</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>无缝贴袋用B布</t>
+          <t>压胶</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>普洗</t>
+          <t>哨牙线</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>普通胶浆</t>
+          <t>坎双线</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>植绒印</t>
+          <t>小两针四线小哈苏</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>毛巾绣</t>
+          <t>小分中坎</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>水浆</t>
+          <t>小双线（窄针）</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>洗水酵洗</t>
+          <t>峰哥工艺线（高弹丝）</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>滴塑</t>
+          <t>来去缝</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>炒盐</t>
+          <t>牙签线</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>炒雪花</t>
+          <t>落行窄针小双线</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>烫金</t>
-        </is>
-      </c>
-    </row>
-    <row r="48">
-      <c r="A48" t="inlineStr">
-        <is>
-          <t>烫银</t>
-        </is>
-      </c>
-    </row>
-    <row r="49">
-      <c r="A49" t="inlineStr">
-        <is>
-          <t>热转印</t>
-        </is>
-      </c>
-    </row>
-    <row r="50">
-      <c r="A50" t="inlineStr">
-        <is>
-          <t>热转印B</t>
-        </is>
-      </c>
-    </row>
-    <row r="51">
-      <c r="A51" t="inlineStr">
-        <is>
-          <t>白色</t>
-        </is>
-      </c>
-    </row>
-    <row r="52">
-      <c r="A52" t="inlineStr">
-        <is>
-          <t>石磨</t>
-        </is>
-      </c>
-    </row>
-    <row r="53">
-      <c r="A53" t="inlineStr">
-        <is>
-          <t>硅胶印</t>
-        </is>
-      </c>
-    </row>
-    <row r="54">
-      <c r="A54" t="inlineStr">
-        <is>
-          <t>碧纹洗</t>
-        </is>
-      </c>
-    </row>
-    <row r="55">
-      <c r="A55" t="inlineStr">
-        <is>
-          <t>绣花</t>
-        </is>
-      </c>
-    </row>
-    <row r="56">
-      <c r="A56" t="inlineStr">
-        <is>
-          <t>绳绣</t>
-        </is>
-      </c>
-    </row>
-    <row r="57">
-      <c r="A57" t="inlineStr">
-        <is>
-          <t>绿色</t>
-        </is>
-      </c>
-    </row>
-    <row r="58">
-      <c r="A58" t="inlineStr">
-        <is>
-          <t>贴布绣</t>
-        </is>
-      </c>
-    </row>
-    <row r="59">
-      <c r="A59" t="inlineStr">
-        <is>
-          <t>透气胶印</t>
-        </is>
-      </c>
-    </row>
-    <row r="60">
-      <c r="A60" t="inlineStr">
-        <is>
-          <t>酵洗</t>
-        </is>
-      </c>
-    </row>
-    <row r="61">
-      <c r="A61" t="inlineStr">
-        <is>
-          <t>酵洗加软</t>
-        </is>
-      </c>
-    </row>
-    <row r="62">
-      <c r="A62" t="inlineStr">
-        <is>
-          <t>隐形拉链16-18cm长上下打枣</t>
-        </is>
-      </c>
-    </row>
-    <row r="63">
-      <c r="A63" t="inlineStr">
-        <is>
-          <t>高周波</t>
-        </is>
-      </c>
-    </row>
-    <row r="64">
-      <c r="A64" t="inlineStr">
-        <is>
-          <t>高频烫画</t>
-        </is>
-      </c>
-    </row>
-    <row r="65">
-      <c r="A65" t="inlineStr">
-        <is>
-          <t>黑色</t>
+          <t>龅牙线</t>
         </is>
       </c>
     </row>

--- a/config/成衣工艺单_设计师填表模板_v7.xlsx
+++ b/config/成衣工艺单_设计师填表模板_v7.xlsx
@@ -7,20 +7,20 @@
   </bookViews>
   <sheets>
     <sheet name="成衣工艺制单" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="工艺数据库" sheetId="2" state="hidden" r:id="rId2"/>
+    <sheet name="工艺数据库" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="cat_make_洗水">工艺数据库!$B$2:$B$21</definedName>
-    <definedName name="cat_make_热转压印">工艺数据库!$C$2:$C$21</definedName>
-    <definedName name="cat_make_直喷印花">工艺数据库!$D$2:$D$21</definedName>
-    <definedName name="cat_make_绣花">工艺数据库!$E$2:$E$21</definedName>
-    <definedName name="cat_make_网板印花">工艺数据库!$F$2:$F$21</definedName>
-    <definedName name="cat_sew_无缝">工艺数据库!$B$11:$B$24</definedName>
-    <definedName name="cat_sew_洗水">工艺数据库!$C$11:$C$24</definedName>
-    <definedName name="cat_sew_热转压印">工艺数据库!$D$11:$D$24</definedName>
-    <definedName name="cat_sew_绣花">工艺数据库!$E$11:$E$24</definedName>
-    <definedName name="cat_sew_网板印花">工艺数据库!$F$11:$F$24</definedName>
-    <definedName name="cat_garm">工艺数据库!$A$30:$A$47</definedName>
+    <definedName name="cat_make_洗水">工艺数据库!$A$5:$A$24</definedName>
+    <definedName name="cat_make_热转压印">工艺数据库!$B$5:$B$24</definedName>
+    <definedName name="cat_make_直喷印花">工艺数据库!$C$5:$C$24</definedName>
+    <definedName name="cat_make_绣花">工艺数据库!$D$5:$D$24</definedName>
+    <definedName name="cat_make_网板印花">工艺数据库!$E$5:$E$24</definedName>
+    <definedName name="cat_sew_无缝">工艺数据库!$A$29:$A$42</definedName>
+    <definedName name="cat_sew_洗水">工艺数据库!$B$29:$B$42</definedName>
+    <definedName name="cat_sew_热转压印">工艺数据库!$C$29:$C$42</definedName>
+    <definedName name="cat_sew_绣花">工艺数据库!$D$29:$D$42</definedName>
+    <definedName name="cat_sew_网板印花">工艺数据库!$E$29:$E$42</definedName>
+    <definedName name="cat_garm">工艺数据库!$A$44:$A$61</definedName>
   </definedNames>
   <calcPr calcId="191029" fullCalcOnLoad="1"/>
 </workbook>
@@ -29,7 +29,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="27">
+  <fonts count="29">
     <font>
       <name val="宋体"/>
       <charset val="134"/>
@@ -214,11 +214,19 @@
     </font>
     <font>
       <b val="1"/>
-      <sz val="12"/>
+      <color rgb="00FFFFFF"/>
+      <sz val="14"/>
     </font>
     <font>
       <b val="1"/>
       <color rgb="00FFFFFF"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <sz val="11"/>
+    </font>
+    <font>
+      <b val="1"/>
       <sz val="10"/>
     </font>
   </fonts>
@@ -447,7 +455,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00FFFF00"/>
+        <fgColor rgb="002F5496"/>
       </patternFill>
     </fill>
     <fill>
@@ -456,7 +464,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="17">
+  <borders count="18">
     <border>
       <left/>
       <right/>
@@ -654,6 +662,12 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+    </border>
   </borders>
   <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
@@ -858,19 +872,17 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="25" fillId="38" borderId="17" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="39" borderId="17" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="0" borderId="17" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="25" fillId="38" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="39" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="26" fillId="39" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="38" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="39" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="49">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
@@ -1286,11 +1298,10 @@
   <dimension ref="A1:S43"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
-    <col width="8" customWidth="1" min="1" max="1"/>
-    <col width="18" customWidth="1" min="2" max="2"/>
-    <col width="22" customWidth="1" min="3" max="3"/>
-    <col width="16" customWidth="1" min="4" max="6"/>
-    <col width="10" customWidth="1" min="5" max="5"/>
+    <col width="8.75" customWidth="1" min="1" max="1"/>
+    <col width="13" customWidth="1" min="2" max="2"/>
+    <col width="11.875" customWidth="1" min="3" max="3"/>
+    <col width="13" customWidth="1" min="4" max="6"/>
     <col width="10" customWidth="1" min="7" max="7"/>
     <col width="9.75" customWidth="1" min="8" max="8"/>
     <col width="8.125" customWidth="1" min="9" max="9"/>
@@ -1412,91 +1423,110 @@
       <c r="Q10" s="8" t="inlineStr"/>
     </row>
     <row r="12" ht="24" customHeight="1">
-      <c r="A12" s="23" t="inlineStr">
+      <c r="A12" s="3" t="inlineStr">
         <is>
           <t>▼ 工艺制作</t>
         </is>
       </c>
     </row>
     <row r="13" ht="16.5" customHeight="1">
-      <c r="A13" s="24" t="inlineStr">
+      <c r="A13" s="12" t="inlineStr">
         <is>
           <t>序号</t>
         </is>
       </c>
-      <c r="B13" s="24" t="inlineStr">
-        <is>
-          <t>工艺大类</t>
-        </is>
-      </c>
-      <c r="C13" s="24" t="inlineStr">
-        <is>
-          <t>工艺名称</t>
-        </is>
-      </c>
-      <c r="D13" s="24" t="inlineStr">
-        <is>
-          <t>制衣厂</t>
-        </is>
-      </c>
-      <c r="E13" s="24" t="inlineStr">
-        <is>
-          <t>单价</t>
-        </is>
-      </c>
+      <c r="B13" s="12" t="inlineStr">
+        <is>
+          <t>工艺内容</t>
+        </is>
+      </c>
+      <c r="C13" s="13" t="n"/>
+      <c r="D13" s="13" t="n"/>
+      <c r="E13" s="13" t="n"/>
+      <c r="F13" s="13" t="n"/>
+      <c r="G13" s="13" t="n"/>
+      <c r="H13" s="14" t="n"/>
     </row>
     <row r="14" ht="22" customHeight="1">
-      <c r="A14" t="n">
+      <c r="A14" s="15" t="n">
         <v>1</v>
       </c>
+      <c r="B14" s="10" t="inlineStr"/>
+      <c r="C14" s="6" t="n"/>
+      <c r="D14" s="6" t="n"/>
+      <c r="E14" s="6" t="n"/>
+      <c r="F14" s="6" t="n"/>
+      <c r="G14" s="6" t="n"/>
+      <c r="H14" s="7" t="n"/>
     </row>
     <row r="15" ht="22" customHeight="1">
-      <c r="A15" t="n">
+      <c r="A15" s="15" t="n">
         <v>2</v>
       </c>
+      <c r="B15" s="10" t="inlineStr"/>
+      <c r="C15" s="6" t="n"/>
+      <c r="D15" s="6" t="n"/>
+      <c r="E15" s="6" t="n"/>
+      <c r="F15" s="6" t="n"/>
+      <c r="G15" s="6" t="n"/>
+      <c r="H15" s="7" t="n"/>
     </row>
     <row r="16" ht="22" customHeight="1">
-      <c r="A16" t="n">
+      <c r="A16" s="15" t="n">
         <v>3</v>
       </c>
+      <c r="B16" s="10" t="inlineStr"/>
+      <c r="C16" s="6" t="n"/>
+      <c r="D16" s="6" t="n"/>
+      <c r="E16" s="6" t="n"/>
+      <c r="F16" s="6" t="n"/>
+      <c r="G16" s="6" t="n"/>
+      <c r="H16" s="7" t="n"/>
     </row>
     <row r="17" ht="22" customHeight="1">
-      <c r="A17" t="n">
+      <c r="A17" s="15" t="n">
         <v>4</v>
       </c>
+      <c r="B17" s="10" t="inlineStr"/>
+      <c r="C17" s="6" t="n"/>
+      <c r="D17" s="6" t="n"/>
+      <c r="E17" s="6" t="n"/>
+      <c r="F17" s="6" t="n"/>
+      <c r="G17" s="6" t="n"/>
+      <c r="H17" s="7" t="n"/>
     </row>
     <row r="19" ht="24" customHeight="1">
-      <c r="A19" s="23" t="inlineStr">
-        <is>
-          <t>▼ 车缝工艺</t>
+      <c r="A19" s="3" t="inlineStr">
+        <is>
+          <t>▼ SKU 与面料</t>
         </is>
       </c>
       <c r="S19" s="16" t="n"/>
     </row>
     <row r="20" ht="20" customHeight="1">
-      <c r="A20" s="25" t="inlineStr">
-        <is>
-          <t>序号</t>
-        </is>
-      </c>
-      <c r="B20" s="25" t="inlineStr">
-        <is>
-          <t>工艺大类</t>
-        </is>
-      </c>
-      <c r="C20" s="25" t="inlineStr">
-        <is>
-          <t>工艺名称</t>
-        </is>
-      </c>
-      <c r="D20" s="25" t="inlineStr">
-        <is>
-          <t>制衣厂</t>
-        </is>
-      </c>
-      <c r="E20" s="25" t="inlineStr">
-        <is>
-          <t>单价</t>
+      <c r="A20" s="9" t="inlineStr">
+        <is>
+          <t>SKU编号</t>
+        </is>
+      </c>
+      <c r="B20" s="4" t="inlineStr">
+        <is>
+          <t>颜色</t>
+        </is>
+      </c>
+      <c r="C20" s="4" t="inlineStr">
+        <is>
+          <t>尺码</t>
+        </is>
+      </c>
+      <c r="D20" s="4" t="inlineStr">
+        <is>
+          <t>件数</t>
+        </is>
+      </c>
+      <c r="E20" s="17" t="inlineStr">
+        <is>
+          <t>布类</t>
         </is>
       </c>
       <c r="F20" s="4" t="inlineStr">
@@ -1592,9 +1622,7 @@
       <c r="R21" s="19" t="n"/>
     </row>
     <row r="22" ht="22" customHeight="1">
-      <c r="A22" s="15" t="n">
-        <v>2</v>
-      </c>
+      <c r="A22" s="15" t="inlineStr"/>
       <c r="B22" s="5" t="inlineStr"/>
       <c r="C22" s="5" t="inlineStr"/>
       <c r="D22" s="5" t="inlineStr"/>
@@ -1618,9 +1646,7 @@
       <c r="R22" s="19" t="n"/>
     </row>
     <row r="23" ht="22" customHeight="1">
-      <c r="A23" s="15" t="n">
-        <v>3</v>
-      </c>
+      <c r="A23" s="15" t="inlineStr"/>
       <c r="B23" s="5" t="inlineStr"/>
       <c r="C23" s="5" t="inlineStr"/>
       <c r="D23" s="5" t="inlineStr"/>
@@ -1640,9 +1666,7 @@
       <c r="R23" s="19" t="n"/>
     </row>
     <row r="24" ht="22" customHeight="1">
-      <c r="A24" s="15" t="n">
-        <v>4</v>
-      </c>
+      <c r="A24" s="15" t="inlineStr"/>
       <c r="B24" s="5" t="inlineStr"/>
       <c r="C24" s="5" t="inlineStr"/>
       <c r="D24" s="5" t="inlineStr"/>
@@ -1682,15 +1706,11 @@
       <c r="R25" s="19" t="n"/>
     </row>
     <row r="26" ht="22" customHeight="1">
-      <c r="A26" s="26" t="inlineStr">
-        <is>
-          <t>▼ 成衣工艺</t>
-        </is>
-      </c>
-      <c r="B26" s="6" t="n"/>
-      <c r="C26" s="6" t="n"/>
-      <c r="D26" s="6" t="n"/>
-      <c r="E26" s="7" t="n"/>
+      <c r="A26" s="15" t="inlineStr"/>
+      <c r="B26" s="5" t="inlineStr"/>
+      <c r="C26" s="5" t="inlineStr"/>
+      <c r="D26" s="5" t="inlineStr"/>
+      <c r="E26" s="15" t="inlineStr"/>
       <c r="F26" s="18" t="inlineStr"/>
       <c r="G26" s="18" t="inlineStr"/>
       <c r="H26" s="18" t="inlineStr"/>
@@ -1706,26 +1726,10 @@
       <c r="R26" s="19" t="n"/>
     </row>
     <row r="27" ht="22" customHeight="1">
-      <c r="A27" s="25" t="inlineStr">
-        <is>
-          <t>序号</t>
-        </is>
-      </c>
-      <c r="B27" s="27" t="inlineStr">
-        <is>
-          <t>工艺名称</t>
-        </is>
-      </c>
-      <c r="C27" s="27" t="inlineStr">
-        <is>
-          <t>制衣厂</t>
-        </is>
-      </c>
-      <c r="D27" s="27" t="inlineStr">
-        <is>
-          <t>单价</t>
-        </is>
-      </c>
+      <c r="A27" s="15" t="inlineStr"/>
+      <c r="B27" s="5" t="inlineStr"/>
+      <c r="C27" s="5" t="n"/>
+      <c r="D27" s="5" t="inlineStr"/>
       <c r="E27" s="15" t="inlineStr"/>
       <c r="F27" s="18" t="inlineStr"/>
       <c r="G27" s="18" t="inlineStr"/>
@@ -1742,9 +1746,7 @@
       <c r="R27" s="19" t="n"/>
     </row>
     <row r="28" ht="22" customHeight="1">
-      <c r="A28" s="15" t="n">
-        <v>1</v>
-      </c>
+      <c r="A28" s="15" t="inlineStr"/>
       <c r="B28" s="5" t="inlineStr"/>
       <c r="C28" s="5" t="inlineStr"/>
       <c r="D28" s="5" t="inlineStr"/>
@@ -1763,19 +1765,18 @@
       <c r="Q28" s="19" t="n"/>
       <c r="R28" s="19" t="n"/>
     </row>
-    <row r="29">
-      <c r="A29" t="n">
-        <v>2</v>
-      </c>
-    </row>
     <row r="30" ht="24" customHeight="1">
-      <c r="A30" s="3" t="n">
-        <v>3</v>
+      <c r="A30" s="3" t="inlineStr">
+        <is>
+          <t>▼ 辅料信息</t>
+        </is>
       </c>
     </row>
     <row r="31" ht="14.25" customHeight="1">
-      <c r="A31" s="20" t="n">
-        <v>4</v>
+      <c r="A31" s="20" t="inlineStr">
+        <is>
+          <t>序号</t>
+        </is>
       </c>
       <c r="B31" s="20" t="inlineStr">
         <is>
@@ -2026,25 +2027,29 @@
       <c r="L43" s="22" t="inlineStr"/>
     </row>
   </sheetData>
-  <mergeCells count="16">
+  <mergeCells count="20">
+    <mergeCell ref="B15:H15"/>
     <mergeCell ref="A1:H1"/>
     <mergeCell ref="B10:D10"/>
     <mergeCell ref="B9:D9"/>
+    <mergeCell ref="B16:H16"/>
     <mergeCell ref="F9:H9"/>
     <mergeCell ref="B6:D6"/>
+    <mergeCell ref="A12:H12"/>
     <mergeCell ref="A3:H3"/>
-    <mergeCell ref="A12:E12"/>
-    <mergeCell ref="A26:E26"/>
     <mergeCell ref="A19:R19"/>
     <mergeCell ref="A5:H5"/>
     <mergeCell ref="B7:D7"/>
     <mergeCell ref="A30:L30"/>
     <mergeCell ref="B8:H8"/>
     <mergeCell ref="F10:H10"/>
+    <mergeCell ref="B14:H14"/>
     <mergeCell ref="F6:H6"/>
+    <mergeCell ref="B17:H17"/>
+    <mergeCell ref="B13:H13"/>
     <mergeCell ref="F7:H7"/>
   </mergeCells>
-  <dataValidations count="17">
+  <dataValidations count="7">
     <dataValidation sqref="F6" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="0" type="list">
       <formula1>"OEM,ODM,OBM"</formula1>
     </dataValidation>
@@ -2063,38 +2068,8 @@
     <dataValidation sqref="I21:I28" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="输入错误" error="请选择是或否" type="list">
       <formula1>"是,否"</formula1>
     </dataValidation>
-    <dataValidation sqref="B14 B15 B16 B17" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="无效选择" error="请选择工艺制作的工艺大类" promptTitle="工艺大类" prompt="点击选择工艺制作的工艺大类" type="list">
-      <formula1>工艺数据库!$A$2:$A$6</formula1>
-    </dataValidation>
-    <dataValidation sqref="C14" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="无效" error="请先选择大类，再选择工艺制作" promptTitle="工艺名称" prompt="先选大类，再选工艺制作名称" type="list">
-      <formula1>=INDIRECT("'cat_make_'"&amp;SUBSTITUTE($B14,"/","_"))</formula1>
-    </dataValidation>
-    <dataValidation sqref="C15" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="无效" error="请先选择大类，再选择工艺制作" promptTitle="工艺名称" prompt="先选大类，再选工艺制作名称" type="list">
-      <formula1>=INDIRECT("'cat_make_'"&amp;SUBSTITUTE($B15,"/","_"))</formula1>
-    </dataValidation>
-    <dataValidation sqref="C16" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="无效" error="请先选择大类，再选择工艺制作" promptTitle="工艺名称" prompt="先选大类，再选工艺制作名称" type="list">
-      <formula1>=INDIRECT("'cat_make_'"&amp;SUBSTITUTE($B16,"/","_"))</formula1>
-    </dataValidation>
-    <dataValidation sqref="C17" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="无效" error="请先选择大类，再选择工艺制作" promptTitle="工艺名称" prompt="先选大类，再选工艺制作名称" type="list">
-      <formula1>=INDIRECT("'cat_make_'"&amp;SUBSTITUTE($B17,"/","_"))</formula1>
-    </dataValidation>
-    <dataValidation sqref="B21 B22 B23 B24" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="无效选择" error="请选择车缝工艺的工艺大类" promptTitle="工艺大类" prompt="点击选择车缝工艺的工艺大类" type="list">
-      <formula1>工艺数据库!$A$11:$A$15</formula1>
-    </dataValidation>
-    <dataValidation sqref="C21" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="无效" error="请先选择大类，再选择车缝工艺" promptTitle="工艺名称" prompt="先选大类，再选车缝工艺名称" type="list">
-      <formula1>=INDIRECT("'cat_sew_'"&amp;SUBSTITUTE($B21,"/","_"))</formula1>
-    </dataValidation>
-    <dataValidation sqref="C22" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="无效" error="请先选择大类，再选择车缝工艺" promptTitle="工艺名称" prompt="先选大类，再选车缝工艺名称" type="list">
-      <formula1>=INDIRECT("'cat_sew_'"&amp;SUBSTITUTE($B22,"/","_"))</formula1>
-    </dataValidation>
-    <dataValidation sqref="C23" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="无效" error="请先选择大类，再选择车缝工艺" promptTitle="工艺名称" prompt="先选大类，再选车缝工艺名称" type="list">
-      <formula1>=INDIRECT("'cat_sew_'"&amp;SUBSTITUTE($B23,"/","_"))</formula1>
-    </dataValidation>
-    <dataValidation sqref="C24" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="无效" error="请先选择大类，再选择车缝工艺" promptTitle="工艺名称" prompt="先选大类，再选车缝工艺名称" type="list">
-      <formula1>=INDIRECT("'cat_sew_'"&amp;SUBSTITUTE($B24,"/","_"))</formula1>
-    </dataValidation>
-    <dataValidation sqref="B28 B29 B30 B31" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="无效" error="请选择成衣工艺" promptTitle="成衣工艺" prompt="点击选择成衣工艺" type="list">
-      <formula1>工艺数据库!$A$30:$A$47</formula1>
+    <dataValidation sqref="B14 B15 B16 B17" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="无效" error="请选择工艺项目" promptTitle="工艺制作" prompt="从系统工艺库中选择" type="list">
+      <formula1>工艺数据库!$A$66:$A$132</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -2107,686 +2082,1306 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F47"/>
+  <dimension ref="A1:E132"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="26" customWidth="1" min="1" max="1"/>
+    <col width="22" customWidth="1" min="2" max="2"/>
+    <col width="22" customWidth="1" min="3" max="3"/>
+    <col width="22" customWidth="1" min="4" max="4"/>
+    <col width="22" customWidth="1" min="5" max="5"/>
+  </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
-        <is>
-          <t>工艺制作-大类</t>
-        </is>
-      </c>
-      <c r="B1" t="inlineStr">
+      <c r="A1" s="23" t="inlineStr">
+        <is>
+          <t>工艺制作（弹窗一级/二级菜单）</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="24" t="inlineStr">
         <is>
           <t>洗水</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="B2" s="24" t="inlineStr">
         <is>
           <t>热转压印</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="C2" s="24" t="inlineStr">
         <is>
           <t>直喷印花</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="D2" s="24" t="inlineStr">
         <is>
           <t>绣花</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="E2" s="24" t="inlineStr">
         <is>
           <t>网板印花</t>
         </is>
       </c>
     </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
+    <row r="3">
+      <c r="A3" s="25" t="inlineStr">
+        <is>
+          <t>吊染</t>
+        </is>
+      </c>
+      <c r="B3" s="25" t="inlineStr">
+        <is>
+          <t>丝印刻字膜烫标</t>
+        </is>
+      </c>
+      <c r="C3" s="25" t="inlineStr">
+        <is>
+          <t>数码直喷/不打底</t>
+        </is>
+      </c>
+      <c r="D3" s="25" t="inlineStr">
+        <is>
+          <t>V字针绣</t>
+        </is>
+      </c>
+      <c r="E3" s="25" t="inlineStr">
+        <is>
+          <t>仿拨印</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="25" t="inlineStr">
+        <is>
+          <t>喷色</t>
+        </is>
+      </c>
+      <c r="B4" s="25" t="inlineStr">
+        <is>
+          <t>丝印烫标（加防升华）</t>
+        </is>
+      </c>
+      <c r="C4" s="25" t="inlineStr">
+        <is>
+          <t>数码直喷/打底</t>
+        </is>
+      </c>
+      <c r="D4" s="25" t="inlineStr">
+        <is>
+          <t>一字绣（特种专机）</t>
+        </is>
+      </c>
+      <c r="E4" s="25" t="inlineStr">
+        <is>
+          <t>光感印</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="25" t="inlineStr">
+        <is>
+          <t>喷马骝</t>
+        </is>
+      </c>
+      <c r="B5" s="25" t="inlineStr">
+        <is>
+          <t>刻字膜</t>
+        </is>
+      </c>
+      <c r="C5" s="25" t="inlineStr">
+        <is>
+          <t>热转印/热升华</t>
+        </is>
+      </c>
+      <c r="D5" s="25" t="inlineStr">
+        <is>
+          <t>中空绣</t>
+        </is>
+      </c>
+      <c r="E5" s="25" t="inlineStr">
+        <is>
+          <t>厚板印</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="25" t="inlineStr">
+        <is>
+          <t>手擦</t>
+        </is>
+      </c>
+      <c r="B6" s="25" t="inlineStr">
+        <is>
+          <t>压褶</t>
+        </is>
+      </c>
+      <c r="C6" s="25" t="inlineStr">
+        <is>
+          <t>白墨直喷/不打底</t>
+        </is>
+      </c>
+      <c r="D6" s="25" t="inlineStr">
+        <is>
+          <t>人字车</t>
+        </is>
+      </c>
+      <c r="E6" s="25" t="inlineStr">
+        <is>
+          <t>反光浆</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="25" t="inlineStr">
+        <is>
+          <t>扎染</t>
+        </is>
+      </c>
+      <c r="B7" s="25" t="inlineStr">
+        <is>
+          <t>厚版肤感弹力硅胶章</t>
+        </is>
+      </c>
+      <c r="C7" s="25" t="inlineStr">
+        <is>
+          <t>白墨直喷/打底</t>
+        </is>
+      </c>
+      <c r="D7" s="25" t="inlineStr">
+        <is>
+          <t>充棉工艺</t>
+        </is>
+      </c>
+      <c r="E7" s="25" t="inlineStr">
+        <is>
+          <t>发泡印</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="25" t="inlineStr">
+        <is>
+          <t>炒盐</t>
+        </is>
+      </c>
+      <c r="B8" s="25" t="inlineStr">
+        <is>
+          <t>反光刻字膜</t>
+        </is>
+      </c>
+      <c r="C8" s="25" t="inlineStr"/>
+      <c r="D8" s="25" t="inlineStr">
+        <is>
+          <t>包边绣</t>
+        </is>
+      </c>
+      <c r="E8" s="25" t="inlineStr">
+        <is>
+          <t>哑光胶浆</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="25" t="inlineStr">
+        <is>
+          <t>炒色</t>
+        </is>
+      </c>
+      <c r="B9" s="25" t="inlineStr">
+        <is>
+          <t>激光冲孔</t>
+        </is>
+      </c>
+      <c r="C9" s="25" t="inlineStr"/>
+      <c r="D9" s="25" t="inlineStr">
+        <is>
+          <t>十字绣</t>
+        </is>
+      </c>
+      <c r="E9" s="25" t="inlineStr">
+        <is>
+          <t>彩色硅胶印</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="25" t="inlineStr">
+        <is>
+          <t>炒雪花</t>
+        </is>
+      </c>
+      <c r="B10" s="25" t="inlineStr">
+        <is>
+          <t>烫画</t>
+        </is>
+      </c>
+      <c r="C10" s="25" t="inlineStr"/>
+      <c r="D10" s="25" t="inlineStr">
+        <is>
+          <t>平绣</t>
+        </is>
+      </c>
+      <c r="E10" s="25" t="inlineStr">
+        <is>
+          <t>拉浆/石头浆</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="25" t="inlineStr">
+        <is>
+          <t>砂洗</t>
+        </is>
+      </c>
+      <c r="B11" s="25" t="inlineStr">
+        <is>
+          <t>热转印</t>
+        </is>
+      </c>
+      <c r="C11" s="25" t="inlineStr"/>
+      <c r="D11" s="25" t="inlineStr">
+        <is>
+          <t>挨针绣</t>
+        </is>
+      </c>
+      <c r="E11" s="25" t="inlineStr">
+        <is>
+          <t>拨印</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="25" t="inlineStr">
+        <is>
+          <t>碧纹染</t>
+        </is>
+      </c>
+      <c r="B12" s="25" t="inlineStr">
+        <is>
+          <t>立体钢印</t>
+        </is>
+      </c>
+      <c r="C12" s="25" t="inlineStr"/>
+      <c r="D12" s="25" t="inlineStr">
+        <is>
+          <t>明星特种专机-207</t>
+        </is>
+      </c>
+      <c r="E12" s="25" t="inlineStr">
+        <is>
+          <t>植绒印花</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="25" t="inlineStr">
+        <is>
+          <t>酵洗</t>
+        </is>
+      </c>
+      <c r="B13" s="25" t="inlineStr">
+        <is>
+          <t>高周波</t>
+        </is>
+      </c>
+      <c r="C13" s="25" t="inlineStr"/>
+      <c r="D13" s="25" t="inlineStr">
+        <is>
+          <t>榻榻米绣</t>
+        </is>
+      </c>
+      <c r="E13" s="25" t="inlineStr">
+        <is>
+          <t>水显印</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="25" t="inlineStr"/>
+      <c r="B14" s="25" t="inlineStr"/>
+      <c r="C14" s="25" t="inlineStr"/>
+      <c r="D14" s="25" t="inlineStr">
+        <is>
+          <t>毛巾绣</t>
+        </is>
+      </c>
+      <c r="E14" s="25" t="inlineStr">
+        <is>
+          <t>水浆</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="25" t="inlineStr"/>
+      <c r="B15" s="25" t="inlineStr"/>
+      <c r="C15" s="25" t="inlineStr"/>
+      <c r="D15" s="25" t="inlineStr">
+        <is>
+          <t>牙刷绣</t>
+        </is>
+      </c>
+      <c r="E15" s="25" t="inlineStr">
+        <is>
+          <t>活性印花</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="25" t="inlineStr"/>
+      <c r="B16" s="25" t="inlineStr"/>
+      <c r="C16" s="25" t="inlineStr"/>
+      <c r="D16" s="25" t="inlineStr">
+        <is>
+          <t>珠片绣</t>
+        </is>
+      </c>
+      <c r="E16" s="25" t="inlineStr">
+        <is>
+          <t>温变印</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="25" t="inlineStr"/>
+      <c r="B17" s="25" t="inlineStr"/>
+      <c r="C17" s="25" t="inlineStr"/>
+      <c r="D17" s="25" t="inlineStr">
+        <is>
+          <t>立体绣</t>
+        </is>
+      </c>
+      <c r="E17" s="25" t="inlineStr">
+        <is>
+          <t>烫金/烫银</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="25" t="inlineStr"/>
+      <c r="B18" s="25" t="inlineStr"/>
+      <c r="C18" s="25" t="inlineStr"/>
+      <c r="D18" s="25" t="inlineStr">
+        <is>
+          <t>绳绣</t>
+        </is>
+      </c>
+      <c r="E18" s="25" t="inlineStr">
+        <is>
+          <t>热固油墨</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="25" t="inlineStr"/>
+      <c r="B19" s="25" t="inlineStr"/>
+      <c r="C19" s="25" t="inlineStr"/>
+      <c r="D19" s="25" t="inlineStr">
+        <is>
+          <t>菱形打边绣（特种专机）</t>
+        </is>
+      </c>
+      <c r="E19" s="25" t="inlineStr">
+        <is>
+          <t>硅胶印</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="25" t="inlineStr"/>
+      <c r="B20" s="25" t="inlineStr"/>
+      <c r="C20" s="25" t="inlineStr"/>
+      <c r="D20" s="25" t="inlineStr">
+        <is>
+          <t>贴布绣</t>
+        </is>
+      </c>
+      <c r="E20" s="25" t="inlineStr">
+        <is>
+          <t>网点印</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="25" t="inlineStr"/>
+      <c r="B21" s="25" t="inlineStr"/>
+      <c r="C21" s="25" t="inlineStr"/>
+      <c r="D21" s="25" t="inlineStr">
+        <is>
+          <t>锁链绣</t>
+        </is>
+      </c>
+      <c r="E21" s="25" t="inlineStr">
+        <is>
+          <t>裂纹印</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="25" t="inlineStr"/>
+      <c r="B22" s="25" t="inlineStr"/>
+      <c r="C22" s="25" t="inlineStr"/>
+      <c r="D22" s="25" t="inlineStr">
+        <is>
+          <t>镂空绣</t>
+        </is>
+      </c>
+      <c r="E22" s="25" t="inlineStr">
+        <is>
+          <t>轻薄热固油墨</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="26" t="inlineStr">
+        <is>
+          <t>车缝工艺（弹窗一级/二级菜单）</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="24" t="inlineStr">
+        <is>
+          <t>无缝</t>
+        </is>
+      </c>
+      <c r="B26" s="24" t="inlineStr">
         <is>
           <t>洗水</t>
         </is>
       </c>
-      <c r="B2" t="inlineStr">
+      <c r="C26" s="24" t="inlineStr">
+        <is>
+          <t>热转压印</t>
+        </is>
+      </c>
+      <c r="D26" s="24" t="inlineStr">
+        <is>
+          <t>绣花</t>
+        </is>
+      </c>
+      <c r="E26" s="24" t="inlineStr">
+        <is>
+          <t>网板印花</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="25" t="inlineStr">
+        <is>
+          <t>无缝压胶</t>
+        </is>
+      </c>
+      <c r="B27" s="25" t="inlineStr">
         <is>
           <t>吊染</t>
         </is>
       </c>
-      <c r="C2" t="inlineStr">
+      <c r="C27" s="25" t="inlineStr">
+        <is>
+          <t>成衣刻字膜</t>
+        </is>
+      </c>
+      <c r="D27" s="25" t="inlineStr">
+        <is>
+          <t>背胶章仔绣</t>
+        </is>
+      </c>
+      <c r="E27" s="25" t="inlineStr">
+        <is>
+          <t>丝印烫标</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="25" t="inlineStr"/>
+      <c r="B28" s="25" t="inlineStr">
+        <is>
+          <t>喷色</t>
+        </is>
+      </c>
+      <c r="C28" s="25" t="inlineStr">
+        <is>
+          <t>高弹肤感硅胶</t>
+        </is>
+      </c>
+      <c r="D28" s="25" t="inlineStr"/>
+      <c r="E28" s="25" t="inlineStr"/>
+    </row>
+    <row r="29">
+      <c r="A29" s="25" t="inlineStr"/>
+      <c r="B29" s="25" t="inlineStr">
+        <is>
+          <t>喷马骝</t>
+        </is>
+      </c>
+      <c r="C29" s="25" t="inlineStr"/>
+      <c r="D29" s="25" t="inlineStr"/>
+      <c r="E29" s="25" t="inlineStr"/>
+    </row>
+    <row r="30">
+      <c r="A30" s="25" t="inlineStr"/>
+      <c r="B30" s="25" t="inlineStr">
+        <is>
+          <t>手擦</t>
+        </is>
+      </c>
+      <c r="C30" s="25" t="inlineStr"/>
+      <c r="D30" s="25" t="inlineStr"/>
+      <c r="E30" s="25" t="inlineStr"/>
+    </row>
+    <row r="31">
+      <c r="A31" s="25" t="inlineStr"/>
+      <c r="B31" s="25" t="inlineStr">
+        <is>
+          <t>扎染</t>
+        </is>
+      </c>
+      <c r="C31" s="25" t="inlineStr"/>
+      <c r="D31" s="25" t="inlineStr"/>
+      <c r="E31" s="25" t="inlineStr"/>
+    </row>
+    <row r="32">
+      <c r="A32" s="25" t="inlineStr"/>
+      <c r="B32" s="25" t="inlineStr">
+        <is>
+          <t>普洗</t>
+        </is>
+      </c>
+      <c r="C32" s="25" t="inlineStr"/>
+      <c r="D32" s="25" t="inlineStr"/>
+      <c r="E32" s="25" t="inlineStr"/>
+    </row>
+    <row r="33">
+      <c r="A33" s="25" t="inlineStr"/>
+      <c r="B33" s="25" t="inlineStr">
+        <is>
+          <t>水床冲孔</t>
+        </is>
+      </c>
+      <c r="C33" s="25" t="inlineStr"/>
+      <c r="D33" s="25" t="inlineStr"/>
+      <c r="E33" s="25" t="inlineStr"/>
+    </row>
+    <row r="34">
+      <c r="A34" s="25" t="inlineStr"/>
+      <c r="B34" s="25" t="inlineStr">
+        <is>
+          <t>激光烧花</t>
+        </is>
+      </c>
+      <c r="C34" s="25" t="inlineStr"/>
+      <c r="D34" s="25" t="inlineStr"/>
+      <c r="E34" s="25" t="inlineStr"/>
+    </row>
+    <row r="35">
+      <c r="A35" s="25" t="inlineStr"/>
+      <c r="B35" s="25" t="inlineStr">
+        <is>
+          <t>炒盐</t>
+        </is>
+      </c>
+      <c r="C35" s="25" t="inlineStr"/>
+      <c r="D35" s="25" t="inlineStr"/>
+      <c r="E35" s="25" t="inlineStr"/>
+    </row>
+    <row r="36">
+      <c r="A36" s="25" t="inlineStr"/>
+      <c r="B36" s="25" t="inlineStr">
+        <is>
+          <t>炒色</t>
+        </is>
+      </c>
+      <c r="C36" s="25" t="inlineStr"/>
+      <c r="D36" s="25" t="inlineStr"/>
+      <c r="E36" s="25" t="inlineStr"/>
+    </row>
+    <row r="37">
+      <c r="A37" s="25" t="inlineStr"/>
+      <c r="B37" s="25" t="inlineStr">
+        <is>
+          <t>炒雪花</t>
+        </is>
+      </c>
+      <c r="C37" s="25" t="inlineStr"/>
+      <c r="D37" s="25" t="inlineStr"/>
+      <c r="E37" s="25" t="inlineStr"/>
+    </row>
+    <row r="38">
+      <c r="A38" s="25" t="inlineStr"/>
+      <c r="B38" s="25" t="inlineStr">
+        <is>
+          <t>砂洗</t>
+        </is>
+      </c>
+      <c r="C38" s="25" t="inlineStr"/>
+      <c r="D38" s="25" t="inlineStr"/>
+      <c r="E38" s="25" t="inlineStr"/>
+    </row>
+    <row r="39">
+      <c r="A39" s="25" t="inlineStr"/>
+      <c r="B39" s="25" t="inlineStr">
+        <is>
+          <t>破坏</t>
+        </is>
+      </c>
+      <c r="C39" s="25" t="inlineStr"/>
+      <c r="D39" s="25" t="inlineStr"/>
+      <c r="E39" s="25" t="inlineStr"/>
+    </row>
+    <row r="40">
+      <c r="A40" s="25" t="inlineStr"/>
+      <c r="B40" s="25" t="inlineStr">
+        <is>
+          <t>酵洗</t>
+        </is>
+      </c>
+      <c r="C40" s="25" t="inlineStr"/>
+      <c r="D40" s="25" t="inlineStr"/>
+      <c r="E40" s="25" t="inlineStr"/>
+    </row>
+    <row r="43">
+      <c r="A43" s="26" t="inlineStr">
+        <is>
+          <t>成衣工艺（无分类）</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="25" t="inlineStr">
+        <is>
+          <t>0.2边线</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="25" t="inlineStr">
+        <is>
+          <t>0.5单线</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="25" t="inlineStr">
+        <is>
+          <t>2号反底</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="25" t="inlineStr">
+        <is>
+          <t>三针五线大哈苏</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="25" t="inlineStr">
+        <is>
+          <t>三针四线</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="25" t="inlineStr">
+        <is>
+          <t>两针四线大哈苏</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="25" t="inlineStr">
+        <is>
+          <t>分中坎</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="25" t="inlineStr">
+        <is>
+          <t>压胶</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="25" t="inlineStr">
+        <is>
+          <t>哨牙线</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="25" t="inlineStr">
+        <is>
+          <t>坎双线</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="25" t="inlineStr">
+        <is>
+          <t>小两针四线小哈苏</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="25" t="inlineStr">
+        <is>
+          <t>小分中坎</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="25" t="inlineStr">
+        <is>
+          <t>小双线（窄针）</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="25" t="inlineStr">
+        <is>
+          <t>峰哥工艺线（高弹丝）</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="25" t="inlineStr">
+        <is>
+          <t>来去缝</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" s="25" t="inlineStr">
+        <is>
+          <t>牙签线</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" s="25" t="inlineStr">
+        <is>
+          <t>落行窄针小双线</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" s="25" t="inlineStr">
+        <is>
+          <t>龅牙线</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" s="27" t="inlineStr">
+        <is>
+          <t>全部工艺名称（供Sheet1下拉）</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>V字针绣</t>
+        </is>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>洗水</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>一字绣（特种专机）</t>
+        </is>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>热转压印</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
         <is>
           <t>丝印刻字膜烫标</t>
         </is>
       </c>
-      <c r="D2" t="inlineStr">
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>直喷印花</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>丝印烫标（加防升华）</t>
+        </is>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>绣花</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>中空绣</t>
+        </is>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>网板印花</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>人字车</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>仿拨印</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>充棉工艺</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>光感印</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>刻字膜</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>包边绣</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>十字绣</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>压褶</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="inlineStr">
+        <is>
+          <t>厚板印</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="inlineStr">
+        <is>
+          <t>厚版肤感弹力硅胶章</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="inlineStr">
+        <is>
+          <t>反光刻字膜</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="inlineStr">
+        <is>
+          <t>反光浆</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="inlineStr">
+        <is>
+          <t>发泡印</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="inlineStr">
+        <is>
+          <t>吊染</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="inlineStr">
+        <is>
+          <t>哑光胶浆</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="inlineStr">
+        <is>
+          <t>喷色</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="inlineStr">
+        <is>
+          <t>喷马骝</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="inlineStr">
+        <is>
+          <t>平绣</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="inlineStr">
+        <is>
+          <t>彩色硅胶印</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="inlineStr">
+        <is>
+          <t>手擦</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="inlineStr">
+        <is>
+          <t>扎染</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="inlineStr">
+        <is>
+          <t>拉浆/石头浆</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="inlineStr">
+        <is>
+          <t>拨印</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="inlineStr">
+        <is>
+          <t>挨针绣</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="inlineStr">
         <is>
           <t>数码直喷/不打底</t>
         </is>
       </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>V字针绣</t>
-        </is>
-      </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>仿拨印</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>热转压印</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>喷色</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>丝印烫标（加防升华）</t>
-        </is>
-      </c>
-      <c r="D3" t="inlineStr">
+    </row>
+    <row r="96">
+      <c r="A96" t="inlineStr">
         <is>
           <t>数码直喷/打底</t>
         </is>
       </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>一字绣（特种专机）</t>
-        </is>
-      </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>光感印</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>直喷印花</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>喷马骝</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>刻字膜</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr">
+    </row>
+    <row r="97">
+      <c r="A97" t="inlineStr">
+        <is>
+          <t>明星特种专机-207</t>
+        </is>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" t="inlineStr">
+        <is>
+          <t>植绒印花</t>
+        </is>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" t="inlineStr">
+        <is>
+          <t>榻榻米绣</t>
+        </is>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" t="inlineStr">
+        <is>
+          <t>毛巾绣</t>
+        </is>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" t="inlineStr">
+        <is>
+          <t>水显印</t>
+        </is>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" t="inlineStr">
+        <is>
+          <t>水浆</t>
+        </is>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" t="inlineStr">
+        <is>
+          <t>活性印花</t>
+        </is>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" t="inlineStr">
+        <is>
+          <t>温变印</t>
+        </is>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" t="inlineStr">
+        <is>
+          <t>激光冲孔</t>
+        </is>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" t="inlineStr">
+        <is>
+          <t>炒盐</t>
+        </is>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" t="inlineStr">
+        <is>
+          <t>炒色</t>
+        </is>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" t="inlineStr">
+        <is>
+          <t>炒雪花</t>
+        </is>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" t="inlineStr">
+        <is>
+          <t>烫画</t>
+        </is>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" t="inlineStr">
+        <is>
+          <t>烫金/烫银</t>
+        </is>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" t="inlineStr">
+        <is>
+          <t>热固油墨</t>
+        </is>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" t="inlineStr">
+        <is>
+          <t>热转印</t>
+        </is>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" t="inlineStr">
         <is>
           <t>热转印/热升华</t>
         </is>
       </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>中空绣</t>
-        </is>
-      </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>厚板印</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>绣花</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>手擦</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>压褶</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr">
+    </row>
+    <row r="114">
+      <c r="A114" t="inlineStr">
+        <is>
+          <t>牙刷绣</t>
+        </is>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" t="inlineStr">
+        <is>
+          <t>珠片绣</t>
+        </is>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" t="inlineStr">
         <is>
           <t>白墨直喷/不打底</t>
         </is>
       </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>人字车</t>
-        </is>
-      </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>反光浆</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>网板印花</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>扎染</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>厚版肤感弹力硅胶章</t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr">
+    </row>
+    <row r="117">
+      <c r="A117" t="inlineStr">
         <is>
           <t>白墨直喷/打底</t>
         </is>
       </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>充棉工艺</t>
-        </is>
-      </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t>发泡印</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>炒盐</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>反光刻字膜</t>
-        </is>
-      </c>
-      <c r="E7" t="inlineStr">
-        <is>
-          <t>包边绣</t>
-        </is>
-      </c>
-      <c r="F7" t="inlineStr">
-        <is>
-          <t>哑光胶浆</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>炒色</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>激光冲孔</t>
-        </is>
-      </c>
-      <c r="E8" t="inlineStr">
-        <is>
-          <t>十字绣</t>
-        </is>
-      </c>
-      <c r="F8" t="inlineStr">
-        <is>
-          <t>彩色硅胶印</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>炒雪花</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>烫画</t>
-        </is>
-      </c>
-      <c r="E9" t="inlineStr">
-        <is>
-          <t>平绣</t>
-        </is>
-      </c>
-      <c r="F9" t="inlineStr">
-        <is>
-          <t>拉浆/石头浆</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>车缝工艺-大类</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>无缝</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>洗水</t>
-        </is>
-      </c>
-      <c r="D10" t="inlineStr">
-        <is>
-          <t>热转压印</t>
-        </is>
-      </c>
-      <c r="E10" t="inlineStr">
-        <is>
-          <t>绣花</t>
-        </is>
-      </c>
-      <c r="F10" t="inlineStr">
-        <is>
-          <t>网板印花</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>无缝</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>无缝压胶</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>吊染</t>
-        </is>
-      </c>
-      <c r="D11" t="inlineStr">
-        <is>
-          <t>成衣刻字膜</t>
-        </is>
-      </c>
-      <c r="E11" t="inlineStr">
-        <is>
-          <t>背胶章仔绣</t>
-        </is>
-      </c>
-      <c r="F11" t="inlineStr">
-        <is>
-          <t>丝印烫标</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>洗水</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
+    </row>
+    <row r="118">
+      <c r="A118" t="inlineStr">
+        <is>
+          <t>砂洗</t>
+        </is>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" t="inlineStr">
+        <is>
+          <t>硅胶印</t>
+        </is>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" t="inlineStr">
+        <is>
+          <t>碧纹染</t>
+        </is>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" t="inlineStr">
+        <is>
+          <t>立体绣</t>
+        </is>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" t="inlineStr">
+        <is>
+          <t>立体钢印</t>
+        </is>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" t="inlineStr">
+        <is>
+          <t>绳绣</t>
+        </is>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" t="inlineStr">
+        <is>
+          <t>网点印</t>
+        </is>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" t="inlineStr">
+        <is>
+          <t>菱形打边绣（特种专机）</t>
+        </is>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" t="inlineStr">
+        <is>
+          <t>裂纹印</t>
+        </is>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" t="inlineStr">
+        <is>
+          <t>贴布绣</t>
+        </is>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" t="inlineStr">
+        <is>
+          <t>轻薄热固油墨</t>
+        </is>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" t="inlineStr">
         <is>
           <t>酵洗</t>
         </is>
       </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>喷色</t>
-        </is>
-      </c>
-      <c r="D12" t="inlineStr">
-        <is>
-          <t>高弹肤感硅胶</t>
-        </is>
-      </c>
-      <c r="E12" t="inlineStr">
-        <is>
-          <t>榻榻米绣</t>
-        </is>
-      </c>
-      <c r="F12" t="inlineStr">
-        <is>
-          <t>水显印</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>热转压印</t>
-        </is>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>喷马骝</t>
-        </is>
-      </c>
-      <c r="E13" t="inlineStr">
-        <is>
-          <t>毛巾绣</t>
-        </is>
-      </c>
-      <c r="F13" t="inlineStr">
-        <is>
-          <t>水浆</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>绣花</t>
-        </is>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>手擦</t>
-        </is>
-      </c>
-      <c r="E14" t="inlineStr">
-        <is>
-          <t>牙刷绣</t>
-        </is>
-      </c>
-      <c r="F14" t="inlineStr">
-        <is>
-          <t>活性印花</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>网板印花</t>
-        </is>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>扎染</t>
-        </is>
-      </c>
-      <c r="E15" t="inlineStr">
-        <is>
-          <t>珠片绣</t>
-        </is>
-      </c>
-      <c r="F15" t="inlineStr">
-        <is>
-          <t>温变印</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>普洗</t>
-        </is>
-      </c>
-      <c r="E16" t="inlineStr">
-        <is>
-          <t>立体绣</t>
-        </is>
-      </c>
-      <c r="F16" t="inlineStr">
-        <is>
-          <t>烫金/烫银</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>水床冲孔</t>
-        </is>
-      </c>
-      <c r="E17" t="inlineStr">
-        <is>
-          <t>绳绣</t>
-        </is>
-      </c>
-      <c r="F17" t="inlineStr">
-        <is>
-          <t>热固油墨</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>激光烧花</t>
-        </is>
-      </c>
-      <c r="E18" t="inlineStr">
-        <is>
-          <t>菱形打边绣（特种专机）</t>
-        </is>
-      </c>
-      <c r="F18" t="inlineStr">
-        <is>
-          <t>硅胶印</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>炒盐</t>
-        </is>
-      </c>
-      <c r="E19" t="inlineStr">
-        <is>
-          <t>贴布绣</t>
-        </is>
-      </c>
-      <c r="F19" t="inlineStr">
-        <is>
-          <t>网点印</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>炒色</t>
-        </is>
-      </c>
-      <c r="E20" t="inlineStr">
+    </row>
+    <row r="130">
+      <c r="A130" t="inlineStr">
         <is>
           <t>锁链绣</t>
         </is>
       </c>
-      <c r="F20" t="inlineStr">
-        <is>
-          <t>裂纹印</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>炒雪花</t>
-        </is>
-      </c>
-      <c r="E21" t="inlineStr">
+    </row>
+    <row r="131">
+      <c r="A131" t="inlineStr">
         <is>
           <t>镂空绣</t>
         </is>
       </c>
-      <c r="F21" t="inlineStr">
-        <is>
-          <t>轻薄热固油墨</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>砂洗</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>破坏</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>酵洗</t>
-        </is>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" t="inlineStr">
-        <is>
-          <t>成衣工艺</t>
-        </is>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" t="inlineStr">
-        <is>
-          <t>0.2边线</t>
-        </is>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" t="inlineStr">
-        <is>
-          <t>0.5单线</t>
-        </is>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" t="inlineStr">
-        <is>
-          <t>2号反底</t>
-        </is>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" t="inlineStr">
-        <is>
-          <t>三针五线大哈苏</t>
-        </is>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" t="inlineStr">
-        <is>
-          <t>三针四线</t>
-        </is>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" t="inlineStr">
-        <is>
-          <t>两针四线大哈苏</t>
-        </is>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" t="inlineStr">
-        <is>
-          <t>分中坎</t>
-        </is>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" t="inlineStr">
-        <is>
-          <t>压胶</t>
-        </is>
-      </c>
-    </row>
-    <row r="38">
-      <c r="A38" t="inlineStr">
-        <is>
-          <t>哨牙线</t>
-        </is>
-      </c>
-    </row>
-    <row r="39">
-      <c r="A39" t="inlineStr">
-        <is>
-          <t>坎双线</t>
-        </is>
-      </c>
-    </row>
-    <row r="40">
-      <c r="A40" t="inlineStr">
-        <is>
-          <t>小两针四线小哈苏</t>
-        </is>
-      </c>
-    </row>
-    <row r="41">
-      <c r="A41" t="inlineStr">
-        <is>
-          <t>小分中坎</t>
-        </is>
-      </c>
-    </row>
-    <row r="42">
-      <c r="A42" t="inlineStr">
-        <is>
-          <t>小双线（窄针）</t>
-        </is>
-      </c>
-    </row>
-    <row r="43">
-      <c r="A43" t="inlineStr">
-        <is>
-          <t>峰哥工艺线（高弹丝）</t>
-        </is>
-      </c>
-    </row>
-    <row r="44">
-      <c r="A44" t="inlineStr">
-        <is>
-          <t>来去缝</t>
-        </is>
-      </c>
-    </row>
-    <row r="45">
-      <c r="A45" t="inlineStr">
-        <is>
-          <t>牙签线</t>
-        </is>
-      </c>
-    </row>
-    <row r="46">
-      <c r="A46" t="inlineStr">
-        <is>
-          <t>落行窄针小双线</t>
-        </is>
-      </c>
-    </row>
-    <row r="47">
-      <c r="A47" t="inlineStr">
-        <is>
-          <t>龅牙线</t>
+    </row>
+    <row r="132">
+      <c r="A132" t="inlineStr">
+        <is>
+          <t>高周波</t>
         </is>
       </c>
     </row>
   </sheetData>
+  <mergeCells count="3">
+    <mergeCell ref="A43"/>
+    <mergeCell ref="A1:E1"/>
+    <mergeCell ref="A25:E25"/>
+  </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/config/成衣工艺单_设计师填表模板_v7.xlsx
+++ b/config/成衣工艺单_设计师填表模板_v7.xlsx
@@ -230,7 +230,7 @@
       <sz val="11"/>
     </font>
   </fonts>
-  <fills count="42">
+  <fills count="43">
     <fill>
       <patternFill/>
     </fill>
@@ -472,6 +472,11 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="00548235"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00595959"/>
       </patternFill>
     </fill>
   </fills>
@@ -794,7 +799,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="30">
+  <cellXfs count="32">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -861,12 +866,18 @@
     </xf>
     <xf numFmtId="0" fontId="28" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="27" fillId="39" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="42" borderId="14" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="29" fillId="40" borderId="14" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="14" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="27" fillId="40" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="41" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="49">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
@@ -2190,15 +2201,24 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E110"/>
+  <dimension ref="A1:E133"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
     <col width="28" customWidth="1" min="2" max="2"/>
     <col width="28" customWidth="1" min="3" max="3"/>
-    <col width="22" customWidth="1" min="4" max="4"/>
-    <col width="22" customWidth="1" min="5" max="5"/>
-    <col width="22" customWidth="1" min="6" max="6"/>
+    <col width="28" customWidth="1" min="4" max="4"/>
+    <col width="28" customWidth="1" min="5" max="5"/>
+    <col width="28" customWidth="1" min="6" max="6"/>
+    <col width="28" customWidth="1" min="7" max="7"/>
+    <col width="28" customWidth="1" min="8" max="8"/>
+    <col width="28" customWidth="1" min="9" max="9"/>
+    <col width="28" customWidth="1" min="10" max="10"/>
+    <col width="28" customWidth="1" min="11" max="11"/>
+    <col width="28" customWidth="1" min="12" max="12"/>
+    <col width="28" customWidth="1" min="13" max="13"/>
+    <col width="28" customWidth="1" min="14" max="14"/>
+    <col width="28" customWidth="1" min="15" max="15"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -2226,12 +2246,12 @@
       </c>
       <c r="B2" s="26" t="inlineStr">
         <is>
+          <t>0.2边线</t>
+        </is>
+      </c>
+      <c r="C2" s="26" t="inlineStr">
+        <is>
           <t>丝印烫标</t>
-        </is>
-      </c>
-      <c r="C2" s="26" t="inlineStr">
-        <is>
-          <t>0.2边线</t>
         </is>
       </c>
     </row>
@@ -2243,12 +2263,12 @@
       </c>
       <c r="B3" s="26" t="inlineStr">
         <is>
+          <t>0.5单线</t>
+        </is>
+      </c>
+      <c r="C3" s="26" t="inlineStr">
+        <is>
           <t>吊染</t>
-        </is>
-      </c>
-      <c r="C3" s="26" t="inlineStr">
-        <is>
-          <t>0.5单线</t>
         </is>
       </c>
     </row>
@@ -2260,12 +2280,12 @@
       </c>
       <c r="B4" s="26" t="inlineStr">
         <is>
+          <t>2号反底</t>
+        </is>
+      </c>
+      <c r="C4" s="26" t="inlineStr">
+        <is>
           <t>喷色</t>
-        </is>
-      </c>
-      <c r="C4" s="26" t="inlineStr">
-        <is>
-          <t>2号反底</t>
         </is>
       </c>
     </row>
@@ -2277,12 +2297,12 @@
       </c>
       <c r="B5" s="26" t="inlineStr">
         <is>
+          <t>三针五线大哈苏</t>
+        </is>
+      </c>
+      <c r="C5" s="26" t="inlineStr">
+        <is>
           <t>喷马骝</t>
-        </is>
-      </c>
-      <c r="C5" s="26" t="inlineStr">
-        <is>
-          <t>三针五线大哈苏</t>
         </is>
       </c>
     </row>
@@ -2294,12 +2314,12 @@
       </c>
       <c r="B6" s="26" t="inlineStr">
         <is>
+          <t>三针四线</t>
+        </is>
+      </c>
+      <c r="C6" s="26" t="inlineStr">
+        <is>
           <t>成衣刻字膜</t>
-        </is>
-      </c>
-      <c r="C6" s="26" t="inlineStr">
-        <is>
-          <t>三针四线</t>
         </is>
       </c>
     </row>
@@ -2311,12 +2331,12 @@
       </c>
       <c r="B7" s="26" t="inlineStr">
         <is>
+          <t>两针四线大哈苏</t>
+        </is>
+      </c>
+      <c r="C7" s="26" t="inlineStr">
+        <is>
           <t>手擦</t>
-        </is>
-      </c>
-      <c r="C7" s="26" t="inlineStr">
-        <is>
-          <t>两针四线大哈苏</t>
         </is>
       </c>
     </row>
@@ -2328,12 +2348,12 @@
       </c>
       <c r="B8" s="26" t="inlineStr">
         <is>
+          <t>分中坎</t>
+        </is>
+      </c>
+      <c r="C8" s="26" t="inlineStr">
+        <is>
           <t>扎染</t>
-        </is>
-      </c>
-      <c r="C8" s="26" t="inlineStr">
-        <is>
-          <t>分中坎</t>
         </is>
       </c>
     </row>
@@ -2345,12 +2365,12 @@
       </c>
       <c r="B9" s="26" t="inlineStr">
         <is>
+          <t>压胶</t>
+        </is>
+      </c>
+      <c r="C9" s="26" t="inlineStr">
+        <is>
           <t>无缝压胶</t>
-        </is>
-      </c>
-      <c r="C9" s="26" t="inlineStr">
-        <is>
-          <t>压胶</t>
         </is>
       </c>
     </row>
@@ -2362,12 +2382,12 @@
       </c>
       <c r="B10" s="26" t="inlineStr">
         <is>
+          <t>哨牙线</t>
+        </is>
+      </c>
+      <c r="C10" s="26" t="inlineStr">
+        <is>
           <t>普洗</t>
-        </is>
-      </c>
-      <c r="C10" s="26" t="inlineStr">
-        <is>
-          <t>哨牙线</t>
         </is>
       </c>
     </row>
@@ -2379,12 +2399,12 @@
       </c>
       <c r="B11" s="26" t="inlineStr">
         <is>
+          <t>坎双线</t>
+        </is>
+      </c>
+      <c r="C11" s="26" t="inlineStr">
+        <is>
           <t>水床冲孔</t>
-        </is>
-      </c>
-      <c r="C11" s="26" t="inlineStr">
-        <is>
-          <t>坎双线</t>
         </is>
       </c>
     </row>
@@ -2396,12 +2416,12 @@
       </c>
       <c r="B12" s="26" t="inlineStr">
         <is>
+          <t>小两针四线小哈苏</t>
+        </is>
+      </c>
+      <c r="C12" s="26" t="inlineStr">
+        <is>
           <t>激光烧花</t>
-        </is>
-      </c>
-      <c r="C12" s="26" t="inlineStr">
-        <is>
-          <t>小两针四线小哈苏</t>
         </is>
       </c>
     </row>
@@ -2413,12 +2433,12 @@
       </c>
       <c r="B13" s="26" t="inlineStr">
         <is>
+          <t>小分中坎</t>
+        </is>
+      </c>
+      <c r="C13" s="26" t="inlineStr">
+        <is>
           <t>炒盐</t>
-        </is>
-      </c>
-      <c r="C13" s="26" t="inlineStr">
-        <is>
-          <t>小分中坎</t>
         </is>
       </c>
     </row>
@@ -2430,12 +2450,12 @@
       </c>
       <c r="B14" s="26" t="inlineStr">
         <is>
+          <t>小双线（窄针）</t>
+        </is>
+      </c>
+      <c r="C14" s="26" t="inlineStr">
+        <is>
           <t>炒色</t>
-        </is>
-      </c>
-      <c r="C14" s="26" t="inlineStr">
-        <is>
-          <t>小双线（窄针）</t>
         </is>
       </c>
     </row>
@@ -2447,12 +2467,12 @@
       </c>
       <c r="B15" s="26" t="inlineStr">
         <is>
+          <t>峰哥工艺线（高弹丝）</t>
+        </is>
+      </c>
+      <c r="C15" s="26" t="inlineStr">
+        <is>
           <t>炒雪花</t>
-        </is>
-      </c>
-      <c r="C15" s="26" t="inlineStr">
-        <is>
-          <t>峰哥工艺线（高弹丝）</t>
         </is>
       </c>
     </row>
@@ -2464,12 +2484,12 @@
       </c>
       <c r="B16" s="26" t="inlineStr">
         <is>
+          <t>来去缝</t>
+        </is>
+      </c>
+      <c r="C16" s="26" t="inlineStr">
+        <is>
           <t>砂洗</t>
-        </is>
-      </c>
-      <c r="C16" s="26" t="inlineStr">
-        <is>
-          <t>来去缝</t>
         </is>
       </c>
     </row>
@@ -2481,12 +2501,12 @@
       </c>
       <c r="B17" s="26" t="inlineStr">
         <is>
+          <t>牙签线</t>
+        </is>
+      </c>
+      <c r="C17" s="26" t="inlineStr">
+        <is>
           <t>破坏</t>
-        </is>
-      </c>
-      <c r="C17" s="26" t="inlineStr">
-        <is>
-          <t>牙签线</t>
         </is>
       </c>
     </row>
@@ -2498,12 +2518,12 @@
       </c>
       <c r="B18" s="26" t="inlineStr">
         <is>
+          <t>落行窄针小双线</t>
+        </is>
+      </c>
+      <c r="C18" s="26" t="inlineStr">
+        <is>
           <t>背胶章仔绣</t>
-        </is>
-      </c>
-      <c r="C18" s="26" t="inlineStr">
-        <is>
-          <t>落行窄针小双线</t>
         </is>
       </c>
     </row>
@@ -2515,12 +2535,12 @@
       </c>
       <c r="B19" s="26" t="inlineStr">
         <is>
+          <t>龅牙线</t>
+        </is>
+      </c>
+      <c r="C19" s="26" t="inlineStr">
+        <is>
           <t>酵洗</t>
-        </is>
-      </c>
-      <c r="C19" s="26" t="inlineStr">
-        <is>
-          <t>龅牙线</t>
         </is>
       </c>
     </row>
@@ -2530,7 +2550,7 @@
           <t>吊染</t>
         </is>
       </c>
-      <c r="B20" s="26" t="inlineStr">
+      <c r="C20" s="26" t="inlineStr">
         <is>
           <t>高弹肤感硅胶</t>
         </is>
@@ -2872,325 +2892,310 @@
         </is>
       </c>
     </row>
-    <row r="71">
-      <c r="A71" s="27" t="inlineStr">
-        <is>
-          <t>工艺制作（类别展示）</t>
-        </is>
-      </c>
-    </row>
     <row r="72">
-      <c r="A72" s="28" t="inlineStr">
+      <c r="A72" s="27" t="inlineStr">
+        <is>
+          <t>工艺制作（类别展示，仅供设计师参考）</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" s="28" t="inlineStr">
         <is>
           <t>洗水</t>
         </is>
       </c>
-      <c r="B72" s="28" t="inlineStr">
+      <c r="B73" s="28" t="inlineStr">
         <is>
           <t>热转压印</t>
         </is>
       </c>
-      <c r="C72" s="28" t="inlineStr">
+      <c r="C73" s="28" t="inlineStr">
         <is>
           <t>直喷印花</t>
         </is>
       </c>
-      <c r="D72" s="28" t="inlineStr">
+      <c r="D73" s="28" t="inlineStr">
         <is>
           <t>绣花</t>
         </is>
       </c>
-      <c r="E72" s="28" t="inlineStr">
+      <c r="E73" s="28" t="inlineStr">
         <is>
           <t>网板印花</t>
-        </is>
-      </c>
-    </row>
-    <row r="73">
-      <c r="A73" s="29" t="inlineStr">
-        <is>
-          <t>吊染</t>
-        </is>
-      </c>
-      <c r="B73" s="29" t="inlineStr">
-        <is>
-          <t>丝印刻字膜烫标</t>
-        </is>
-      </c>
-      <c r="C73" s="29" t="inlineStr">
-        <is>
-          <t>数码直喷/不打底</t>
-        </is>
-      </c>
-      <c r="D73" s="29" t="inlineStr">
-        <is>
-          <t>V字针绣</t>
-        </is>
-      </c>
-      <c r="E73" s="29" t="inlineStr">
-        <is>
-          <t>仿拨印</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" s="29" t="inlineStr">
         <is>
-          <t>喷色</t>
+          <t>吊染</t>
         </is>
       </c>
       <c r="B74" s="29" t="inlineStr">
         <is>
-          <t>丝印烫标（加防升华）</t>
+          <t>丝印刻字膜烫标</t>
         </is>
       </c>
       <c r="C74" s="29" t="inlineStr">
         <is>
-          <t>数码直喷/打底</t>
+          <t>数码直喷/不打底</t>
         </is>
       </c>
       <c r="D74" s="29" t="inlineStr">
         <is>
-          <t>一字绣（特种专机）</t>
+          <t>V字针绣</t>
         </is>
       </c>
       <c r="E74" s="29" t="inlineStr">
         <is>
-          <t>光感印</t>
+          <t>仿拨印</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" s="29" t="inlineStr">
         <is>
-          <t>喷马骝</t>
+          <t>喷色</t>
         </is>
       </c>
       <c r="B75" s="29" t="inlineStr">
         <is>
-          <t>刻字膜</t>
+          <t>丝印烫标（加防升华）</t>
         </is>
       </c>
       <c r="C75" s="29" t="inlineStr">
         <is>
-          <t>热转印/热升华</t>
+          <t>数码直喷/打底</t>
         </is>
       </c>
       <c r="D75" s="29" t="inlineStr">
         <is>
-          <t>中空绣</t>
+          <t>一字绣（特种专机）</t>
         </is>
       </c>
       <c r="E75" s="29" t="inlineStr">
         <is>
-          <t>厚板印</t>
+          <t>光感印</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" s="29" t="inlineStr">
         <is>
-          <t>手擦</t>
+          <t>喷马骝</t>
         </is>
       </c>
       <c r="B76" s="29" t="inlineStr">
         <is>
-          <t>压褶</t>
+          <t>刻字膜</t>
         </is>
       </c>
       <c r="C76" s="29" t="inlineStr">
         <is>
-          <t>白墨直喷/不打底</t>
+          <t>热转印/热升华</t>
         </is>
       </c>
       <c r="D76" s="29" t="inlineStr">
         <is>
-          <t>人字车</t>
+          <t>中空绣</t>
         </is>
       </c>
       <c r="E76" s="29" t="inlineStr">
         <is>
-          <t>反光浆</t>
+          <t>厚板印</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" s="29" t="inlineStr">
         <is>
-          <t>扎染</t>
+          <t>手擦</t>
         </is>
       </c>
       <c r="B77" s="29" t="inlineStr">
         <is>
-          <t>厚版肤感弹力硅胶章</t>
+          <t>压褶</t>
         </is>
       </c>
       <c r="C77" s="29" t="inlineStr">
         <is>
-          <t>白墨直喷/打底</t>
+          <t>白墨直喷/不打底</t>
         </is>
       </c>
       <c r="D77" s="29" t="inlineStr">
         <is>
-          <t>充棉工艺</t>
+          <t>人字车</t>
         </is>
       </c>
       <c r="E77" s="29" t="inlineStr">
         <is>
-          <t>发泡印</t>
+          <t>反光浆</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" s="29" t="inlineStr">
         <is>
-          <t>炒盐</t>
+          <t>扎染</t>
         </is>
       </c>
       <c r="B78" s="29" t="inlineStr">
         <is>
-          <t>反光刻字膜</t>
-        </is>
-      </c>
-      <c r="C78" s="29" t="inlineStr"/>
+          <t>厚版肤感弹力硅胶章</t>
+        </is>
+      </c>
+      <c r="C78" s="29" t="inlineStr">
+        <is>
+          <t>白墨直喷/打底</t>
+        </is>
+      </c>
       <c r="D78" s="29" t="inlineStr">
         <is>
-          <t>包边绣</t>
+          <t>充棉工艺</t>
         </is>
       </c>
       <c r="E78" s="29" t="inlineStr">
         <is>
-          <t>哑光胶浆</t>
+          <t>发泡印</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" s="29" t="inlineStr">
         <is>
-          <t>炒色</t>
+          <t>炒盐</t>
         </is>
       </c>
       <c r="B79" s="29" t="inlineStr">
         <is>
-          <t>激光冲孔</t>
+          <t>反光刻字膜</t>
         </is>
       </c>
       <c r="C79" s="29" t="inlineStr"/>
       <c r="D79" s="29" t="inlineStr">
         <is>
-          <t>十字绣</t>
+          <t>包边绣</t>
         </is>
       </c>
       <c r="E79" s="29" t="inlineStr">
         <is>
-          <t>彩色硅胶印</t>
+          <t>哑光胶浆</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" s="29" t="inlineStr">
         <is>
-          <t>炒雪花</t>
+          <t>炒色</t>
         </is>
       </c>
       <c r="B80" s="29" t="inlineStr">
         <is>
-          <t>烫画</t>
+          <t>激光冲孔</t>
         </is>
       </c>
       <c r="C80" s="29" t="inlineStr"/>
       <c r="D80" s="29" t="inlineStr">
         <is>
-          <t>平绣</t>
+          <t>十字绣</t>
         </is>
       </c>
       <c r="E80" s="29" t="inlineStr">
         <is>
-          <t>拉浆/石头浆</t>
+          <t>彩色硅胶印</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" s="29" t="inlineStr">
         <is>
-          <t>砂洗</t>
+          <t>炒雪花</t>
         </is>
       </c>
       <c r="B81" s="29" t="inlineStr">
         <is>
-          <t>热转印</t>
+          <t>烫画</t>
         </is>
       </c>
       <c r="C81" s="29" t="inlineStr"/>
       <c r="D81" s="29" t="inlineStr">
         <is>
-          <t>挨针绣</t>
+          <t>平绣</t>
         </is>
       </c>
       <c r="E81" s="29" t="inlineStr">
         <is>
-          <t>拨印</t>
+          <t>拉浆/石头浆</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" s="29" t="inlineStr">
         <is>
-          <t>碧纹染</t>
+          <t>砂洗</t>
         </is>
       </c>
       <c r="B82" s="29" t="inlineStr">
         <is>
-          <t>立体钢印</t>
+          <t>热转印</t>
         </is>
       </c>
       <c r="C82" s="29" t="inlineStr"/>
       <c r="D82" s="29" t="inlineStr">
         <is>
-          <t>明星特种专机-207</t>
+          <t>挨针绣</t>
         </is>
       </c>
       <c r="E82" s="29" t="inlineStr">
         <is>
-          <t>植绒印花</t>
+          <t>拨印</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" s="29" t="inlineStr">
         <is>
-          <t>酵洗</t>
+          <t>碧纹染</t>
         </is>
       </c>
       <c r="B83" s="29" t="inlineStr">
         <is>
-          <t>高周波</t>
+          <t>立体钢印</t>
         </is>
       </c>
       <c r="C83" s="29" t="inlineStr"/>
       <c r="D83" s="29" t="inlineStr">
         <is>
-          <t>榻榻米绣</t>
+          <t>明星特种专机-207</t>
         </is>
       </c>
       <c r="E83" s="29" t="inlineStr">
         <is>
-          <t>水显印</t>
+          <t>植绒印花</t>
         </is>
       </c>
     </row>
     <row r="84">
-      <c r="A84" s="29" t="inlineStr"/>
-      <c r="B84" s="29" t="inlineStr"/>
+      <c r="A84" s="29" t="inlineStr">
+        <is>
+          <t>酵洗</t>
+        </is>
+      </c>
+      <c r="B84" s="29" t="inlineStr">
+        <is>
+          <t>高周波</t>
+        </is>
+      </c>
       <c r="C84" s="29" t="inlineStr"/>
       <c r="D84" s="29" t="inlineStr">
         <is>
-          <t>毛巾绣</t>
+          <t>榻榻米绣</t>
         </is>
       </c>
       <c r="E84" s="29" t="inlineStr">
         <is>
-          <t>水浆</t>
+          <t>水显印</t>
         </is>
       </c>
     </row>
@@ -3200,12 +3205,12 @@
       <c r="C85" s="29" t="inlineStr"/>
       <c r="D85" s="29" t="inlineStr">
         <is>
-          <t>牙刷绣</t>
+          <t>毛巾绣</t>
         </is>
       </c>
       <c r="E85" s="29" t="inlineStr">
         <is>
-          <t>活性印花</t>
+          <t>水浆</t>
         </is>
       </c>
     </row>
@@ -3215,12 +3220,12 @@
       <c r="C86" s="29" t="inlineStr"/>
       <c r="D86" s="29" t="inlineStr">
         <is>
-          <t>珠片绣</t>
+          <t>牙刷绣</t>
         </is>
       </c>
       <c r="E86" s="29" t="inlineStr">
         <is>
-          <t>温变印</t>
+          <t>活性印花</t>
         </is>
       </c>
     </row>
@@ -3230,12 +3235,12 @@
       <c r="C87" s="29" t="inlineStr"/>
       <c r="D87" s="29" t="inlineStr">
         <is>
-          <t>立体绣</t>
+          <t>珠片绣</t>
         </is>
       </c>
       <c r="E87" s="29" t="inlineStr">
         <is>
-          <t>烫金/烫银</t>
+          <t>温变印</t>
         </is>
       </c>
     </row>
@@ -3245,12 +3250,12 @@
       <c r="C88" s="29" t="inlineStr"/>
       <c r="D88" s="29" t="inlineStr">
         <is>
-          <t>绳绣</t>
+          <t>立体绣</t>
         </is>
       </c>
       <c r="E88" s="29" t="inlineStr">
         <is>
-          <t>热固油墨</t>
+          <t>烫金/烫银</t>
         </is>
       </c>
     </row>
@@ -3260,12 +3265,12 @@
       <c r="C89" s="29" t="inlineStr"/>
       <c r="D89" s="29" t="inlineStr">
         <is>
-          <t>菱形打边绣（特种专机）</t>
+          <t>绳绣</t>
         </is>
       </c>
       <c r="E89" s="29" t="inlineStr">
         <is>
-          <t>硅胶印</t>
+          <t>热固油墨</t>
         </is>
       </c>
     </row>
@@ -3275,12 +3280,12 @@
       <c r="C90" s="29" t="inlineStr"/>
       <c r="D90" s="29" t="inlineStr">
         <is>
-          <t>贴布绣</t>
+          <t>菱形打边绣（特种专机）</t>
         </is>
       </c>
       <c r="E90" s="29" t="inlineStr">
         <is>
-          <t>网点印</t>
+          <t>硅胶印</t>
         </is>
       </c>
     </row>
@@ -3290,12 +3295,12 @@
       <c r="C91" s="29" t="inlineStr"/>
       <c r="D91" s="29" t="inlineStr">
         <is>
-          <t>锁链绣</t>
+          <t>贴布绣</t>
         </is>
       </c>
       <c r="E91" s="29" t="inlineStr">
         <is>
-          <t>裂纹印</t>
+          <t>网点印</t>
         </is>
       </c>
     </row>
@@ -3305,227 +3310,383 @@
       <c r="C92" s="29" t="inlineStr"/>
       <c r="D92" s="29" t="inlineStr">
         <is>
+          <t>锁链绣</t>
+        </is>
+      </c>
+      <c r="E92" s="29" t="inlineStr">
+        <is>
+          <t>裂纹印</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" s="29" t="inlineStr"/>
+      <c r="B93" s="29" t="inlineStr"/>
+      <c r="C93" s="29" t="inlineStr"/>
+      <c r="D93" s="29" t="inlineStr">
+        <is>
           <t>镂空绣</t>
         </is>
       </c>
-      <c r="E92" s="29" t="inlineStr">
+      <c r="E93" s="29" t="inlineStr">
         <is>
           <t>轻薄热固油墨</t>
         </is>
       </c>
     </row>
-    <row r="95">
-      <c r="A95" s="27" t="inlineStr">
-        <is>
-          <t>车缝工艺（类别展示）</t>
-        </is>
-      </c>
-    </row>
     <row r="96">
-      <c r="A96" s="28" t="inlineStr">
+      <c r="A96" s="30" t="inlineStr">
+        <is>
+          <t>车缝工艺（类别展示，仅供设计师参考）</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" s="28" t="inlineStr">
+        <is>
+          <t>车缝工艺</t>
+        </is>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" s="29" t="inlineStr">
+        <is>
+          <t>0.2边线</t>
+        </is>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" s="29" t="inlineStr">
+        <is>
+          <t>0.5单线</t>
+        </is>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" s="29" t="inlineStr">
+        <is>
+          <t>2号反底</t>
+        </is>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" s="29" t="inlineStr">
+        <is>
+          <t>三针五线大哈苏</t>
+        </is>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" s="29" t="inlineStr">
+        <is>
+          <t>三针四线</t>
+        </is>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" s="29" t="inlineStr">
+        <is>
+          <t>两针四线大哈苏</t>
+        </is>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" s="29" t="inlineStr">
+        <is>
+          <t>分中坎</t>
+        </is>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" s="29" t="inlineStr">
+        <is>
+          <t>压胶</t>
+        </is>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" s="29" t="inlineStr">
+        <is>
+          <t>哨牙线</t>
+        </is>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" s="29" t="inlineStr">
+        <is>
+          <t>坎双线</t>
+        </is>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" s="29" t="inlineStr">
+        <is>
+          <t>小两针四线小哈苏</t>
+        </is>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" s="29" t="inlineStr">
+        <is>
+          <t>小分中坎</t>
+        </is>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" s="29" t="inlineStr">
+        <is>
+          <t>小双线（窄针）</t>
+        </is>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" s="29" t="inlineStr">
+        <is>
+          <t>峰哥工艺线（高弹丝）</t>
+        </is>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" s="29" t="inlineStr">
+        <is>
+          <t>来去缝</t>
+        </is>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" s="29" t="inlineStr">
+        <is>
+          <t>牙签线</t>
+        </is>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" s="29" t="inlineStr">
+        <is>
+          <t>落行窄针小双线</t>
+        </is>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" s="29" t="inlineStr">
+        <is>
+          <t>龅牙线</t>
+        </is>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" s="31" t="inlineStr">
+        <is>
+          <t>成衣工艺（类别展示，仅供设计师参考）</t>
+        </is>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" s="28" t="inlineStr">
         <is>
           <t>无缝</t>
         </is>
       </c>
-      <c r="B96" s="28" t="inlineStr">
+      <c r="B119" s="28" t="inlineStr">
         <is>
           <t>洗水</t>
         </is>
       </c>
-      <c r="C96" s="28" t="inlineStr">
+      <c r="C119" s="28" t="inlineStr">
         <is>
           <t>热转压印</t>
         </is>
       </c>
-      <c r="D96" s="28" t="inlineStr">
+      <c r="D119" s="28" t="inlineStr">
         <is>
           <t>绣花</t>
         </is>
       </c>
-      <c r="E96" s="28" t="inlineStr">
+      <c r="E119" s="28" t="inlineStr">
         <is>
           <t>网板印花</t>
         </is>
       </c>
     </row>
-    <row r="97">
-      <c r="A97" s="29" t="inlineStr">
+    <row r="120">
+      <c r="A120" s="29" t="inlineStr">
         <is>
           <t>无缝压胶</t>
         </is>
       </c>
-      <c r="B97" s="29" t="inlineStr">
+      <c r="B120" s="29" t="inlineStr">
         <is>
           <t>吊染</t>
         </is>
       </c>
-      <c r="C97" s="29" t="inlineStr">
+      <c r="C120" s="29" t="inlineStr">
         <is>
           <t>成衣刻字膜</t>
         </is>
       </c>
-      <c r="D97" s="29" t="inlineStr">
+      <c r="D120" s="29" t="inlineStr">
         <is>
           <t>背胶章仔绣</t>
         </is>
       </c>
-      <c r="E97" s="29" t="inlineStr">
+      <c r="E120" s="29" t="inlineStr">
         <is>
           <t>丝印烫标</t>
         </is>
       </c>
     </row>
-    <row r="98">
-      <c r="A98" s="29" t="inlineStr"/>
-      <c r="B98" s="29" t="inlineStr">
+    <row r="121">
+      <c r="A121" s="29" t="inlineStr"/>
+      <c r="B121" s="29" t="inlineStr">
         <is>
           <t>喷色</t>
         </is>
       </c>
-      <c r="C98" s="29" t="inlineStr">
+      <c r="C121" s="29" t="inlineStr">
         <is>
           <t>高弹肤感硅胶</t>
         </is>
       </c>
-      <c r="D98" s="29" t="inlineStr"/>
-      <c r="E98" s="29" t="inlineStr"/>
-    </row>
-    <row r="99">
-      <c r="A99" s="29" t="inlineStr"/>
-      <c r="B99" s="29" t="inlineStr">
+      <c r="D121" s="29" t="inlineStr"/>
+      <c r="E121" s="29" t="inlineStr"/>
+    </row>
+    <row r="122">
+      <c r="A122" s="29" t="inlineStr"/>
+      <c r="B122" s="29" t="inlineStr">
         <is>
           <t>喷马骝</t>
         </is>
       </c>
-      <c r="C99" s="29" t="inlineStr"/>
-      <c r="D99" s="29" t="inlineStr"/>
-      <c r="E99" s="29" t="inlineStr"/>
-    </row>
-    <row r="100">
-      <c r="A100" s="29" t="inlineStr"/>
-      <c r="B100" s="29" t="inlineStr">
+      <c r="C122" s="29" t="inlineStr"/>
+      <c r="D122" s="29" t="inlineStr"/>
+      <c r="E122" s="29" t="inlineStr"/>
+    </row>
+    <row r="123">
+      <c r="A123" s="29" t="inlineStr"/>
+      <c r="B123" s="29" t="inlineStr">
         <is>
           <t>手擦</t>
         </is>
       </c>
-      <c r="C100" s="29" t="inlineStr"/>
-      <c r="D100" s="29" t="inlineStr"/>
-      <c r="E100" s="29" t="inlineStr"/>
-    </row>
-    <row r="101">
-      <c r="A101" s="29" t="inlineStr"/>
-      <c r="B101" s="29" t="inlineStr">
+      <c r="C123" s="29" t="inlineStr"/>
+      <c r="D123" s="29" t="inlineStr"/>
+      <c r="E123" s="29" t="inlineStr"/>
+    </row>
+    <row r="124">
+      <c r="A124" s="29" t="inlineStr"/>
+      <c r="B124" s="29" t="inlineStr">
         <is>
           <t>扎染</t>
         </is>
       </c>
-      <c r="C101" s="29" t="inlineStr"/>
-      <c r="D101" s="29" t="inlineStr"/>
-      <c r="E101" s="29" t="inlineStr"/>
-    </row>
-    <row r="102">
-      <c r="A102" s="29" t="inlineStr"/>
-      <c r="B102" s="29" t="inlineStr">
+      <c r="C124" s="29" t="inlineStr"/>
+      <c r="D124" s="29" t="inlineStr"/>
+      <c r="E124" s="29" t="inlineStr"/>
+    </row>
+    <row r="125">
+      <c r="A125" s="29" t="inlineStr"/>
+      <c r="B125" s="29" t="inlineStr">
         <is>
           <t>普洗</t>
         </is>
       </c>
-      <c r="C102" s="29" t="inlineStr"/>
-      <c r="D102" s="29" t="inlineStr"/>
-      <c r="E102" s="29" t="inlineStr"/>
-    </row>
-    <row r="103">
-      <c r="A103" s="29" t="inlineStr"/>
-      <c r="B103" s="29" t="inlineStr">
+      <c r="C125" s="29" t="inlineStr"/>
+      <c r="D125" s="29" t="inlineStr"/>
+      <c r="E125" s="29" t="inlineStr"/>
+    </row>
+    <row r="126">
+      <c r="A126" s="29" t="inlineStr"/>
+      <c r="B126" s="29" t="inlineStr">
         <is>
           <t>水床冲孔</t>
         </is>
       </c>
-      <c r="C103" s="29" t="inlineStr"/>
-      <c r="D103" s="29" t="inlineStr"/>
-      <c r="E103" s="29" t="inlineStr"/>
-    </row>
-    <row r="104">
-      <c r="A104" s="29" t="inlineStr"/>
-      <c r="B104" s="29" t="inlineStr">
+      <c r="C126" s="29" t="inlineStr"/>
+      <c r="D126" s="29" t="inlineStr"/>
+      <c r="E126" s="29" t="inlineStr"/>
+    </row>
+    <row r="127">
+      <c r="A127" s="29" t="inlineStr"/>
+      <c r="B127" s="29" t="inlineStr">
         <is>
           <t>激光烧花</t>
         </is>
       </c>
-      <c r="C104" s="29" t="inlineStr"/>
-      <c r="D104" s="29" t="inlineStr"/>
-      <c r="E104" s="29" t="inlineStr"/>
-    </row>
-    <row r="105">
-      <c r="A105" s="29" t="inlineStr"/>
-      <c r="B105" s="29" t="inlineStr">
+      <c r="C127" s="29" t="inlineStr"/>
+      <c r="D127" s="29" t="inlineStr"/>
+      <c r="E127" s="29" t="inlineStr"/>
+    </row>
+    <row r="128">
+      <c r="A128" s="29" t="inlineStr"/>
+      <c r="B128" s="29" t="inlineStr">
         <is>
           <t>炒盐</t>
         </is>
       </c>
-      <c r="C105" s="29" t="inlineStr"/>
-      <c r="D105" s="29" t="inlineStr"/>
-      <c r="E105" s="29" t="inlineStr"/>
-    </row>
-    <row r="106">
-      <c r="A106" s="29" t="inlineStr"/>
-      <c r="B106" s="29" t="inlineStr">
+      <c r="C128" s="29" t="inlineStr"/>
+      <c r="D128" s="29" t="inlineStr"/>
+      <c r="E128" s="29" t="inlineStr"/>
+    </row>
+    <row r="129">
+      <c r="A129" s="29" t="inlineStr"/>
+      <c r="B129" s="29" t="inlineStr">
         <is>
           <t>炒色</t>
         </is>
       </c>
-      <c r="C106" s="29" t="inlineStr"/>
-      <c r="D106" s="29" t="inlineStr"/>
-      <c r="E106" s="29" t="inlineStr"/>
-    </row>
-    <row r="107">
-      <c r="A107" s="29" t="inlineStr"/>
-      <c r="B107" s="29" t="inlineStr">
+      <c r="C129" s="29" t="inlineStr"/>
+      <c r="D129" s="29" t="inlineStr"/>
+      <c r="E129" s="29" t="inlineStr"/>
+    </row>
+    <row r="130">
+      <c r="A130" s="29" t="inlineStr"/>
+      <c r="B130" s="29" t="inlineStr">
         <is>
           <t>炒雪花</t>
         </is>
       </c>
-      <c r="C107" s="29" t="inlineStr"/>
-      <c r="D107" s="29" t="inlineStr"/>
-      <c r="E107" s="29" t="inlineStr"/>
-    </row>
-    <row r="108">
-      <c r="A108" s="29" t="inlineStr"/>
-      <c r="B108" s="29" t="inlineStr">
+      <c r="C130" s="29" t="inlineStr"/>
+      <c r="D130" s="29" t="inlineStr"/>
+      <c r="E130" s="29" t="inlineStr"/>
+    </row>
+    <row r="131">
+      <c r="A131" s="29" t="inlineStr"/>
+      <c r="B131" s="29" t="inlineStr">
         <is>
           <t>砂洗</t>
         </is>
       </c>
-      <c r="C108" s="29" t="inlineStr"/>
-      <c r="D108" s="29" t="inlineStr"/>
-      <c r="E108" s="29" t="inlineStr"/>
-    </row>
-    <row r="109">
-      <c r="A109" s="29" t="inlineStr"/>
-      <c r="B109" s="29" t="inlineStr">
+      <c r="C131" s="29" t="inlineStr"/>
+      <c r="D131" s="29" t="inlineStr"/>
+      <c r="E131" s="29" t="inlineStr"/>
+    </row>
+    <row r="132">
+      <c r="A132" s="29" t="inlineStr"/>
+      <c r="B132" s="29" t="inlineStr">
         <is>
           <t>破坏</t>
         </is>
       </c>
-      <c r="C109" s="29" t="inlineStr"/>
-      <c r="D109" s="29" t="inlineStr"/>
-      <c r="E109" s="29" t="inlineStr"/>
-    </row>
-    <row r="110">
-      <c r="A110" s="29" t="inlineStr"/>
-      <c r="B110" s="29" t="inlineStr">
+      <c r="C132" s="29" t="inlineStr"/>
+      <c r="D132" s="29" t="inlineStr"/>
+      <c r="E132" s="29" t="inlineStr"/>
+    </row>
+    <row r="133">
+      <c r="A133" s="29" t="inlineStr"/>
+      <c r="B133" s="29" t="inlineStr">
         <is>
           <t>酵洗</t>
         </is>
       </c>
-      <c r="C110" s="29" t="inlineStr"/>
-      <c r="D110" s="29" t="inlineStr"/>
-      <c r="E110" s="29" t="inlineStr"/>
+      <c r="C133" s="29" t="inlineStr"/>
+      <c r="D133" s="29" t="inlineStr"/>
+      <c r="E133" s="29" t="inlineStr"/>
     </row>
   </sheetData>
-  <mergeCells count="2">
-    <mergeCell ref="A95:E95"/>
-    <mergeCell ref="A71:E71"/>
+  <mergeCells count="3">
+    <mergeCell ref="A72:E72"/>
+    <mergeCell ref="A96"/>
+    <mergeCell ref="A118:E118"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/config/成衣工艺单_设计师填表模板_v7.xlsx
+++ b/config/成衣工艺单_设计师填表模板_v7.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowHeight="17325" activeTab="1"/>
+    <workbookView windowHeight="17775"/>
   </bookViews>
   <sheets>
     <sheet name="成衣工艺制单" sheetId="1" r:id="rId1"/>
@@ -3035,7 +3035,6 @@
       <c r="A20" s="4" t="s">
         <v>57</v>
       </c>
-      <c r="B20"/>
       <c r="C20" s="4" t="s">
         <v>106</v>
       </c>
